--- a/data/temp1.xlsx
+++ b/data/temp1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D71A353-73B0-401A-8EB7-6476BB57407A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD14C143-B7D4-4636-8AD3-715F5C3432EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="국내생산 계획" sheetId="1" r:id="rId1"/>
@@ -1787,7 +1787,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1826,6 +1829,13 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2020,40 +2030,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2079,11 +2074,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2427,4255 +2444,4257 @@
   <dimension ref="A1:H302"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
-    <col min="3" max="8" width="10.77734375" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="10.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
+    <col min="3" max="6" width="10.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="18" t="s">
         <v>581</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="18" t="s">
         <v>582</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="12" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="7"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="7"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="7"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="7"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="7"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="7"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="7"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="7"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="7"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="7"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="7"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="7"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="7" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="7"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="7"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="7"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="7"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="7"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="7"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="7"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="7"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="7"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="7"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="7"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="7"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="7"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="7"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="7"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="7"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="7"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="7"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="7"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="7"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="7"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="7"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="7"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="7"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="7" t="s">
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="7"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="7"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="7"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="7"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="7"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="7"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="7"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="7"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="7"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="7"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="7"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="7"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="7"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="7"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="4"/>
     </row>
     <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="7"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="7"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="7"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="7"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="7"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="7"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="7"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="4"/>
     </row>
     <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="7"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="7"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="7"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="7"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="7"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="4"/>
     </row>
     <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="7"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="7"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="7"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="7"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="7"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="4"/>
     </row>
     <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="7" t="s">
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="7"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="4"/>
     </row>
     <row r="81" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="7"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="7"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="4"/>
     </row>
     <row r="83" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="7"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="4"/>
     </row>
     <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="7"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="4"/>
     </row>
     <row r="85" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="7"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="4"/>
     </row>
     <row r="86" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="7"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="4"/>
     </row>
     <row r="87" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="7"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="4"/>
     </row>
     <row r="88" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="7"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="4"/>
     </row>
     <row r="89" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="7"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="4"/>
     </row>
     <row r="90" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="7"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="4"/>
     </row>
     <row r="91" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="7"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="4"/>
     </row>
     <row r="92" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="7"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="4"/>
     </row>
     <row r="93" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="7"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="4"/>
     </row>
     <row r="94" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="7"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="4"/>
     </row>
     <row r="95" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="7"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="4"/>
     </row>
     <row r="96" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="7"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="4"/>
     </row>
     <row r="97" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="7"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="4"/>
     </row>
     <row r="98" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="7"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="4"/>
     </row>
     <row r="99" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="7"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="4"/>
     </row>
     <row r="100" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="7"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="4"/>
     </row>
     <row r="101" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="7"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="7"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="4"/>
     </row>
     <row r="103" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="7"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="4"/>
     </row>
     <row r="104" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="7"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="4"/>
     </row>
     <row r="105" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="7"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="4"/>
     </row>
     <row r="106" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="7"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="4"/>
     </row>
     <row r="107" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="7"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="4"/>
     </row>
     <row r="108" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="7"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="4"/>
     </row>
     <row r="109" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-      <c r="E109" s="4"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="7"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="7"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="4"/>
     </row>
     <row r="111" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="7"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="4"/>
     </row>
     <row r="112" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="7"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="4"/>
     </row>
     <row r="113" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="8" t="s">
+      <c r="A113" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="7" t="s">
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="7"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="4"/>
     </row>
     <row r="115" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
-      <c r="E115" s="4"/>
-      <c r="F115" s="4"/>
-      <c r="G115" s="4"/>
-      <c r="H115" s="7"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="4"/>
     </row>
     <row r="116" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
-      <c r="H116" s="7"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="4"/>
     </row>
     <row r="117" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
-      <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="7"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="4"/>
     </row>
     <row r="118" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="7"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="4"/>
     </row>
     <row r="119" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
-      <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="7"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="4"/>
     </row>
     <row r="120" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="4"/>
-      <c r="F120" s="4"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="7"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="4"/>
     </row>
     <row r="121" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="7"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="4"/>
     </row>
     <row r="122" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="7"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="4"/>
     </row>
     <row r="123" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="4"/>
-      <c r="F123" s="4"/>
-      <c r="G123" s="4"/>
-      <c r="H123" s="7"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="4"/>
     </row>
     <row r="124" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
-      <c r="F124" s="4"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="7"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="4"/>
     </row>
     <row r="125" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
-      <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="7"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="4"/>
     </row>
     <row r="126" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="8" t="s">
+      <c r="A126" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="4"/>
-      <c r="G126" s="4"/>
-      <c r="H126" s="7" t="s">
+      <c r="B126" s="14"/>
+      <c r="C126" s="14"/>
+      <c r="D126" s="14"/>
+      <c r="E126" s="14"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="7"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="4"/>
     </row>
     <row r="128" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
-      <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="7"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+      <c r="H128" s="4"/>
     </row>
     <row r="129" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-      <c r="E129" s="4"/>
-      <c r="F129" s="4"/>
-      <c r="G129" s="4"/>
-      <c r="H129" s="7"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="4"/>
     </row>
     <row r="130" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="6" t="s">
+      <c r="A130" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-      <c r="E130" s="4"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="7"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="4"/>
     </row>
     <row r="131" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="6" t="s">
+      <c r="A131" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="4"/>
-      <c r="F131" s="4"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="7"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="4"/>
     </row>
     <row r="132" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="6" t="s">
+      <c r="A132" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-      <c r="E132" s="4"/>
-      <c r="F132" s="4"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="7"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="4"/>
     </row>
     <row r="133" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
-      <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="7"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="4"/>
     </row>
     <row r="134" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="4"/>
-      <c r="F134" s="4"/>
-      <c r="G134" s="4"/>
-      <c r="H134" s="7"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="4"/>
     </row>
     <row r="135" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="6" t="s">
+      <c r="A135" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="4"/>
-      <c r="F135" s="4"/>
-      <c r="G135" s="4"/>
-      <c r="H135" s="7"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="4"/>
     </row>
     <row r="136" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="6" t="s">
+      <c r="A136" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="4"/>
-      <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="7"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="4"/>
     </row>
     <row r="137" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="7"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="4"/>
     </row>
     <row r="138" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="6" t="s">
+      <c r="A138" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C138" s="4"/>
-      <c r="D138" s="4"/>
-      <c r="E138" s="4"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="7"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="4"/>
     </row>
     <row r="139" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="6" t="s">
+      <c r="A139" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-      <c r="E139" s="4"/>
-      <c r="F139" s="4"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="7"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="4"/>
     </row>
     <row r="140" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="6" t="s">
+      <c r="A140" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="4"/>
-      <c r="F140" s="4"/>
-      <c r="G140" s="4"/>
-      <c r="H140" s="7"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="4"/>
     </row>
     <row r="141" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B141" s="5"/>
-      <c r="C141" s="5"/>
-      <c r="D141" s="5"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="7" t="s">
+      <c r="B141" s="14"/>
+      <c r="C141" s="14"/>
+      <c r="D141" s="14"/>
+      <c r="E141" s="14"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="6" t="s">
+      <c r="A142" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="4"/>
-      <c r="F142" s="4"/>
-      <c r="G142" s="4"/>
-      <c r="H142" s="7"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="4"/>
     </row>
     <row r="143" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="6" t="s">
+      <c r="A143" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-      <c r="E143" s="4"/>
-      <c r="F143" s="4"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="7"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="4"/>
     </row>
     <row r="144" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="6" t="s">
+      <c r="A144" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C144" s="4"/>
-      <c r="D144" s="4"/>
-      <c r="E144" s="4"/>
-      <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="7"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="4"/>
     </row>
     <row r="145" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="6" t="s">
+      <c r="A145" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
-      <c r="E145" s="4"/>
-      <c r="F145" s="4"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="7"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="4"/>
     </row>
     <row r="146" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="6" t="s">
+      <c r="A146" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
-      <c r="F146" s="4"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="7"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="4"/>
     </row>
     <row r="147" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="6" t="s">
+      <c r="A147" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C147" s="4"/>
-      <c r="D147" s="4"/>
-      <c r="E147" s="4"/>
-      <c r="F147" s="4"/>
-      <c r="G147" s="4"/>
-      <c r="H147" s="7"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="4"/>
     </row>
     <row r="148" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="6" t="s">
+      <c r="A148" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C148" s="4"/>
-      <c r="D148" s="4"/>
-      <c r="E148" s="4"/>
-      <c r="F148" s="4"/>
-      <c r="G148" s="4"/>
-      <c r="H148" s="7"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="4"/>
     </row>
     <row r="149" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="8" t="s">
+      <c r="A149" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B149" s="5"/>
-      <c r="C149" s="5"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="4"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="7" t="s">
+      <c r="B149" s="14"/>
+      <c r="C149" s="14"/>
+      <c r="D149" s="14"/>
+      <c r="E149" s="14"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="6" t="s">
+      <c r="A150" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C150" s="4"/>
-      <c r="D150" s="4"/>
-      <c r="E150" s="4"/>
-      <c r="F150" s="4"/>
-      <c r="G150" s="4"/>
-      <c r="H150" s="7"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="4"/>
     </row>
     <row r="151" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="6" t="s">
+      <c r="A151" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C151" s="4"/>
-      <c r="D151" s="4"/>
-      <c r="E151" s="4"/>
-      <c r="F151" s="4"/>
-      <c r="G151" s="4"/>
-      <c r="H151" s="7"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="4"/>
     </row>
     <row r="152" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="6" t="s">
+      <c r="A152" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C152" s="4"/>
-      <c r="D152" s="4"/>
-      <c r="E152" s="4"/>
-      <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
-      <c r="H152" s="7"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="4"/>
     </row>
     <row r="153" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="6" t="s">
+      <c r="A153" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
-      <c r="F153" s="4"/>
-      <c r="G153" s="4"/>
-      <c r="H153" s="7"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="4"/>
     </row>
     <row r="154" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="6" t="s">
+      <c r="A154" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B154" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C154" s="4"/>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
-      <c r="F154" s="4"/>
-      <c r="G154" s="4"/>
-      <c r="H154" s="7"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="4"/>
     </row>
     <row r="155" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="6" t="s">
+      <c r="A155" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
-      <c r="F155" s="4"/>
-      <c r="G155" s="4"/>
-      <c r="H155" s="7"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="4"/>
     </row>
     <row r="156" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="6" t="s">
+      <c r="A156" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C156" s="4"/>
-      <c r="D156" s="4"/>
-      <c r="E156" s="4"/>
-      <c r="F156" s="4"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="7"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="4"/>
     </row>
     <row r="157" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C157" s="4"/>
-      <c r="D157" s="4"/>
-      <c r="E157" s="4"/>
-      <c r="F157" s="4"/>
-      <c r="G157" s="4"/>
-      <c r="H157" s="7"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="8" t="s">
+      <c r="A158" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B158" s="5"/>
-      <c r="C158" s="5"/>
-      <c r="D158" s="5"/>
-      <c r="E158" s="5"/>
-      <c r="F158" s="4"/>
-      <c r="G158" s="4"/>
-      <c r="H158" s="7" t="s">
+      <c r="B158" s="14"/>
+      <c r="C158" s="14"/>
+      <c r="D158" s="14"/>
+      <c r="E158" s="14"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="6" t="s">
+      <c r="A159" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-      <c r="E159" s="4"/>
-      <c r="F159" s="4"/>
-      <c r="G159" s="4"/>
-      <c r="H159" s="7"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="4"/>
     </row>
     <row r="160" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="6" t="s">
+      <c r="A160" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
-      <c r="F160" s="4"/>
-      <c r="G160" s="4"/>
-      <c r="H160" s="7"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="4"/>
     </row>
     <row r="161" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="6" t="s">
+      <c r="A161" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C161" s="4"/>
-      <c r="D161" s="4"/>
-      <c r="E161" s="4"/>
-      <c r="F161" s="4"/>
-      <c r="G161" s="4"/>
-      <c r="H161" s="7"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="4"/>
     </row>
     <row r="162" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="6" t="s">
+      <c r="A162" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C162" s="4"/>
-      <c r="D162" s="4"/>
-      <c r="E162" s="4"/>
-      <c r="F162" s="4"/>
-      <c r="G162" s="4"/>
-      <c r="H162" s="7"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="4"/>
     </row>
     <row r="163" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="6" t="s">
+      <c r="A163" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C163" s="4"/>
-      <c r="D163" s="4"/>
-      <c r="E163" s="4"/>
-      <c r="F163" s="4"/>
-      <c r="G163" s="4"/>
-      <c r="H163" s="7"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="4"/>
     </row>
     <row r="164" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="6" t="s">
+      <c r="A164" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-      <c r="E164" s="4"/>
-      <c r="F164" s="4"/>
-      <c r="G164" s="4"/>
-      <c r="H164" s="7"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="4"/>
     </row>
     <row r="165" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="6" t="s">
+      <c r="A165" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="7"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="4"/>
     </row>
     <row r="166" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="4"/>
-      <c r="F166" s="4"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="7"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="4"/>
     </row>
     <row r="167" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="6" t="s">
+      <c r="A167" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C167" s="4"/>
-      <c r="D167" s="4"/>
-      <c r="E167" s="4"/>
-      <c r="F167" s="4"/>
-      <c r="G167" s="4"/>
-      <c r="H167" s="7"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="4"/>
     </row>
     <row r="168" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="6" t="s">
+      <c r="A168" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C168" s="4"/>
-      <c r="D168" s="4"/>
-      <c r="E168" s="4"/>
-      <c r="F168" s="4"/>
-      <c r="G168" s="4"/>
-      <c r="H168" s="7"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="4"/>
     </row>
     <row r="169" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="6" t="s">
+      <c r="A169" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C169" s="4"/>
-      <c r="D169" s="4"/>
-      <c r="E169" s="4"/>
-      <c r="F169" s="4"/>
-      <c r="G169" s="4"/>
-      <c r="H169" s="7"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="4"/>
     </row>
     <row r="170" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="6" t="s">
+      <c r="A170" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C170" s="4"/>
-      <c r="D170" s="4"/>
-      <c r="E170" s="4"/>
-      <c r="F170" s="4"/>
-      <c r="G170" s="4"/>
-      <c r="H170" s="7"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="4"/>
     </row>
     <row r="171" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="6" t="s">
+      <c r="A171" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C171" s="4"/>
-      <c r="D171" s="4"/>
-      <c r="E171" s="4"/>
-      <c r="F171" s="4"/>
-      <c r="G171" s="4"/>
-      <c r="H171" s="7"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="4"/>
     </row>
     <row r="172" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="6" t="s">
+      <c r="A172" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C172" s="4"/>
-      <c r="D172" s="4"/>
-      <c r="E172" s="4"/>
-      <c r="F172" s="4"/>
-      <c r="G172" s="4"/>
-      <c r="H172" s="7"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="4"/>
     </row>
     <row r="173" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="6" t="s">
+      <c r="A173" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C173" s="4"/>
-      <c r="D173" s="4"/>
-      <c r="E173" s="4"/>
-      <c r="F173" s="4"/>
-      <c r="G173" s="4"/>
-      <c r="H173" s="7"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="4"/>
     </row>
     <row r="174" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="6" t="s">
+      <c r="A174" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B174" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C174" s="4"/>
-      <c r="D174" s="4"/>
-      <c r="E174" s="4"/>
-      <c r="F174" s="4"/>
-      <c r="G174" s="4"/>
-      <c r="H174" s="7"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="4"/>
     </row>
     <row r="175" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="6" t="s">
+      <c r="A175" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C175" s="4"/>
-      <c r="D175" s="4"/>
-      <c r="E175" s="4"/>
-      <c r="F175" s="4"/>
-      <c r="G175" s="4"/>
-      <c r="H175" s="7"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="4"/>
     </row>
     <row r="176" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="6" t="s">
+      <c r="A176" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C176" s="4"/>
-      <c r="D176" s="4"/>
-      <c r="E176" s="4"/>
-      <c r="F176" s="4"/>
-      <c r="G176" s="4"/>
-      <c r="H176" s="7"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="4"/>
     </row>
     <row r="177" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="6" t="s">
+      <c r="A177" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C177" s="4"/>
-      <c r="D177" s="4"/>
-      <c r="E177" s="4"/>
-      <c r="F177" s="4"/>
-      <c r="G177" s="4"/>
-      <c r="H177" s="7"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="4"/>
     </row>
     <row r="178" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="s">
+      <c r="A178" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C178" s="4"/>
-      <c r="D178" s="4"/>
-      <c r="E178" s="4"/>
-      <c r="F178" s="4"/>
-      <c r="G178" s="4"/>
-      <c r="H178" s="7"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="4"/>
     </row>
     <row r="179" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="6" t="s">
+      <c r="A179" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
-      <c r="E179" s="4"/>
-      <c r="F179" s="4"/>
-      <c r="G179" s="4"/>
-      <c r="H179" s="7"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+      <c r="H179" s="4"/>
     </row>
     <row r="180" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="6" t="s">
+      <c r="A180" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B180" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C180" s="4"/>
-      <c r="D180" s="4"/>
-      <c r="E180" s="4"/>
-      <c r="F180" s="4"/>
-      <c r="G180" s="4"/>
-      <c r="H180" s="7"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+      <c r="H180" s="4"/>
     </row>
     <row r="181" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="6" t="s">
+      <c r="A181" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B181" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C181" s="4"/>
-      <c r="D181" s="4"/>
-      <c r="E181" s="4"/>
-      <c r="F181" s="4"/>
-      <c r="G181" s="4"/>
-      <c r="H181" s="7"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="4"/>
     </row>
     <row r="182" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="6" t="s">
+      <c r="A182" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B182" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C182" s="4"/>
-      <c r="D182" s="4"/>
-      <c r="E182" s="4"/>
-      <c r="F182" s="4"/>
-      <c r="G182" s="4"/>
-      <c r="H182" s="7"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+      <c r="H182" s="4"/>
     </row>
     <row r="183" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="6" t="s">
+      <c r="A183" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C183" s="4"/>
-      <c r="D183" s="4"/>
-      <c r="E183" s="4"/>
-      <c r="F183" s="4"/>
-      <c r="G183" s="4"/>
-      <c r="H183" s="7"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+      <c r="H183" s="4"/>
     </row>
     <row r="184" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="6" t="s">
+      <c r="A184" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B184" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C184" s="4"/>
-      <c r="D184" s="4"/>
-      <c r="E184" s="4"/>
-      <c r="F184" s="4"/>
-      <c r="G184" s="4"/>
-      <c r="H184" s="7"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+      <c r="H184" s="4"/>
     </row>
     <row r="185" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="6" t="s">
+      <c r="A185" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C185" s="4"/>
-      <c r="D185" s="4"/>
-      <c r="E185" s="4"/>
-      <c r="F185" s="4"/>
-      <c r="G185" s="4"/>
-      <c r="H185" s="7"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+      <c r="H185" s="4"/>
     </row>
     <row r="186" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="6" t="s">
+      <c r="A186" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B186" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C186" s="4"/>
-      <c r="D186" s="4"/>
-      <c r="E186" s="4"/>
-      <c r="F186" s="4"/>
-      <c r="G186" s="4"/>
-      <c r="H186" s="7"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+      <c r="H186" s="4"/>
     </row>
     <row r="187" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="6" t="s">
+      <c r="A187" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B187" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C187" s="4"/>
-      <c r="D187" s="4"/>
-      <c r="E187" s="4"/>
-      <c r="F187" s="4"/>
-      <c r="G187" s="4"/>
-      <c r="H187" s="7"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+      <c r="H187" s="4"/>
     </row>
     <row r="188" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="B188" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C188" s="4"/>
-      <c r="D188" s="4"/>
-      <c r="E188" s="4"/>
-      <c r="F188" s="4"/>
-      <c r="G188" s="4"/>
-      <c r="H188" s="7"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="4"/>
     </row>
     <row r="189" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="6" t="s">
+      <c r="A189" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B189" s="4" t="s">
+      <c r="B189" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C189" s="4"/>
-      <c r="D189" s="4"/>
-      <c r="E189" s="4"/>
-      <c r="F189" s="4"/>
-      <c r="G189" s="4"/>
-      <c r="H189" s="7"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="4"/>
     </row>
     <row r="190" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="B190" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C190" s="4"/>
-      <c r="D190" s="4"/>
-      <c r="E190" s="4"/>
-      <c r="F190" s="4"/>
-      <c r="G190" s="4"/>
-      <c r="H190" s="7"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="4"/>
     </row>
     <row r="191" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B191" s="5"/>
-      <c r="C191" s="5"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="5"/>
-      <c r="F191" s="4"/>
-      <c r="G191" s="4"/>
-      <c r="H191" s="7" t="s">
+      <c r="B191" s="14"/>
+      <c r="C191" s="14"/>
+      <c r="D191" s="14"/>
+      <c r="E191" s="14"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+      <c r="H191" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="6" t="s">
+      <c r="A192" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B192" s="4" t="s">
+      <c r="B192" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C192" s="4"/>
-      <c r="D192" s="4"/>
-      <c r="E192" s="4"/>
-      <c r="F192" s="4"/>
-      <c r="G192" s="4"/>
-      <c r="H192" s="7"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+      <c r="H192" s="4"/>
     </row>
     <row r="193" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="6" t="s">
+      <c r="A193" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="B193" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C193" s="4"/>
-      <c r="D193" s="4"/>
-      <c r="E193" s="4"/>
-      <c r="F193" s="4"/>
-      <c r="G193" s="4"/>
-      <c r="H193" s="7"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+      <c r="H193" s="4"/>
     </row>
     <row r="194" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="6" t="s">
+      <c r="A194" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C194" s="4"/>
-      <c r="D194" s="4"/>
-      <c r="E194" s="4"/>
-      <c r="F194" s="4"/>
-      <c r="G194" s="4"/>
-      <c r="H194" s="7"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+      <c r="H194" s="4"/>
     </row>
     <row r="195" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="6" t="s">
+      <c r="A195" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C195" s="4"/>
-      <c r="D195" s="4"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="7"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
+      <c r="H195" s="4"/>
     </row>
     <row r="196" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="6" t="s">
+      <c r="A196" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C196" s="4"/>
-      <c r="D196" s="4"/>
-      <c r="E196" s="4"/>
-      <c r="F196" s="4"/>
-      <c r="G196" s="4"/>
-      <c r="H196" s="7"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+      <c r="H196" s="4"/>
     </row>
     <row r="197" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="6" t="s">
+      <c r="A197" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C197" s="4"/>
-      <c r="D197" s="4"/>
-      <c r="E197" s="4"/>
-      <c r="F197" s="4"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="7"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+      <c r="H197" s="4"/>
     </row>
     <row r="198" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="6" t="s">
+      <c r="A198" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C198" s="4"/>
-      <c r="D198" s="4"/>
-      <c r="E198" s="4"/>
-      <c r="F198" s="4"/>
-      <c r="G198" s="4"/>
-      <c r="H198" s="7"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+      <c r="H198" s="4"/>
     </row>
     <row r="199" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="6" t="s">
+      <c r="A199" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B199" s="4" t="s">
+      <c r="B199" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C199" s="4"/>
-      <c r="D199" s="4"/>
-      <c r="E199" s="4"/>
-      <c r="F199" s="4"/>
-      <c r="G199" s="4"/>
-      <c r="H199" s="7"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+      <c r="H199" s="4"/>
     </row>
     <row r="200" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="6" t="s">
+      <c r="A200" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C200" s="4"/>
-      <c r="D200" s="4"/>
-      <c r="E200" s="4"/>
-      <c r="F200" s="4"/>
-      <c r="G200" s="4"/>
-      <c r="H200" s="7"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="4"/>
     </row>
     <row r="201" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="6" t="s">
+      <c r="A201" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="4"/>
-      <c r="D201" s="4"/>
-      <c r="E201" s="4"/>
-      <c r="F201" s="4"/>
-      <c r="G201" s="4"/>
-      <c r="H201" s="7"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="4"/>
     </row>
     <row r="202" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="6" t="s">
+      <c r="A202" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C202" s="4"/>
-      <c r="D202" s="4"/>
-      <c r="E202" s="4"/>
-      <c r="F202" s="4"/>
-      <c r="G202" s="4"/>
-      <c r="H202" s="7"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="2"/>
+      <c r="H202" s="4"/>
     </row>
     <row r="203" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="6" t="s">
+      <c r="A203" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="B203" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C203" s="4"/>
-      <c r="D203" s="4"/>
-      <c r="E203" s="4"/>
-      <c r="F203" s="4"/>
-      <c r="G203" s="4"/>
-      <c r="H203" s="7"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+      <c r="H203" s="4"/>
     </row>
     <row r="204" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="6" t="s">
+      <c r="A204" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B204" s="4" t="s">
+      <c r="B204" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C204" s="4"/>
-      <c r="D204" s="4"/>
-      <c r="E204" s="4"/>
-      <c r="F204" s="4"/>
-      <c r="G204" s="4"/>
-      <c r="H204" s="7"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+      <c r="H204" s="4"/>
     </row>
     <row r="205" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="6" t="s">
+      <c r="A205" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B205" s="4" t="s">
+      <c r="B205" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C205" s="4"/>
-      <c r="D205" s="4"/>
-      <c r="E205" s="4"/>
-      <c r="F205" s="4"/>
-      <c r="G205" s="4"/>
-      <c r="H205" s="7"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+      <c r="H205" s="4"/>
     </row>
     <row r="206" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="6" t="s">
+      <c r="A206" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C206" s="4"/>
-      <c r="D206" s="4"/>
-      <c r="E206" s="4"/>
-      <c r="F206" s="4"/>
-      <c r="G206" s="4"/>
-      <c r="H206" s="7"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+      <c r="H206" s="4"/>
     </row>
     <row r="207" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="6" t="s">
+      <c r="A207" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C207" s="4"/>
-      <c r="D207" s="4"/>
-      <c r="E207" s="4"/>
-      <c r="F207" s="4"/>
-      <c r="G207" s="4"/>
-      <c r="H207" s="7"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+      <c r="H207" s="4"/>
     </row>
     <row r="208" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="6" t="s">
+      <c r="A208" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B208" s="4" t="s">
+      <c r="B208" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C208" s="4"/>
-      <c r="D208" s="4"/>
-      <c r="E208" s="4"/>
-      <c r="F208" s="4"/>
-      <c r="G208" s="4"/>
-      <c r="H208" s="7"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+      <c r="F208" s="2"/>
+      <c r="G208" s="2"/>
+      <c r="H208" s="4"/>
     </row>
     <row r="209" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="6" t="s">
+      <c r="A209" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C209" s="4"/>
-      <c r="D209" s="4"/>
-      <c r="E209" s="4"/>
-      <c r="F209" s="4"/>
-      <c r="G209" s="4"/>
-      <c r="H209" s="7"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
+      <c r="E209" s="2"/>
+      <c r="F209" s="2"/>
+      <c r="G209" s="2"/>
+      <c r="H209" s="4"/>
     </row>
     <row r="210" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="6" t="s">
+      <c r="A210" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C210" s="4"/>
-      <c r="D210" s="4"/>
-      <c r="E210" s="4"/>
-      <c r="F210" s="4"/>
-      <c r="G210" s="4"/>
-      <c r="H210" s="7"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+      <c r="E210" s="2"/>
+      <c r="F210" s="2"/>
+      <c r="G210" s="2"/>
+      <c r="H210" s="4"/>
     </row>
     <row r="211" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="6" t="s">
+      <c r="A211" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C211" s="4"/>
-      <c r="D211" s="4"/>
-      <c r="E211" s="4"/>
-      <c r="F211" s="4"/>
-      <c r="G211" s="4"/>
-      <c r="H211" s="7"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+      <c r="E211" s="2"/>
+      <c r="F211" s="2"/>
+      <c r="G211" s="2"/>
+      <c r="H211" s="4"/>
     </row>
     <row r="212" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="6" t="s">
+      <c r="A212" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C212" s="4"/>
-      <c r="D212" s="4"/>
-      <c r="E212" s="4"/>
-      <c r="F212" s="4"/>
-      <c r="G212" s="4"/>
-      <c r="H212" s="7"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
+      <c r="G212" s="2"/>
+      <c r="H212" s="4"/>
     </row>
     <row r="213" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="6" t="s">
+      <c r="A213" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="B213" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C213" s="4"/>
-      <c r="D213" s="4"/>
-      <c r="E213" s="4"/>
-      <c r="F213" s="4"/>
-      <c r="G213" s="4"/>
-      <c r="H213" s="7"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="2"/>
+      <c r="H213" s="4"/>
     </row>
     <row r="214" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B214" s="4" t="s">
+      <c r="B214" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C214" s="4"/>
-      <c r="D214" s="4"/>
-      <c r="E214" s="4"/>
-      <c r="F214" s="4"/>
-      <c r="G214" s="4"/>
-      <c r="H214" s="7"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2"/>
+      <c r="F214" s="2"/>
+      <c r="G214" s="2"/>
+      <c r="H214" s="4"/>
     </row>
     <row r="215" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="6" t="s">
+      <c r="A215" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C215" s="4"/>
-      <c r="D215" s="4"/>
-      <c r="E215" s="4"/>
-      <c r="F215" s="4"/>
-      <c r="G215" s="4"/>
-      <c r="H215" s="7"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="4"/>
     </row>
     <row r="216" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="6" t="s">
+      <c r="A216" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C216" s="4"/>
-      <c r="D216" s="4"/>
-      <c r="E216" s="4"/>
-      <c r="F216" s="4"/>
-      <c r="G216" s="4"/>
-      <c r="H216" s="7"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2"/>
+      <c r="H216" s="4"/>
     </row>
     <row r="217" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="6" t="s">
+      <c r="A217" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C217" s="4"/>
-      <c r="D217" s="4"/>
-      <c r="E217" s="4"/>
-      <c r="F217" s="4"/>
-      <c r="G217" s="4"/>
-      <c r="H217" s="7"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="4"/>
     </row>
     <row r="218" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="6" t="s">
+      <c r="A218" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B218" s="4" t="s">
+      <c r="B218" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C218" s="4"/>
-      <c r="D218" s="4"/>
-      <c r="E218" s="4"/>
-      <c r="F218" s="4"/>
-      <c r="G218" s="4"/>
-      <c r="H218" s="7"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="4"/>
     </row>
     <row r="219" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="8" t="s">
+      <c r="A219" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B219" s="5"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
-      <c r="E219" s="5"/>
-      <c r="F219" s="4"/>
-      <c r="G219" s="4"/>
-      <c r="H219" s="7" t="s">
+      <c r="B219" s="14"/>
+      <c r="C219" s="14"/>
+      <c r="D219" s="14"/>
+      <c r="E219" s="14"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="6" t="s">
+      <c r="A220" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C220" s="4"/>
-      <c r="D220" s="4"/>
-      <c r="E220" s="4"/>
-      <c r="F220" s="4"/>
-      <c r="G220" s="4"/>
-      <c r="H220" s="7"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="4"/>
     </row>
     <row r="221" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="6" t="s">
+      <c r="A221" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B221" s="4" t="s">
+      <c r="B221" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C221" s="4"/>
-      <c r="D221" s="4"/>
-      <c r="E221" s="4"/>
-      <c r="F221" s="4"/>
-      <c r="G221" s="4"/>
-      <c r="H221" s="7"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="4"/>
     </row>
     <row r="222" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="6" t="s">
+      <c r="A222" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B222" s="4" t="s">
+      <c r="B222" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C222" s="4"/>
-      <c r="D222" s="4"/>
-      <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
-      <c r="G222" s="4"/>
-      <c r="H222" s="7"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="4"/>
     </row>
     <row r="223" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="6" t="s">
+      <c r="A223" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B223" s="4" t="s">
+      <c r="B223" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C223" s="4"/>
-      <c r="D223" s="4"/>
-      <c r="E223" s="4"/>
-      <c r="F223" s="4"/>
-      <c r="G223" s="4"/>
-      <c r="H223" s="7"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="4"/>
     </row>
     <row r="224" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="6" t="s">
+      <c r="A224" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B224" s="4" t="s">
+      <c r="B224" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C224" s="4"/>
-      <c r="D224" s="4"/>
-      <c r="E224" s="4"/>
-      <c r="F224" s="4"/>
-      <c r="G224" s="4"/>
-      <c r="H224" s="7"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="4"/>
     </row>
     <row r="225" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="6" t="s">
+      <c r="A225" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B225" s="4" t="s">
+      <c r="B225" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C225" s="4"/>
-      <c r="D225" s="4"/>
-      <c r="E225" s="4"/>
-      <c r="F225" s="4"/>
-      <c r="G225" s="4"/>
-      <c r="H225" s="7"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
+      <c r="E225" s="2"/>
+      <c r="F225" s="2"/>
+      <c r="G225" s="2"/>
+      <c r="H225" s="4"/>
     </row>
     <row r="226" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="6" t="s">
+      <c r="A226" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B226" s="4" t="s">
+      <c r="B226" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C226" s="4"/>
-      <c r="D226" s="4"/>
-      <c r="E226" s="4"/>
-      <c r="F226" s="4"/>
-      <c r="G226" s="4"/>
-      <c r="H226" s="7"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+      <c r="F226" s="2"/>
+      <c r="G226" s="2"/>
+      <c r="H226" s="4"/>
     </row>
     <row r="227" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="6" t="s">
+      <c r="A227" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B227" s="4" t="s">
+      <c r="B227" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C227" s="4"/>
-      <c r="D227" s="4"/>
-      <c r="E227" s="4"/>
-      <c r="F227" s="4"/>
-      <c r="G227" s="4"/>
-      <c r="H227" s="7"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+      <c r="F227" s="2"/>
+      <c r="G227" s="2"/>
+      <c r="H227" s="4"/>
     </row>
     <row r="228" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="6" t="s">
+      <c r="A228" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B228" s="4" t="s">
+      <c r="B228" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C228" s="4"/>
-      <c r="D228" s="4"/>
-      <c r="E228" s="4"/>
-      <c r="F228" s="4"/>
-      <c r="G228" s="4"/>
-      <c r="H228" s="7"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
+      <c r="E228" s="2"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="2"/>
+      <c r="H228" s="4"/>
     </row>
     <row r="229" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="6" t="s">
+      <c r="A229" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B229" s="4" t="s">
+      <c r="B229" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C229" s="4"/>
-      <c r="D229" s="4"/>
-      <c r="E229" s="4"/>
-      <c r="F229" s="4"/>
-      <c r="G229" s="4"/>
-      <c r="H229" s="7"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
+      <c r="E229" s="2"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="4"/>
     </row>
     <row r="230" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="6" t="s">
+      <c r="A230" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B230" s="4" t="s">
+      <c r="B230" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C230" s="4"/>
-      <c r="D230" s="4"/>
-      <c r="E230" s="4"/>
-      <c r="F230" s="4"/>
-      <c r="G230" s="4"/>
-      <c r="H230" s="7"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2"/>
+      <c r="H230" s="4"/>
     </row>
     <row r="231" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="6" t="s">
+      <c r="A231" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B231" s="4" t="s">
+      <c r="B231" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C231" s="4"/>
-      <c r="D231" s="4"/>
-      <c r="E231" s="4"/>
-      <c r="F231" s="4"/>
-      <c r="G231" s="4"/>
-      <c r="H231" s="7"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+      <c r="H231" s="4"/>
     </row>
     <row r="232" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="6" t="s">
+      <c r="A232" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B232" s="4" t="s">
+      <c r="B232" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C232" s="4"/>
-      <c r="D232" s="4"/>
-      <c r="E232" s="4"/>
-      <c r="F232" s="4"/>
-      <c r="G232" s="4"/>
-      <c r="H232" s="7"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+      <c r="H232" s="4"/>
     </row>
     <row r="233" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="6" t="s">
+      <c r="A233" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B233" s="4" t="s">
+      <c r="B233" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C233" s="4"/>
-      <c r="D233" s="4"/>
-      <c r="E233" s="4"/>
-      <c r="F233" s="4"/>
-      <c r="G233" s="4"/>
-      <c r="H233" s="7"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="2"/>
+      <c r="H233" s="4"/>
     </row>
     <row r="234" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="6" t="s">
+      <c r="A234" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B234" s="4" t="s">
+      <c r="B234" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C234" s="4"/>
-      <c r="D234" s="4"/>
-      <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="7"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+      <c r="H234" s="4"/>
     </row>
     <row r="235" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="6" t="s">
+      <c r="A235" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B235" s="4" t="s">
+      <c r="B235" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C235" s="4"/>
-      <c r="D235" s="4"/>
-      <c r="E235" s="4"/>
-      <c r="F235" s="4"/>
-      <c r="G235" s="4"/>
-      <c r="H235" s="7"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+      <c r="H235" s="4"/>
     </row>
     <row r="236" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="6" t="s">
+      <c r="A236" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B236" s="4" t="s">
+      <c r="B236" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C236" s="4"/>
-      <c r="D236" s="4"/>
-      <c r="E236" s="4"/>
-      <c r="F236" s="4"/>
-      <c r="G236" s="4"/>
-      <c r="H236" s="7"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2"/>
+      <c r="H236" s="4"/>
     </row>
     <row r="237" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="6" t="s">
+      <c r="A237" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B237" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C237" s="4"/>
-      <c r="D237" s="4"/>
-      <c r="E237" s="4"/>
-      <c r="F237" s="4"/>
-      <c r="G237" s="4"/>
-      <c r="H237" s="7"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="2"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="2"/>
+      <c r="H237" s="4"/>
     </row>
     <row r="238" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="6" t="s">
+      <c r="A238" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C238" s="4"/>
-      <c r="D238" s="4"/>
-      <c r="E238" s="4"/>
-      <c r="F238" s="4"/>
-      <c r="G238" s="4"/>
-      <c r="H238" s="7"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="2"/>
+      <c r="H238" s="4"/>
     </row>
     <row r="239" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="6" t="s">
+      <c r="A239" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B239" s="4" t="s">
+      <c r="B239" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C239" s="4"/>
-      <c r="D239" s="4"/>
-      <c r="E239" s="4"/>
-      <c r="F239" s="4"/>
-      <c r="G239" s="4"/>
-      <c r="H239" s="7"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="4"/>
     </row>
     <row r="240" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="8" t="s">
+      <c r="A240" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="B240" s="5"/>
-      <c r="C240" s="5"/>
-      <c r="D240" s="5"/>
-      <c r="E240" s="5"/>
-      <c r="F240" s="4"/>
-      <c r="G240" s="4"/>
-      <c r="H240" s="7" t="s">
+      <c r="B240" s="14"/>
+      <c r="C240" s="14"/>
+      <c r="D240" s="14"/>
+      <c r="E240" s="14"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="2"/>
+      <c r="H240" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="6" t="s">
+      <c r="A241" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="B241" s="4" t="s">
+      <c r="B241" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C241" s="4"/>
-      <c r="D241" s="4"/>
-      <c r="E241" s="4"/>
-      <c r="F241" s="4"/>
-      <c r="G241" s="4"/>
-      <c r="H241" s="7"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+      <c r="F241" s="2"/>
+      <c r="G241" s="2"/>
+      <c r="H241" s="4"/>
     </row>
     <row r="242" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="6" t="s">
+      <c r="A242" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B242" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="C242" s="4"/>
-      <c r="D242" s="4"/>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4"/>
-      <c r="G242" s="4"/>
-      <c r="H242" s="7"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="2"/>
+      <c r="H242" s="4"/>
     </row>
     <row r="243" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="6" t="s">
+      <c r="A243" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="B243" s="4" t="s">
+      <c r="B243" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C243" s="4"/>
-      <c r="D243" s="4"/>
-      <c r="E243" s="4"/>
-      <c r="F243" s="4"/>
-      <c r="G243" s="4"/>
-      <c r="H243" s="7"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="2"/>
+      <c r="H243" s="4"/>
     </row>
     <row r="244" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="6" t="s">
+      <c r="A244" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B244" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C244" s="4"/>
-      <c r="D244" s="4"/>
-      <c r="E244" s="4"/>
-      <c r="F244" s="4"/>
-      <c r="G244" s="4"/>
-      <c r="H244" s="7"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="2"/>
+      <c r="H244" s="4"/>
     </row>
     <row r="245" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="6" t="s">
+      <c r="A245" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="B245" s="4" t="s">
+      <c r="B245" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C245" s="4"/>
-      <c r="D245" s="4"/>
-      <c r="E245" s="4"/>
-      <c r="F245" s="4"/>
-      <c r="G245" s="4"/>
-      <c r="H245" s="7"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="2"/>
+      <c r="H245" s="4"/>
     </row>
     <row r="246" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="6" t="s">
+      <c r="A246" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B246" s="4" t="s">
+      <c r="B246" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
-      <c r="E246" s="4"/>
-      <c r="F246" s="4"/>
-      <c r="G246" s="4"/>
-      <c r="H246" s="7"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="2"/>
+      <c r="H246" s="4"/>
     </row>
     <row r="247" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="6" t="s">
+      <c r="A247" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="B247" s="4" t="s">
+      <c r="B247" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C247" s="4"/>
-      <c r="D247" s="4"/>
-      <c r="E247" s="4"/>
-      <c r="F247" s="4"/>
-      <c r="G247" s="4"/>
-      <c r="H247" s="7"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="2"/>
+      <c r="H247" s="4"/>
     </row>
     <row r="248" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="6" t="s">
+      <c r="A248" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="B248" s="4" t="s">
+      <c r="B248" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C248" s="4"/>
-      <c r="D248" s="4"/>
-      <c r="E248" s="4"/>
-      <c r="F248" s="4"/>
-      <c r="G248" s="4"/>
-      <c r="H248" s="7"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+      <c r="H248" s="4"/>
     </row>
     <row r="249" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="6" t="s">
+      <c r="A249" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="B249" s="4" t="s">
+      <c r="B249" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="C249" s="4"/>
-      <c r="D249" s="4"/>
-      <c r="E249" s="4"/>
-      <c r="F249" s="4"/>
-      <c r="G249" s="4"/>
-      <c r="H249" s="7"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
+      <c r="H249" s="4"/>
     </row>
     <row r="250" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="6" t="s">
+      <c r="A250" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="C250" s="4"/>
-      <c r="D250" s="4"/>
-      <c r="E250" s="4"/>
-      <c r="F250" s="4"/>
-      <c r="G250" s="4"/>
-      <c r="H250" s="7"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="2"/>
+      <c r="H250" s="4"/>
     </row>
     <row r="251" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="6" t="s">
+      <c r="A251" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B251" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C251" s="4"/>
-      <c r="D251" s="4"/>
-      <c r="E251" s="4"/>
-      <c r="F251" s="4"/>
-      <c r="G251" s="4"/>
-      <c r="H251" s="7"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="2"/>
+      <c r="H251" s="4"/>
     </row>
     <row r="252" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="6" t="s">
+      <c r="A252" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="B252" s="4" t="s">
+      <c r="B252" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C252" s="4"/>
-      <c r="D252" s="4"/>
-      <c r="E252" s="4"/>
-      <c r="F252" s="4"/>
-      <c r="G252" s="4"/>
-      <c r="H252" s="7"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="2"/>
+      <c r="H252" s="4"/>
     </row>
     <row r="253" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="6" t="s">
+      <c r="A253" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="B253" s="4" t="s">
+      <c r="B253" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="C253" s="4"/>
-      <c r="D253" s="4"/>
-      <c r="E253" s="4"/>
-      <c r="F253" s="4"/>
-      <c r="G253" s="4"/>
-      <c r="H253" s="7"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="2"/>
+      <c r="H253" s="4"/>
     </row>
     <row r="254" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="6" t="s">
+      <c r="A254" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="B254" s="4" t="s">
+      <c r="B254" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="C254" s="4"/>
-      <c r="D254" s="4"/>
-      <c r="E254" s="4"/>
-      <c r="F254" s="4"/>
-      <c r="G254" s="4"/>
-      <c r="H254" s="7"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="2"/>
+      <c r="H254" s="4"/>
     </row>
     <row r="255" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="6" t="s">
+      <c r="A255" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="B255" s="4" t="s">
+      <c r="B255" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="C255" s="4"/>
-      <c r="D255" s="4"/>
-      <c r="E255" s="4"/>
-      <c r="F255" s="4"/>
-      <c r="G255" s="4"/>
-      <c r="H255" s="7"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="2"/>
+      <c r="F255" s="2"/>
+      <c r="G255" s="2"/>
+      <c r="H255" s="4"/>
     </row>
     <row r="256" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="6" t="s">
+      <c r="A256" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B256" s="4" t="s">
+      <c r="B256" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C256" s="4"/>
-      <c r="D256" s="4"/>
-      <c r="E256" s="4"/>
-      <c r="F256" s="4"/>
-      <c r="G256" s="4"/>
-      <c r="H256" s="7"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="2"/>
+      <c r="H256" s="4"/>
     </row>
     <row r="257" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="6" t="s">
+      <c r="A257" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="B257" s="4" t="s">
+      <c r="B257" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="C257" s="4"/>
-      <c r="D257" s="4"/>
-      <c r="E257" s="4"/>
-      <c r="F257" s="4"/>
-      <c r="G257" s="4"/>
-      <c r="H257" s="7"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
+      <c r="E257" s="2"/>
+      <c r="F257" s="2"/>
+      <c r="G257" s="2"/>
+      <c r="H257" s="4"/>
     </row>
     <row r="258" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="6" t="s">
+      <c r="A258" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B258" s="4" t="s">
+      <c r="B258" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-      <c r="E258" s="4"/>
-      <c r="F258" s="4"/>
-      <c r="G258" s="4"/>
-      <c r="H258" s="7"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="2"/>
+      <c r="H258" s="4"/>
     </row>
     <row r="259" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="6" t="s">
+      <c r="A259" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B259" s="4" t="s">
+      <c r="B259" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="C259" s="4"/>
-      <c r="D259" s="4"/>
-      <c r="E259" s="4"/>
-      <c r="F259" s="4"/>
-      <c r="G259" s="4"/>
-      <c r="H259" s="7"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
+      <c r="E259" s="2"/>
+      <c r="F259" s="2"/>
+      <c r="G259" s="2"/>
+      <c r="H259" s="4"/>
     </row>
     <row r="260" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="6" t="s">
+      <c r="A260" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="B260" s="4" t="s">
+      <c r="B260" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C260" s="4"/>
-      <c r="D260" s="4"/>
-      <c r="E260" s="4"/>
-      <c r="F260" s="4"/>
-      <c r="G260" s="4"/>
-      <c r="H260" s="7"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="2"/>
+      <c r="H260" s="4"/>
     </row>
     <row r="261" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="8" t="s">
+      <c r="A261" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="B261" s="5"/>
-      <c r="C261" s="5"/>
-      <c r="D261" s="5"/>
-      <c r="E261" s="5"/>
-      <c r="F261" s="4"/>
-      <c r="G261" s="4"/>
-      <c r="H261" s="7" t="s">
+      <c r="B261" s="14"/>
+      <c r="C261" s="14"/>
+      <c r="D261" s="14"/>
+      <c r="E261" s="14"/>
+      <c r="F261" s="2"/>
+      <c r="G261" s="2"/>
+      <c r="H261" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="6" t="s">
+      <c r="A262" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B262" s="4" t="s">
+      <c r="B262" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C262" s="4"/>
-      <c r="D262" s="4"/>
-      <c r="E262" s="4"/>
-      <c r="F262" s="4"/>
-      <c r="G262" s="4"/>
-      <c r="H262" s="7"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="2"/>
+      <c r="H262" s="4"/>
     </row>
     <row r="263" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="6" t="s">
+      <c r="A263" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B263" s="4" t="s">
+      <c r="B263" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C263" s="4"/>
-      <c r="D263" s="4"/>
-      <c r="E263" s="4"/>
-      <c r="F263" s="4"/>
-      <c r="G263" s="4"/>
-      <c r="H263" s="7"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
+      <c r="E263" s="2"/>
+      <c r="F263" s="2"/>
+      <c r="G263" s="2"/>
+      <c r="H263" s="4"/>
     </row>
     <row r="264" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="6" t="s">
+      <c r="A264" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B264" s="4" t="s">
+      <c r="B264" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C264" s="4"/>
-      <c r="D264" s="4"/>
-      <c r="E264" s="4"/>
-      <c r="F264" s="4"/>
-      <c r="G264" s="4"/>
-      <c r="H264" s="7"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+      <c r="E264" s="2"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="2"/>
+      <c r="H264" s="4"/>
     </row>
     <row r="265" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="6" t="s">
+      <c r="A265" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B265" s="4" t="s">
+      <c r="B265" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C265" s="4"/>
-      <c r="D265" s="4"/>
-      <c r="E265" s="4"/>
-      <c r="F265" s="4"/>
-      <c r="G265" s="4"/>
-      <c r="H265" s="7"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
+      <c r="E265" s="2"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="2"/>
+      <c r="H265" s="4"/>
     </row>
     <row r="266" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="6" t="s">
+      <c r="A266" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B266" s="4" t="s">
+      <c r="B266" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C266" s="4"/>
-      <c r="D266" s="4"/>
-      <c r="E266" s="4"/>
-      <c r="F266" s="4"/>
-      <c r="G266" s="4"/>
-      <c r="H266" s="7"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+      <c r="E266" s="2"/>
+      <c r="F266" s="2"/>
+      <c r="G266" s="2"/>
+      <c r="H266" s="4"/>
     </row>
     <row r="267" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="6" t="s">
+      <c r="A267" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B267" s="4" t="s">
+      <c r="B267" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C267" s="4"/>
-      <c r="D267" s="4"/>
-      <c r="E267" s="4"/>
-      <c r="F267" s="4"/>
-      <c r="G267" s="4"/>
-      <c r="H267" s="7"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
+      <c r="E267" s="2"/>
+      <c r="F267" s="2"/>
+      <c r="G267" s="2"/>
+      <c r="H267" s="4"/>
     </row>
     <row r="268" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="6" t="s">
+      <c r="A268" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B268" s="4" t="s">
+      <c r="B268" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C268" s="4"/>
-      <c r="D268" s="4"/>
-      <c r="E268" s="4"/>
-      <c r="F268" s="4"/>
-      <c r="G268" s="4"/>
-      <c r="H268" s="7"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="2"/>
+      <c r="H268" s="4"/>
     </row>
     <row r="269" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="6" t="s">
+      <c r="A269" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B269" s="4" t="s">
+      <c r="B269" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C269" s="4"/>
-      <c r="D269" s="4"/>
-      <c r="E269" s="4"/>
-      <c r="F269" s="4"/>
-      <c r="G269" s="4"/>
-      <c r="H269" s="7"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+      <c r="E269" s="2"/>
+      <c r="F269" s="2"/>
+      <c r="G269" s="2"/>
+      <c r="H269" s="4"/>
     </row>
     <row r="270" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="6" t="s">
+      <c r="A270" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B270" s="4" t="s">
+      <c r="B270" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C270" s="4"/>
-      <c r="D270" s="4"/>
-      <c r="E270" s="4"/>
-      <c r="F270" s="4"/>
-      <c r="G270" s="4"/>
-      <c r="H270" s="7"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
+      <c r="E270" s="2"/>
+      <c r="F270" s="2"/>
+      <c r="G270" s="2"/>
+      <c r="H270" s="4"/>
     </row>
     <row r="271" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="6" t="s">
+      <c r="A271" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B271" s="4" t="s">
+      <c r="B271" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C271" s="4"/>
-      <c r="D271" s="4"/>
-      <c r="E271" s="4"/>
-      <c r="F271" s="4"/>
-      <c r="G271" s="4"/>
-      <c r="H271" s="7"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
+      <c r="E271" s="2"/>
+      <c r="F271" s="2"/>
+      <c r="G271" s="2"/>
+      <c r="H271" s="4"/>
     </row>
     <row r="272" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="6" t="s">
+      <c r="A272" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B272" s="4" t="s">
+      <c r="B272" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C272" s="4"/>
-      <c r="D272" s="4"/>
-      <c r="E272" s="4"/>
-      <c r="F272" s="4"/>
-      <c r="G272" s="4"/>
-      <c r="H272" s="7"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
+      <c r="E272" s="2"/>
+      <c r="F272" s="2"/>
+      <c r="G272" s="2"/>
+      <c r="H272" s="4"/>
     </row>
     <row r="273" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="6" t="s">
+      <c r="A273" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B273" s="4" t="s">
+      <c r="B273" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C273" s="4"/>
-      <c r="D273" s="4"/>
-      <c r="E273" s="4"/>
-      <c r="F273" s="4"/>
-      <c r="G273" s="4"/>
-      <c r="H273" s="7"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
+      <c r="E273" s="2"/>
+      <c r="F273" s="2"/>
+      <c r="G273" s="2"/>
+      <c r="H273" s="4"/>
     </row>
     <row r="274" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="6" t="s">
+      <c r="A274" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B274" s="4" t="s">
+      <c r="B274" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C274" s="4"/>
-      <c r="D274" s="4"/>
-      <c r="E274" s="4"/>
-      <c r="F274" s="4"/>
-      <c r="G274" s="4"/>
-      <c r="H274" s="7"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
+      <c r="E274" s="2"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="2"/>
+      <c r="H274" s="4"/>
     </row>
     <row r="275" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="6" t="s">
+      <c r="A275" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B275" s="4" t="s">
+      <c r="B275" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C275" s="4"/>
-      <c r="D275" s="4"/>
-      <c r="E275" s="4"/>
-      <c r="F275" s="4"/>
-      <c r="G275" s="4"/>
-      <c r="H275" s="7"/>
+      <c r="C275" s="2"/>
+      <c r="D275" s="2"/>
+      <c r="E275" s="2"/>
+      <c r="F275" s="2"/>
+      <c r="G275" s="2"/>
+      <c r="H275" s="4"/>
     </row>
     <row r="276" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="8" t="s">
+      <c r="A276" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B276" s="5"/>
-      <c r="C276" s="5"/>
-      <c r="D276" s="5"/>
-      <c r="E276" s="5"/>
-      <c r="F276" s="4"/>
-      <c r="G276" s="4"/>
-      <c r="H276" s="7" t="s">
+      <c r="B276" s="14"/>
+      <c r="C276" s="14"/>
+      <c r="D276" s="14"/>
+      <c r="E276" s="14"/>
+      <c r="F276" s="2"/>
+      <c r="G276" s="2"/>
+      <c r="H276" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="6" t="s">
+      <c r="A277" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="B277" s="4" t="s">
+      <c r="B277" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C277" s="4"/>
-      <c r="D277" s="4"/>
-      <c r="E277" s="4"/>
-      <c r="F277" s="4"/>
-      <c r="G277" s="4"/>
-      <c r="H277" s="7"/>
+      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
+      <c r="E277" s="2"/>
+      <c r="F277" s="2"/>
+      <c r="G277" s="2"/>
+      <c r="H277" s="4"/>
     </row>
     <row r="278" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="6" t="s">
+      <c r="A278" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B278" s="4" t="s">
+      <c r="B278" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C278" s="4"/>
-      <c r="D278" s="4"/>
-      <c r="E278" s="4"/>
-      <c r="F278" s="4"/>
-      <c r="G278" s="4"/>
-      <c r="H278" s="7"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
+      <c r="E278" s="2"/>
+      <c r="F278" s="2"/>
+      <c r="G278" s="2"/>
+      <c r="H278" s="4"/>
     </row>
     <row r="279" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="6" t="s">
+      <c r="A279" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B279" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C279" s="4"/>
-      <c r="D279" s="4"/>
-      <c r="E279" s="4"/>
-      <c r="F279" s="4"/>
-      <c r="G279" s="4"/>
-      <c r="H279" s="7"/>
+      <c r="C279" s="2"/>
+      <c r="D279" s="2"/>
+      <c r="E279" s="2"/>
+      <c r="F279" s="2"/>
+      <c r="G279" s="2"/>
+      <c r="H279" s="4"/>
     </row>
     <row r="280" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="6" t="s">
+      <c r="A280" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="B280" s="4" t="s">
+      <c r="B280" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C280" s="4"/>
-      <c r="D280" s="4"/>
-      <c r="E280" s="4"/>
-      <c r="F280" s="4"/>
-      <c r="G280" s="4"/>
-      <c r="H280" s="7"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
+      <c r="E280" s="2"/>
+      <c r="F280" s="2"/>
+      <c r="G280" s="2"/>
+      <c r="H280" s="4"/>
     </row>
     <row r="281" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="6" t="s">
+      <c r="A281" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B281" s="4" t="s">
+      <c r="B281" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C281" s="4"/>
-      <c r="D281" s="4"/>
-      <c r="E281" s="4"/>
-      <c r="F281" s="4"/>
-      <c r="G281" s="4"/>
-      <c r="H281" s="7"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
+      <c r="E281" s="2"/>
+      <c r="F281" s="2"/>
+      <c r="G281" s="2"/>
+      <c r="H281" s="4"/>
     </row>
     <row r="282" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="6" t="s">
+      <c r="A282" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="B282" s="4" t="s">
+      <c r="B282" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C282" s="4"/>
-      <c r="D282" s="4"/>
-      <c r="E282" s="4"/>
-      <c r="F282" s="4"/>
-      <c r="G282" s="4"/>
-      <c r="H282" s="7"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
+      <c r="E282" s="2"/>
+      <c r="F282" s="2"/>
+      <c r="G282" s="2"/>
+      <c r="H282" s="4"/>
     </row>
     <row r="283" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="6" t="s">
+      <c r="A283" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B283" s="4" t="s">
+      <c r="B283" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C283" s="4"/>
-      <c r="D283" s="4"/>
-      <c r="E283" s="4"/>
-      <c r="F283" s="4"/>
-      <c r="G283" s="4"/>
-      <c r="H283" s="7"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
+      <c r="E283" s="2"/>
+      <c r="F283" s="2"/>
+      <c r="G283" s="2"/>
+      <c r="H283" s="4"/>
     </row>
     <row r="284" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="6" t="s">
+      <c r="A284" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="B284" s="4" t="s">
+      <c r="B284" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C284" s="4"/>
-      <c r="D284" s="4"/>
-      <c r="E284" s="4"/>
-      <c r="F284" s="4"/>
-      <c r="G284" s="4"/>
-      <c r="H284" s="7"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
+      <c r="E284" s="2"/>
+      <c r="F284" s="2"/>
+      <c r="G284" s="2"/>
+      <c r="H284" s="4"/>
     </row>
     <row r="285" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="6" t="s">
+      <c r="A285" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="B285" s="4" t="s">
+      <c r="B285" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C285" s="4"/>
-      <c r="D285" s="4"/>
-      <c r="E285" s="4"/>
-      <c r="F285" s="4"/>
-      <c r="G285" s="4"/>
-      <c r="H285" s="7"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
+      <c r="E285" s="2"/>
+      <c r="F285" s="2"/>
+      <c r="G285" s="2"/>
+      <c r="H285" s="4"/>
     </row>
     <row r="286" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="6" t="s">
+      <c r="A286" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="B286" s="4" t="s">
+      <c r="B286" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="C286" s="4"/>
-      <c r="D286" s="4"/>
-      <c r="E286" s="4"/>
-      <c r="F286" s="4"/>
-      <c r="G286" s="4"/>
-      <c r="H286" s="7"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
+      <c r="E286" s="2"/>
+      <c r="F286" s="2"/>
+      <c r="G286" s="2"/>
+      <c r="H286" s="4"/>
     </row>
     <row r="287" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="6" t="s">
+      <c r="A287" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B287" s="4" t="s">
+      <c r="B287" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="C287" s="4"/>
-      <c r="D287" s="4"/>
-      <c r="E287" s="4"/>
-      <c r="F287" s="4"/>
-      <c r="G287" s="4"/>
-      <c r="H287" s="7"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
+      <c r="E287" s="2"/>
+      <c r="F287" s="2"/>
+      <c r="G287" s="2"/>
+      <c r="H287" s="4"/>
     </row>
     <row r="288" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="6" t="s">
+      <c r="A288" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B288" s="4" t="s">
+      <c r="B288" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C288" s="4"/>
-      <c r="D288" s="4"/>
-      <c r="E288" s="4"/>
-      <c r="F288" s="4"/>
-      <c r="G288" s="4"/>
-      <c r="H288" s="7"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
+      <c r="E288" s="2"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="2"/>
+      <c r="H288" s="4"/>
     </row>
     <row r="289" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="6" t="s">
+      <c r="A289" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B289" s="4" t="s">
+      <c r="B289" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="C289" s="4"/>
-      <c r="D289" s="4"/>
-      <c r="E289" s="4"/>
-      <c r="F289" s="4"/>
-      <c r="G289" s="4"/>
-      <c r="H289" s="7"/>
+      <c r="C289" s="2"/>
+      <c r="D289" s="2"/>
+      <c r="E289" s="2"/>
+      <c r="F289" s="2"/>
+      <c r="G289" s="2"/>
+      <c r="H289" s="4"/>
     </row>
     <row r="290" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="6" t="s">
+      <c r="A290" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B290" s="4" t="s">
+      <c r="B290" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C290" s="4"/>
-      <c r="D290" s="4"/>
-      <c r="E290" s="4"/>
-      <c r="F290" s="4"/>
-      <c r="G290" s="4"/>
-      <c r="H290" s="7"/>
+      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
+      <c r="E290" s="2"/>
+      <c r="F290" s="2"/>
+      <c r="G290" s="2"/>
+      <c r="H290" s="4"/>
     </row>
     <row r="291" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="6" t="s">
+      <c r="A291" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="B291" s="4" t="s">
+      <c r="B291" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="C291" s="4"/>
-      <c r="D291" s="4"/>
-      <c r="E291" s="4"/>
-      <c r="F291" s="4"/>
-      <c r="G291" s="4"/>
-      <c r="H291" s="7"/>
+      <c r="C291" s="2"/>
+      <c r="D291" s="2"/>
+      <c r="E291" s="2"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+      <c r="H291" s="4"/>
     </row>
     <row r="292" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="6" t="s">
+      <c r="A292" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B292" s="4" t="s">
+      <c r="B292" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C292" s="4"/>
-      <c r="D292" s="4"/>
-      <c r="E292" s="4"/>
-      <c r="F292" s="4"/>
-      <c r="G292" s="4"/>
-      <c r="H292" s="7"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
+      <c r="E292" s="2"/>
+      <c r="F292" s="2"/>
+      <c r="G292" s="2"/>
+      <c r="H292" s="4"/>
     </row>
     <row r="293" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="6" t="s">
+      <c r="A293" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="B293" s="4" t="s">
+      <c r="B293" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="C293" s="4"/>
-      <c r="D293" s="4"/>
-      <c r="E293" s="4"/>
-      <c r="F293" s="4"/>
-      <c r="G293" s="4"/>
-      <c r="H293" s="7"/>
+      <c r="C293" s="2"/>
+      <c r="D293" s="2"/>
+      <c r="E293" s="2"/>
+      <c r="F293" s="2"/>
+      <c r="G293" s="2"/>
+      <c r="H293" s="4"/>
     </row>
     <row r="294" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="8" t="s">
+      <c r="A294" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="B294" s="5"/>
-      <c r="C294" s="5"/>
-      <c r="D294" s="5"/>
-      <c r="E294" s="5"/>
-      <c r="F294" s="4"/>
-      <c r="G294" s="4"/>
-      <c r="H294" s="7" t="s">
+      <c r="B294" s="14"/>
+      <c r="C294" s="14"/>
+      <c r="D294" s="14"/>
+      <c r="E294" s="14"/>
+      <c r="F294" s="2"/>
+      <c r="G294" s="2"/>
+      <c r="H294" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="6" t="s">
+      <c r="A295" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="B295" s="4" t="s">
+      <c r="B295" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="C295" s="4"/>
-      <c r="D295" s="4"/>
-      <c r="E295" s="4"/>
-      <c r="F295" s="4"/>
-      <c r="G295" s="4"/>
-      <c r="H295" s="7"/>
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
+      <c r="E295" s="2"/>
+      <c r="F295" s="2"/>
+      <c r="G295" s="2"/>
+      <c r="H295" s="4"/>
     </row>
     <row r="296" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="6" t="s">
+      <c r="A296" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="B296" s="4" t="s">
+      <c r="B296" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C296" s="4"/>
-      <c r="D296" s="4"/>
-      <c r="E296" s="4"/>
-      <c r="F296" s="4"/>
-      <c r="G296" s="4"/>
-      <c r="H296" s="7"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
+      <c r="E296" s="2"/>
+      <c r="F296" s="2"/>
+      <c r="G296" s="2"/>
+      <c r="H296" s="4"/>
     </row>
     <row r="297" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="6" t="s">
+      <c r="A297" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B297" s="4" t="s">
+      <c r="B297" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="C297" s="4"/>
-      <c r="D297" s="4"/>
-      <c r="E297" s="4"/>
-      <c r="F297" s="4"/>
-      <c r="G297" s="4"/>
-      <c r="H297" s="7"/>
+      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
+      <c r="E297" s="2"/>
+      <c r="F297" s="2"/>
+      <c r="G297" s="2"/>
+      <c r="H297" s="4"/>
     </row>
     <row r="298" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="6" t="s">
+      <c r="A298" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="B298" s="4" t="s">
+      <c r="B298" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="C298" s="4"/>
-      <c r="D298" s="4"/>
-      <c r="E298" s="4"/>
-      <c r="F298" s="4"/>
-      <c r="G298" s="4"/>
-      <c r="H298" s="7"/>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
+      <c r="E298" s="2"/>
+      <c r="F298" s="2"/>
+      <c r="G298" s="2"/>
+      <c r="H298" s="4"/>
     </row>
     <row r="299" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="6" t="s">
+      <c r="A299" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="B299" s="4" t="s">
+      <c r="B299" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C299" s="4"/>
-      <c r="D299" s="4"/>
-      <c r="E299" s="4"/>
-      <c r="F299" s="4"/>
-      <c r="G299" s="4"/>
-      <c r="H299" s="7"/>
+      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
+      <c r="E299" s="2"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="2"/>
+      <c r="H299" s="4"/>
     </row>
     <row r="300" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="6" t="s">
+      <c r="A300" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B300" s="4" t="s">
+      <c r="B300" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C300" s="4"/>
-      <c r="D300" s="4"/>
-      <c r="E300" s="4"/>
-      <c r="F300" s="4"/>
-      <c r="G300" s="4"/>
-      <c r="H300" s="7"/>
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
+      <c r="E300" s="2"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="2"/>
+      <c r="H300" s="4"/>
     </row>
     <row r="301" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="8" t="s">
+      <c r="A301" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="B301" s="5"/>
-      <c r="C301" s="5"/>
-      <c r="D301" s="5"/>
-      <c r="E301" s="5"/>
-      <c r="F301" s="4"/>
-      <c r="G301" s="4"/>
-      <c r="H301" s="7" t="s">
+      <c r="B301" s="14"/>
+      <c r="C301" s="14"/>
+      <c r="D301" s="14"/>
+      <c r="E301" s="14"/>
+      <c r="F301" s="2"/>
+      <c r="G301" s="2"/>
+      <c r="H301" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="302" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A302" s="9" t="s">
+      <c r="A302" s="15" t="s">
         <v>580</v>
       </c>
-      <c r="B302" s="10"/>
-      <c r="C302" s="10"/>
-      <c r="D302" s="10"/>
-      <c r="E302" s="10"/>
-      <c r="F302" s="11"/>
-      <c r="G302" s="11"/>
-      <c r="H302" s="12"/>
+      <c r="B302" s="16"/>
+      <c r="C302" s="16"/>
+      <c r="D302" s="16"/>
+      <c r="E302" s="16"/>
+      <c r="F302" s="5"/>
+      <c r="G302" s="5"/>
+      <c r="H302" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A294:E294"/>
-    <mergeCell ref="A301:E301"/>
-    <mergeCell ref="A261:E261"/>
-    <mergeCell ref="A302:E302"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A141:E141"/>
-    <mergeCell ref="A219:E219"/>
-    <mergeCell ref="A240:E240"/>
-    <mergeCell ref="A276:E276"/>
-    <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A79:E79"/>
     <mergeCell ref="A2:H3"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A191:E191"/>
     <mergeCell ref="A149:E149"/>
     <mergeCell ref="A158:E158"/>
     <mergeCell ref="A126:E126"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A141:E141"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A294:E294"/>
+    <mergeCell ref="A301:E301"/>
+    <mergeCell ref="A261:E261"/>
+    <mergeCell ref="A302:E302"/>
+    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A240:E240"/>
+    <mergeCell ref="A276:E276"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data/temp1.xlsx
+++ b/data/temp1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD14C143-B7D4-4636-8AD3-715F5C3432EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE13DF7-2079-4A60-A36A-1ADB3AF770AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21750" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="국내생산 계획" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="547">
   <si>
     <t/>
   </si>
@@ -340,18 +340,6 @@
     <t>YS DNC4307-64MR10B (기본품)</t>
   </si>
   <si>
-    <t>11315</t>
-  </si>
-  <si>
-    <t>YS CAM S/W(10A)-DNC</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>YS KDNC 10A-02련</t>
-  </si>
-  <si>
     <t>CAM(기본)</t>
   </si>
   <si>
@@ -361,42 +349,6 @@
     <t>YS 5C2207-29MKB</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>YS 5C-2-03M(수동)</t>
-  </si>
-  <si>
-    <t>22245</t>
-  </si>
-  <si>
-    <t>YS RAX 13</t>
-  </si>
-  <si>
-    <t>22561</t>
-  </si>
-  <si>
-    <t>YS RAX 15</t>
-  </si>
-  <si>
-    <t>11316</t>
-  </si>
-  <si>
-    <t>YS CAM S/W(20A)-DNC</t>
-  </si>
-  <si>
-    <t>11317</t>
-  </si>
-  <si>
-    <t>YS CAM S/W(30A)-DNC</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>YS LR2-04</t>
-  </si>
-  <si>
     <t>152</t>
   </si>
   <si>
@@ -1144,18 +1096,6 @@
     <t>릴레이</t>
   </si>
   <si>
-    <t>13757</t>
-  </si>
-  <si>
-    <t>YS E-3712-S</t>
-  </si>
-  <si>
-    <t>13758</t>
-  </si>
-  <si>
-    <t>YS E-3720-S</t>
-  </si>
-  <si>
     <t>24675</t>
   </si>
   <si>
@@ -1174,18 +1114,6 @@
     <t>YS BC30-6</t>
   </si>
   <si>
-    <t>13738</t>
-  </si>
-  <si>
-    <t>YS E-3712-R</t>
-  </si>
-  <si>
-    <t>13739</t>
-  </si>
-  <si>
-    <t>YS E-3720-R</t>
-  </si>
-  <si>
     <t>1079</t>
   </si>
   <si>
@@ -1306,30 +1234,6 @@
     <t>YS FT400-03ZF</t>
   </si>
   <si>
-    <t>1097</t>
-  </si>
-  <si>
-    <t>YS VR 11 1W-9M</t>
-  </si>
-  <si>
-    <t>13754</t>
-  </si>
-  <si>
-    <t>YS 2CG-1180-015</t>
-  </si>
-  <si>
-    <t>16218</t>
-  </si>
-  <si>
-    <t>YS 2CG-1180-007</t>
-  </si>
-  <si>
-    <t>1089</t>
-  </si>
-  <si>
-    <t>YS VR 05 1W-9M</t>
-  </si>
-  <si>
     <t>복합</t>
   </si>
   <si>
@@ -1457,24 +1361,6 @@
   </si>
   <si>
     <t>YS PL3-DL24 Y</t>
-  </si>
-  <si>
-    <t>13779</t>
-  </si>
-  <si>
-    <t>YS APL8-DL24 G</t>
-  </si>
-  <si>
-    <t>13778</t>
-  </si>
-  <si>
-    <t>YS APL8-DL24 R</t>
-  </si>
-  <si>
-    <t>13780</t>
-  </si>
-  <si>
-    <t>YS APL8-DL24 Y</t>
   </si>
   <si>
     <t>서브 라인</t>
@@ -1781,6 +1667,12 @@
   <si>
     <t>총 계획 금액</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YS R1010 GW-B - LS용 UL</t>
+  </si>
+  <si>
+    <t>YS NPBL2-T22A(Y)</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +1928,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2074,10 +1966,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2086,17 +1990,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2441,7 +2336,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H285"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="1" customWidth="1"/>
@@ -2476,24 +2371,24 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
@@ -2517,7 +2412,7 @@
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E5" s="18" t="s">
-        <v>581</v>
+        <v>543</v>
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="17"/>
@@ -2525,7 +2420,7 @@
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E6" s="18" t="s">
-        <v>582</v>
+        <v>544</v>
       </c>
       <c r="F6" s="18"/>
       <c r="G6" s="17"/>
@@ -2540,22 +2435,22 @@
         <v>2</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>574</v>
+        <v>536</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>575</v>
+        <v>537</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>576</v>
+        <v>538</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>578</v>
+        <v>540</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>579</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2709,7 +2604,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="20"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2741,13 +2636,13 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="4" t="s">
@@ -2756,10 +2651,10 @@
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -2770,10 +2665,10 @@
     </row>
     <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -2784,10 +2679,10 @@
     </row>
     <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -2798,10 +2693,10 @@
     </row>
     <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>443</v>
+        <v>411</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -2812,10 +2707,10 @@
     </row>
     <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -2826,10 +2721,10 @@
     </row>
     <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>447</v>
+        <v>415</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -2840,10 +2735,10 @@
     </row>
     <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>448</v>
+        <v>416</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -2854,10 +2749,10 @@
     </row>
     <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -2868,10 +2763,10 @@
     </row>
     <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>452</v>
+        <v>420</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>453</v>
+        <v>421</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -2882,10 +2777,10 @@
     </row>
     <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -2896,10 +2791,10 @@
     </row>
     <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -2910,10 +2805,10 @@
     </row>
     <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>459</v>
+        <v>427</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -2924,10 +2819,10 @@
     </row>
     <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>460</v>
+        <v>428</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -2938,10 +2833,10 @@
     </row>
     <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -2952,10 +2847,10 @@
     </row>
     <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -2966,10 +2861,10 @@
     </row>
     <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -2980,10 +2875,10 @@
     </row>
     <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>468</v>
+        <v>436</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -2994,10 +2889,10 @@
     </row>
     <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -3008,10 +2903,10 @@
     </row>
     <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -3022,10 +2917,10 @@
     </row>
     <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -3036,10 +2931,10 @@
     </row>
     <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -3049,25 +2944,25 @@
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="A44" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="4"/>
+      <c r="H44" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>480</v>
+        <v>357</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>481</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -3078,10 +2973,10 @@
     </row>
     <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>482</v>
+        <v>359</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>483</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -3091,25 +2986,25 @@
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
+      <c r="A47" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -3120,10 +3015,10 @@
     </row>
     <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -3134,10 +3029,10 @@
     </row>
     <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -3148,10 +3043,10 @@
     </row>
     <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -3162,10 +3057,10 @@
     </row>
     <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -3176,10 +3071,10 @@
     </row>
     <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -3190,10 +3085,10 @@
     </row>
     <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -3204,10 +3099,10 @@
     </row>
     <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -3218,10 +3113,10 @@
     </row>
     <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -3232,10 +3127,10 @@
     </row>
     <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -3246,10 +3141,10 @@
     </row>
     <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -3260,10 +3155,10 @@
     </row>
     <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -3274,10 +3169,10 @@
     </row>
     <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -3288,10 +3183,10 @@
     </row>
     <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -3302,10 +3197,10 @@
     </row>
     <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -3316,10 +3211,10 @@
     </row>
     <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -3330,10 +3225,10 @@
     </row>
     <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -3344,10 +3239,10 @@
     </row>
     <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -3358,10 +3253,10 @@
     </row>
     <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -3372,10 +3267,10 @@
     </row>
     <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -3385,25 +3280,25 @@
       <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
+      <c r="A68" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="4"/>
+      <c r="H68" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>415</v>
+        <v>290</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>416</v>
+        <v>291</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -3414,10 +3309,10 @@
     </row>
     <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>417</v>
+        <v>292</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>418</v>
+        <v>293</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -3428,10 +3323,10 @@
     </row>
     <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>419</v>
+        <v>294</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>420</v>
+        <v>295</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -3442,10 +3337,10 @@
     </row>
     <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>421</v>
+        <v>296</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>422</v>
+        <v>297</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -3456,10 +3351,10 @@
     </row>
     <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>423</v>
+        <v>298</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>424</v>
+        <v>299</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -3470,10 +3365,10 @@
     </row>
     <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>425</v>
+        <v>300</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>426</v>
+        <v>301</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -3484,10 +3379,10 @@
     </row>
     <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>427</v>
+        <v>302</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>428</v>
+        <v>303</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -3498,10 +3393,10 @@
     </row>
     <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>429</v>
+        <v>304</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>430</v>
+        <v>305</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -3512,10 +3407,10 @@
     </row>
     <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>431</v>
+        <v>306</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>432</v>
+        <v>307</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -3526,10 +3421,10 @@
     </row>
     <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>433</v>
+        <v>308</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>434</v>
+        <v>309</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -3539,25 +3434,25 @@
       <c r="H78" s="4"/>
     </row>
     <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
+      <c r="A79" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -3568,10 +3463,10 @@
     </row>
     <row r="81" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -3582,10 +3477,10 @@
     </row>
     <row r="82" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -3596,10 +3491,10 @@
     </row>
     <row r="83" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -3610,10 +3505,10 @@
     </row>
     <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -3624,10 +3519,10 @@
     </row>
     <row r="85" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -3638,10 +3533,10 @@
     </row>
     <row r="86" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -3652,10 +3547,10 @@
     </row>
     <row r="87" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -3666,10 +3561,10 @@
     </row>
     <row r="88" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -3680,10 +3575,10 @@
     </row>
     <row r="89" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -3694,10 +3589,10 @@
     </row>
     <row r="90" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -3708,10 +3603,10 @@
     </row>
     <row r="91" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -3722,10 +3617,10 @@
     </row>
     <row r="92" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -3736,10 +3631,10 @@
     </row>
     <row r="93" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -3750,10 +3645,10 @@
     </row>
     <row r="94" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -3764,10 +3659,10 @@
     </row>
     <row r="95" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -3778,10 +3673,10 @@
     </row>
     <row r="96" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -3792,10 +3687,10 @@
     </row>
     <row r="97" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -3806,10 +3701,10 @@
     </row>
     <row r="98" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -3820,10 +3715,10 @@
     </row>
     <row r="99" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -3834,10 +3729,10 @@
     </row>
     <row r="100" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -3848,10 +3743,10 @@
     </row>
     <row r="101" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -3861,25 +3756,25 @@
       <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
+      <c r="A102" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
-      <c r="H102" s="4"/>
+      <c r="H102" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="103" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>352</v>
+        <v>111</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -3890,10 +3785,10 @@
     </row>
     <row r="104" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>354</v>
+        <v>113</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>355</v>
+        <v>114</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -3904,10 +3799,10 @@
     </row>
     <row r="105" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>356</v>
+        <v>115</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>357</v>
+        <v>116</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -3918,10 +3813,10 @@
     </row>
     <row r="106" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>358</v>
+        <v>117</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>359</v>
+        <v>118</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -3932,10 +3827,10 @@
     </row>
     <row r="107" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>360</v>
+        <v>119</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>361</v>
+        <v>120</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -3946,10 +3841,10 @@
     </row>
     <row r="108" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>362</v>
+        <v>121</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>363</v>
+        <v>122</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -3960,10 +3855,10 @@
     </row>
     <row r="109" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>364</v>
+        <v>123</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>365</v>
+        <v>124</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -3974,10 +3869,10 @@
     </row>
     <row r="110" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>366</v>
+        <v>125</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>367</v>
+        <v>126</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -3988,10 +3883,10 @@
     </row>
     <row r="111" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>368</v>
+        <v>127</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>369</v>
+        <v>128</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -4002,10 +3897,10 @@
     </row>
     <row r="112" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>370</v>
+        <v>129</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>371</v>
+        <v>130</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -4015,25 +3910,25 @@
       <c r="H112" s="4"/>
     </row>
     <row r="113" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="B113" s="14"/>
-      <c r="C113" s="14"/>
-      <c r="D113" s="14"/>
-      <c r="E113" s="14"/>
+      <c r="A113" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
-      <c r="H113" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H113" s="4"/>
     </row>
     <row r="114" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -4043,25 +3938,25 @@
       <c r="H114" s="4"/>
     </row>
     <row r="115" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
+      <c r="A115" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="16"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
-      <c r="H115" s="4"/>
+      <c r="H115" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="116" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -4072,10 +3967,10 @@
     </row>
     <row r="117" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -4086,10 +3981,10 @@
     </row>
     <row r="118" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -4100,10 +3995,10 @@
     </row>
     <row r="119" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -4114,10 +4009,10 @@
     </row>
     <row r="120" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -4128,10 +4023,10 @@
     </row>
     <row r="121" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -4142,10 +4037,10 @@
     </row>
     <row r="122" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -4156,10 +4051,10 @@
     </row>
     <row r="123" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -4170,10 +4065,10 @@
     </row>
     <row r="124" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -4184,10 +4079,10 @@
     </row>
     <row r="125" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -4197,25 +4092,25 @@
       <c r="H125" s="4"/>
     </row>
     <row r="126" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="B126" s="14"/>
-      <c r="C126" s="14"/>
-      <c r="D126" s="14"/>
-      <c r="E126" s="14"/>
+      <c r="A126" s="21">
+        <v>29242</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
-      <c r="H126" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H126" s="4"/>
     </row>
     <row r="127" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -4226,10 +4121,10 @@
     </row>
     <row r="128" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -4240,10 +4135,10 @@
     </row>
     <row r="129" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -4254,10 +4149,10 @@
     </row>
     <row r="130" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -4267,25 +4162,25 @@
       <c r="H130" s="4"/>
     </row>
     <row r="131" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
+      <c r="A131" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B131" s="16"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="16"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
-      <c r="H131" s="4"/>
+      <c r="H131" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="132" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -4296,10 +4191,10 @@
     </row>
     <row r="133" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -4310,10 +4205,10 @@
     </row>
     <row r="134" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -4324,10 +4219,10 @@
     </row>
     <row r="135" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -4338,10 +4233,10 @@
     </row>
     <row r="136" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -4351,25 +4246,25 @@
       <c r="H136" s="4"/>
     </row>
     <row r="137" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
+      <c r="A137" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B137" s="16"/>
+      <c r="C137" s="16"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="16"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
-      <c r="H137" s="4"/>
+      <c r="H137" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="138" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -4380,10 +4275,10 @@
     </row>
     <row r="139" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -4393,39 +4288,39 @@
       <c r="H139" s="4"/>
     </row>
     <row r="140" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
+      <c r="A140" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B140" s="16"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
-      <c r="H140" s="4"/>
+      <c r="H140" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="141" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B141" s="14"/>
-      <c r="C141" s="14"/>
-      <c r="D141" s="14"/>
-      <c r="E141" s="14"/>
+      <c r="A141" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
-      <c r="H141" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H141" s="4"/>
     </row>
     <row r="142" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -4436,10 +4331,10 @@
     </row>
     <row r="143" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -4450,10 +4345,10 @@
     </row>
     <row r="144" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -4464,10 +4359,10 @@
     </row>
     <row r="145" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -4478,10 +4373,10 @@
     </row>
     <row r="146" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -4492,10 +4387,10 @@
     </row>
     <row r="147" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -4506,10 +4401,10 @@
     </row>
     <row r="148" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -4519,25 +4414,25 @@
       <c r="H148" s="4"/>
     </row>
     <row r="149" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B149" s="14"/>
-      <c r="C149" s="14"/>
-      <c r="D149" s="14"/>
-      <c r="E149" s="14"/>
+      <c r="A149" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
-      <c r="H149" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H149" s="4"/>
     </row>
     <row r="150" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -4548,10 +4443,10 @@
     </row>
     <row r="151" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -4562,10 +4457,10 @@
     </row>
     <row r="152" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -4576,10 +4471,10 @@
     </row>
     <row r="153" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -4590,10 +4485,10 @@
     </row>
     <row r="154" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -4604,10 +4499,10 @@
     </row>
     <row r="155" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -4618,10 +4513,10 @@
     </row>
     <row r="156" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -4632,10 +4527,10 @@
     </row>
     <row r="157" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -4645,25 +4540,25 @@
       <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B158" s="14"/>
-      <c r="C158" s="14"/>
-      <c r="D158" s="14"/>
-      <c r="E158" s="14"/>
+      <c r="A158" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-      <c r="H158" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H158" s="4"/>
     </row>
     <row r="159" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -4674,10 +4569,10 @@
     </row>
     <row r="160" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -4688,10 +4583,10 @@
     </row>
     <row r="161" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -4702,10 +4597,10 @@
     </row>
     <row r="162" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -4716,10 +4611,10 @@
     </row>
     <row r="163" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -4730,10 +4625,10 @@
     </row>
     <row r="164" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -4744,10 +4639,10 @@
     </row>
     <row r="165" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -4758,10 +4653,10 @@
     </row>
     <row r="166" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -4772,10 +4667,10 @@
     </row>
     <row r="167" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -4786,10 +4681,10 @@
     </row>
     <row r="168" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -4800,10 +4695,10 @@
     </row>
     <row r="169" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -4814,10 +4709,10 @@
     </row>
     <row r="170" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -4828,10 +4723,10 @@
     </row>
     <row r="171" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -4842,10 +4737,10 @@
     </row>
     <row r="172" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -4855,25 +4750,25 @@
       <c r="H172" s="4"/>
     </row>
     <row r="173" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
+      <c r="A173" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B173" s="16"/>
+      <c r="C173" s="16"/>
+      <c r="D173" s="16"/>
+      <c r="E173" s="16"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
-      <c r="H173" s="4"/>
+      <c r="H173" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="174" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -4884,10 +4779,10 @@
     </row>
     <row r="175" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -4897,11 +4792,11 @@
       <c r="H175" s="4"/>
     </row>
     <row r="176" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="3" t="s">
-        <v>64</v>
+      <c r="A176" s="21">
+        <v>1120</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>65</v>
+        <v>546</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -4912,10 +4807,10 @@
     </row>
     <row r="177" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -4926,10 +4821,10 @@
     </row>
     <row r="178" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -4940,10 +4835,10 @@
     </row>
     <row r="179" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>70</v>
+        <v>173</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>71</v>
+        <v>174</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -4954,10 +4849,10 @@
     </row>
     <row r="180" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -4968,10 +4863,10 @@
     </row>
     <row r="181" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -4982,10 +4877,10 @@
     </row>
     <row r="182" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -4996,10 +4891,10 @@
     </row>
     <row r="183" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -5010,10 +4905,10 @@
     </row>
     <row r="184" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -5024,10 +4919,10 @@
     </row>
     <row r="185" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -5038,10 +4933,10 @@
     </row>
     <row r="186" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -5052,10 +4947,10 @@
     </row>
     <row r="187" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -5066,10 +4961,10 @@
     </row>
     <row r="188" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>88</v>
+        <v>191</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -5080,10 +4975,10 @@
     </row>
     <row r="189" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -5094,10 +4989,10 @@
     </row>
     <row r="190" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -5107,25 +5002,25 @@
       <c r="H190" s="4"/>
     </row>
     <row r="191" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B191" s="14"/>
-      <c r="C191" s="14"/>
-      <c r="D191" s="14"/>
-      <c r="E191" s="14"/>
+      <c r="A191" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
-      <c r="H191" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H191" s="4"/>
     </row>
     <row r="192" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -5136,10 +5031,10 @@
     </row>
     <row r="193" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -5150,10 +5045,10 @@
     </row>
     <row r="194" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -5164,10 +5059,10 @@
     </row>
     <row r="195" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -5178,10 +5073,10 @@
     </row>
     <row r="196" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -5192,10 +5087,10 @@
     </row>
     <row r="197" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -5206,10 +5101,10 @@
     </row>
     <row r="198" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -5220,10 +5115,10 @@
     </row>
     <row r="199" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -5234,10 +5129,10 @@
     </row>
     <row r="200" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -5248,10 +5143,10 @@
     </row>
     <row r="201" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -5261,25 +5156,25 @@
       <c r="H201" s="4"/>
     </row>
     <row r="202" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
+      <c r="A202" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B202" s="16"/>
+      <c r="C202" s="16"/>
+      <c r="D202" s="16"/>
+      <c r="E202" s="16"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
-      <c r="H202" s="4"/>
+      <c r="H202" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="203" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
@@ -5290,10 +5185,10 @@
     </row>
     <row r="204" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
@@ -5304,10 +5199,10 @@
     </row>
     <row r="205" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -5318,10 +5213,10 @@
     </row>
     <row r="206" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -5332,10 +5227,10 @@
     </row>
     <row r="207" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
@@ -5346,10 +5241,10 @@
     </row>
     <row r="208" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
@@ -5360,10 +5255,10 @@
     </row>
     <row r="209" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -5374,10 +5269,10 @@
     </row>
     <row r="210" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
@@ -5388,10 +5283,10 @@
     </row>
     <row r="211" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -5402,10 +5297,10 @@
     </row>
     <row r="212" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -5416,10 +5311,10 @@
     </row>
     <row r="213" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
@@ -5430,10 +5325,10 @@
     </row>
     <row r="214" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -5444,10 +5339,10 @@
     </row>
     <row r="215" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
@@ -5458,10 +5353,10 @@
     </row>
     <row r="216" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -5472,10 +5367,10 @@
     </row>
     <row r="217" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
@@ -5486,10 +5381,10 @@
     </row>
     <row r="218" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -5499,25 +5394,25 @@
       <c r="H218" s="4"/>
     </row>
     <row r="219" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="B219" s="14"/>
-      <c r="C219" s="14"/>
-      <c r="D219" s="14"/>
-      <c r="E219" s="14"/>
+      <c r="A219" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
-      <c r="H219" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H219" s="4"/>
     </row>
     <row r="220" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
@@ -5528,10 +5423,10 @@
     </row>
     <row r="221" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
@@ -5542,10 +5437,10 @@
     </row>
     <row r="222" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
@@ -5555,25 +5450,25 @@
       <c r="H222" s="4"/>
     </row>
     <row r="223" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
+      <c r="A223" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B223" s="16"/>
+      <c r="C223" s="16"/>
+      <c r="D223" s="16"/>
+      <c r="E223" s="16"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
-      <c r="H223" s="4"/>
+      <c r="H223" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="224" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>244</v>
+        <v>495</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>245</v>
+        <v>496</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
@@ -5584,10 +5479,10 @@
     </row>
     <row r="225" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>246</v>
+        <v>497</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>247</v>
+        <v>498</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
@@ -5598,10 +5493,10 @@
     </row>
     <row r="226" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>248</v>
+        <v>499</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>249</v>
+        <v>500</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
@@ -5612,10 +5507,10 @@
     </row>
     <row r="227" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>250</v>
+        <v>501</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>251</v>
+        <v>502</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
@@ -5626,10 +5521,10 @@
     </row>
     <row r="228" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>252</v>
+        <v>503</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>253</v>
+        <v>504</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
@@ -5640,10 +5535,10 @@
     </row>
     <row r="229" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>254</v>
+        <v>505</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>255</v>
+        <v>506</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
@@ -5654,10 +5549,10 @@
     </row>
     <row r="230" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>256</v>
+        <v>507</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>257</v>
+        <v>508</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
@@ -5668,10 +5563,10 @@
     </row>
     <row r="231" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>258</v>
+        <v>509</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>259</v>
+        <v>510</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
@@ -5682,10 +5577,10 @@
     </row>
     <row r="232" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>260</v>
+        <v>511</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>261</v>
+        <v>512</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
@@ -5696,10 +5591,10 @@
     </row>
     <row r="233" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>262</v>
+        <v>513</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>263</v>
+        <v>514</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
@@ -5710,10 +5605,10 @@
     </row>
     <row r="234" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>264</v>
+        <v>515</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>265</v>
+        <v>516</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
@@ -5724,10 +5619,10 @@
     </row>
     <row r="235" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>266</v>
+        <v>517</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>267</v>
+        <v>518</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
@@ -5738,10 +5633,10 @@
     </row>
     <row r="236" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>268</v>
+        <v>519</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>269</v>
+        <v>520</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
@@ -5752,10 +5647,10 @@
     </row>
     <row r="237" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>270</v>
+        <v>521</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>271</v>
+        <v>522</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
@@ -5766,10 +5661,10 @@
     </row>
     <row r="238" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>272</v>
+        <v>523</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>273</v>
+        <v>524</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
@@ -5780,10 +5675,10 @@
     </row>
     <row r="239" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>274</v>
+        <v>525</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>275</v>
+        <v>526</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
@@ -5793,25 +5688,25 @@
       <c r="H239" s="4"/>
     </row>
     <row r="240" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="B240" s="14"/>
-      <c r="C240" s="14"/>
-      <c r="D240" s="14"/>
-      <c r="E240" s="14"/>
+      <c r="A240" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
-      <c r="H240" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H240" s="4"/>
     </row>
     <row r="241" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
@@ -5822,10 +5717,10 @@
     </row>
     <row r="242" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
@@ -5836,10 +5731,10 @@
     </row>
     <row r="243" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -5849,25 +5744,25 @@
       <c r="H243" s="4"/>
     </row>
     <row r="244" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
+      <c r="A244" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="B244" s="16"/>
+      <c r="C244" s="16"/>
+      <c r="D244" s="16"/>
+      <c r="E244" s="16"/>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
-      <c r="H244" s="4"/>
+      <c r="H244" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="245" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>541</v>
+        <v>261</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>542</v>
+        <v>262</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
@@ -5878,10 +5773,10 @@
     </row>
     <row r="246" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>543</v>
+        <v>263</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>544</v>
+        <v>264</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
@@ -5892,10 +5787,10 @@
     </row>
     <row r="247" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>545</v>
+        <v>265</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>546</v>
+        <v>266</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
@@ -5906,10 +5801,10 @@
     </row>
     <row r="248" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>547</v>
+        <v>267</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>548</v>
+        <v>268</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
@@ -5920,10 +5815,10 @@
     </row>
     <row r="249" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>549</v>
+        <v>269</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>550</v>
+        <v>270</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
@@ -5934,10 +5829,10 @@
     </row>
     <row r="250" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>551</v>
+        <v>271</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>552</v>
+        <v>272</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
@@ -5948,10 +5843,10 @@
     </row>
     <row r="251" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>553</v>
+        <v>273</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>554</v>
+        <v>274</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
@@ -5962,10 +5857,10 @@
     </row>
     <row r="252" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
-        <v>555</v>
+        <v>275</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>556</v>
+        <v>276</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
@@ -5976,10 +5871,10 @@
     </row>
     <row r="253" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>557</v>
+        <v>277</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>558</v>
+        <v>278</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
@@ -5990,10 +5885,10 @@
     </row>
     <row r="254" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>559</v>
+        <v>279</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>560</v>
+        <v>280</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
@@ -6004,10 +5899,10 @@
     </row>
     <row r="255" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>561</v>
+        <v>281</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>562</v>
+        <v>282</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
@@ -6018,10 +5913,10 @@
     </row>
     <row r="256" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
-        <v>563</v>
+        <v>283</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>564</v>
+        <v>284</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
@@ -6032,10 +5927,10 @@
     </row>
     <row r="257" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>565</v>
+        <v>285</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>566</v>
+        <v>286</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
@@ -6046,10 +5941,10 @@
     </row>
     <row r="258" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
-        <v>567</v>
+        <v>287</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>568</v>
+        <v>288</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
@@ -6059,25 +5954,25 @@
       <c r="H258" s="4"/>
     </row>
     <row r="259" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
+      <c r="A259" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B259" s="16"/>
+      <c r="C259" s="16"/>
+      <c r="D259" s="16"/>
+      <c r="E259" s="16"/>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
-      <c r="H259" s="4"/>
+      <c r="H259" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="260" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
-        <v>571</v>
+        <v>447</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>572</v>
+        <v>448</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
@@ -6087,25 +5982,25 @@
       <c r="H260" s="4"/>
     </row>
     <row r="261" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="13" t="s">
-        <v>573</v>
-      </c>
-      <c r="B261" s="14"/>
-      <c r="C261" s="14"/>
-      <c r="D261" s="14"/>
-      <c r="E261" s="14"/>
+      <c r="A261" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
+      <c r="E261" s="2"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
-      <c r="H261" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H261" s="4"/>
     </row>
     <row r="262" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
-        <v>277</v>
+        <v>451</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>278</v>
+        <v>452</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
@@ -6116,10 +6011,10 @@
     </row>
     <row r="263" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>279</v>
+        <v>453</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>280</v>
+        <v>454</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
@@ -6130,10 +6025,10 @@
     </row>
     <row r="264" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>281</v>
+        <v>455</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>282</v>
+        <v>456</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
@@ -6144,10 +6039,10 @@
     </row>
     <row r="265" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>283</v>
+        <v>457</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>284</v>
+        <v>458</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
@@ -6158,10 +6053,10 @@
     </row>
     <row r="266" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
-        <v>285</v>
+        <v>459</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>286</v>
+        <v>460</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
@@ -6172,10 +6067,10 @@
     </row>
     <row r="267" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>287</v>
+        <v>461</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>288</v>
+        <v>462</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
@@ -6186,10 +6081,10 @@
     </row>
     <row r="268" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
-        <v>289</v>
+        <v>463</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>290</v>
+        <v>464</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
@@ -6200,10 +6095,10 @@
     </row>
     <row r="269" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>291</v>
+        <v>465</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>292</v>
+        <v>466</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
@@ -6214,10 +6109,10 @@
     </row>
     <row r="270" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
-        <v>293</v>
+        <v>467</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>294</v>
+        <v>468</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
@@ -6228,10 +6123,10 @@
     </row>
     <row r="271" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>295</v>
+        <v>469</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>296</v>
+        <v>470</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
@@ -6242,10 +6137,10 @@
     </row>
     <row r="272" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
-        <v>297</v>
+        <v>471</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>298</v>
+        <v>472</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
@@ -6256,10 +6151,10 @@
     </row>
     <row r="273" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>299</v>
+        <v>473</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>300</v>
+        <v>474</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -6270,10 +6165,10 @@
     </row>
     <row r="274" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
-        <v>301</v>
+        <v>475</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>302</v>
+        <v>476</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
@@ -6284,10 +6179,10 @@
     </row>
     <row r="275" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>303</v>
+        <v>477</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>304</v>
+        <v>478</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
@@ -6297,39 +6192,39 @@
       <c r="H275" s="4"/>
     </row>
     <row r="276" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="B276" s="14"/>
-      <c r="C276" s="14"/>
-      <c r="D276" s="14"/>
-      <c r="E276" s="14"/>
+      <c r="A276" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
+      <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
-      <c r="H276" s="4" t="s">
-        <v>0</v>
-      </c>
+      <c r="H276" s="4"/>
     </row>
     <row r="277" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
-      <c r="E277" s="2"/>
+      <c r="A277" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="B277" s="16"/>
+      <c r="C277" s="16"/>
+      <c r="D277" s="16"/>
+      <c r="E277" s="16"/>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
-      <c r="H277" s="4"/>
+      <c r="H277" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="278" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
@@ -6340,10 +6235,10 @@
     </row>
     <row r="279" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
@@ -6354,10 +6249,10 @@
     </row>
     <row r="280" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
@@ -6368,10 +6263,10 @@
     </row>
     <row r="281" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
@@ -6382,10 +6277,10 @@
     </row>
     <row r="282" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
@@ -6396,10 +6291,10 @@
     </row>
     <row r="283" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
@@ -6409,298 +6304,60 @@
       <c r="H283" s="4"/>
     </row>
     <row r="284" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C284" s="2"/>
-      <c r="D284" s="2"/>
-      <c r="E284" s="2"/>
+      <c r="A284" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="B284" s="16"/>
+      <c r="C284" s="16"/>
+      <c r="D284" s="16"/>
+      <c r="E284" s="16"/>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
-      <c r="H284" s="4"/>
-    </row>
-    <row r="285" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
-      <c r="E285" s="2"/>
-      <c r="F285" s="2"/>
-      <c r="G285" s="2"/>
-      <c r="H285" s="4"/>
-    </row>
-    <row r="286" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="C286" s="2"/>
-      <c r="D286" s="2"/>
-      <c r="E286" s="2"/>
-      <c r="F286" s="2"/>
-      <c r="G286" s="2"/>
-      <c r="H286" s="4"/>
-    </row>
-    <row r="287" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C287" s="2"/>
-      <c r="D287" s="2"/>
-      <c r="E287" s="2"/>
-      <c r="F287" s="2"/>
-      <c r="G287" s="2"/>
-      <c r="H287" s="4"/>
-    </row>
-    <row r="288" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C288" s="2"/>
-      <c r="D288" s="2"/>
-      <c r="E288" s="2"/>
-      <c r="F288" s="2"/>
-      <c r="G288" s="2"/>
-      <c r="H288" s="4"/>
-    </row>
-    <row r="289" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C289" s="2"/>
-      <c r="D289" s="2"/>
-      <c r="E289" s="2"/>
-      <c r="F289" s="2"/>
-      <c r="G289" s="2"/>
-      <c r="H289" s="4"/>
-    </row>
-    <row r="290" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C290" s="2"/>
-      <c r="D290" s="2"/>
-      <c r="E290" s="2"/>
-      <c r="F290" s="2"/>
-      <c r="G290" s="2"/>
-      <c r="H290" s="4"/>
-    </row>
-    <row r="291" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C291" s="2"/>
-      <c r="D291" s="2"/>
-      <c r="E291" s="2"/>
-      <c r="F291" s="2"/>
-      <c r="G291" s="2"/>
-      <c r="H291" s="4"/>
-    </row>
-    <row r="292" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C292" s="2"/>
-      <c r="D292" s="2"/>
-      <c r="E292" s="2"/>
-      <c r="F292" s="2"/>
-      <c r="G292" s="2"/>
-      <c r="H292" s="4"/>
-    </row>
-    <row r="293" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="C293" s="2"/>
-      <c r="D293" s="2"/>
-      <c r="E293" s="2"/>
-      <c r="F293" s="2"/>
-      <c r="G293" s="2"/>
-      <c r="H293" s="4"/>
-    </row>
-    <row r="294" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="13" t="s">
-        <v>519</v>
-      </c>
-      <c r="B294" s="14"/>
-      <c r="C294" s="14"/>
-      <c r="D294" s="14"/>
-      <c r="E294" s="14"/>
-      <c r="F294" s="2"/>
-      <c r="G294" s="2"/>
-      <c r="H294" s="4" t="s">
+      <c r="H284" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="C295" s="2"/>
-      <c r="D295" s="2"/>
-      <c r="E295" s="2"/>
-      <c r="F295" s="2"/>
-      <c r="G295" s="2"/>
-      <c r="H295" s="4"/>
-    </row>
-    <row r="296" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C296" s="2"/>
-      <c r="D296" s="2"/>
-      <c r="E296" s="2"/>
-      <c r="F296" s="2"/>
-      <c r="G296" s="2"/>
-      <c r="H296" s="4"/>
-    </row>
-    <row r="297" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C297" s="2"/>
-      <c r="D297" s="2"/>
-      <c r="E297" s="2"/>
-      <c r="F297" s="2"/>
-      <c r="G297" s="2"/>
-      <c r="H297" s="4"/>
-    </row>
-    <row r="298" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="C298" s="2"/>
-      <c r="D298" s="2"/>
-      <c r="E298" s="2"/>
-      <c r="F298" s="2"/>
-      <c r="G298" s="2"/>
-      <c r="H298" s="4"/>
-    </row>
-    <row r="299" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C299" s="2"/>
-      <c r="D299" s="2"/>
-      <c r="E299" s="2"/>
-      <c r="F299" s="2"/>
-      <c r="G299" s="2"/>
-      <c r="H299" s="4"/>
-    </row>
-    <row r="300" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C300" s="2"/>
-      <c r="D300" s="2"/>
-      <c r="E300" s="2"/>
-      <c r="F300" s="2"/>
-      <c r="G300" s="2"/>
-      <c r="H300" s="4"/>
-    </row>
-    <row r="301" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="13" t="s">
-        <v>532</v>
-      </c>
-      <c r="B301" s="14"/>
-      <c r="C301" s="14"/>
-      <c r="D301" s="14"/>
-      <c r="E301" s="14"/>
-      <c r="F301" s="2"/>
-      <c r="G301" s="2"/>
-      <c r="H301" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A302" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="B302" s="16"/>
-      <c r="C302" s="16"/>
-      <c r="D302" s="16"/>
-      <c r="E302" s="16"/>
-      <c r="F302" s="5"/>
-      <c r="G302" s="5"/>
-      <c r="H302" s="6"/>
+    <row r="285" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A285" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="B285" s="20"/>
+      <c r="C285" s="20"/>
+      <c r="D285" s="20"/>
+      <c r="E285" s="20"/>
+      <c r="F285" s="5"/>
+      <c r="G285" s="5"/>
+      <c r="H285" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A277:E277"/>
+    <mergeCell ref="A284:E284"/>
+    <mergeCell ref="A244:E244"/>
+    <mergeCell ref="A285:E285"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A223:E223"/>
+    <mergeCell ref="A259:E259"/>
     <mergeCell ref="A2:H3"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A191:E191"/>
-    <mergeCell ref="A149:E149"/>
-    <mergeCell ref="A158:E158"/>
-    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A173:E173"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A115:E115"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A141:E141"/>
-    <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A294:E294"/>
-    <mergeCell ref="A301:E301"/>
-    <mergeCell ref="A261:E261"/>
-    <mergeCell ref="A302:E302"/>
-    <mergeCell ref="A219:E219"/>
-    <mergeCell ref="A240:E240"/>
-    <mergeCell ref="A276:E276"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A7:B21 D7:H7 B1 D1:H1 A159:B190 A22 H22 A191 H191 A192:B218 A220:B239 A219 H219 A262:B275 A240 H240 A276 H276 A277:B293 A295:B300 A294 A301 H301 H294 D4:H4" numberStoredAsText="1"/>
+    <ignoredError sqref="A7:B21 D7:H7 B1 D1:H1 A141:B172 A22 H22 A173 H173 A177:B201 A203:B222 A202 H202 A245:B258 A223 H223 A259 H259 A260:B276 A278:B283 A277 A284 H284 H277 D4:H4 A174:B175" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/temp1.xlsx
+++ b/data/temp1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE13DF7-2079-4A60-A36A-1ADB3AF770AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E64146-9B11-485A-9C52-D339A2EF8F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21750" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="국내생산 계획" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="549">
   <si>
     <t/>
   </si>
@@ -1673,6 +1673,14 @@
   </si>
   <si>
     <t>YS NPBL2-T22A(Y)</t>
+  </si>
+  <si>
+    <t>전전월 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전월 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1928,7 +1936,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1969,19 +1977,19 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1990,8 +1998,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2336,18 +2350,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:J285"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
-    <col min="3" max="6" width="10.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="8" width="10.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.77734375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2360,37 +2374,41 @@
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+    </row>
+    <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+    </row>
+    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2400,34 +2418,38 @@
       <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="H4" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="18" t="s">
+      <c r="I4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="23" t="s">
         <v>543</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="18" t="s">
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="23" t="s">
         <v>544</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-    </row>
-    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+    </row>
+    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>1</v>
       </c>
@@ -2444,16 +2466,22 @@
         <v>538</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>539</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="I8" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="J8" s="12" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>3</v>
       </c>
@@ -2465,9 +2493,11 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
@@ -2479,9 +2509,11 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -2493,9 +2525,11 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
@@ -2507,9 +2541,11 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
@@ -2521,9 +2557,11 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2535,9 +2573,11 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -2549,9 +2589,11 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -2563,9 +2605,11 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
@@ -2577,9 +2621,11 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>21</v>
       </c>
@@ -2591,9 +2637,11 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
@@ -2604,10 +2652,12 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
@@ -2619,9 +2669,11 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
@@ -2633,23 +2685,27 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="4" t="s">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>404</v>
       </c>
@@ -2661,9 +2717,11 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>406</v>
       </c>
@@ -2675,9 +2733,11 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>408</v>
       </c>
@@ -2689,9 +2749,11 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>410</v>
       </c>
@@ -2703,9 +2765,11 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>412</v>
       </c>
@@ -2717,9 +2781,11 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>414</v>
       </c>
@@ -2731,9 +2797,11 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>416</v>
       </c>
@@ -2745,9 +2813,11 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="4"/>
-    </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>418</v>
       </c>
@@ -2759,9 +2829,11 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>420</v>
       </c>
@@ -2773,9 +2845,11 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>422</v>
       </c>
@@ -2787,9 +2861,11 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>424</v>
       </c>
@@ -2801,9 +2877,11 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>426</v>
       </c>
@@ -2815,9 +2893,11 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>428</v>
       </c>
@@ -2829,9 +2909,11 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>430</v>
       </c>
@@ -2843,9 +2925,11 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>432</v>
       </c>
@@ -2857,9 +2941,11 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>434</v>
       </c>
@@ -2871,9 +2957,11 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>436</v>
       </c>
@@ -2885,9 +2973,11 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>438</v>
       </c>
@@ -2899,9 +2989,11 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>440</v>
       </c>
@@ -2913,9 +3005,11 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>442</v>
       </c>
@@ -2927,9 +3021,11 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>444</v>
       </c>
@@ -2941,23 +3037,27 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="17" t="s">
         <v>446</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="4" t="s">
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>357</v>
       </c>
@@ -2969,9 +3069,11 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>359</v>
       </c>
@@ -2983,9 +3085,11 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>361</v>
       </c>
@@ -2997,9 +3101,11 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>363</v>
       </c>
@@ -3011,9 +3117,11 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>365</v>
       </c>
@@ -3025,9 +3133,11 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>367</v>
       </c>
@@ -3039,9 +3149,11 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>369</v>
       </c>
@@ -3053,9 +3165,11 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="4"/>
-    </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>371</v>
       </c>
@@ -3067,9 +3181,11 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>373</v>
       </c>
@@ -3081,9 +3197,11 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>375</v>
       </c>
@@ -3095,9 +3213,11 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>377</v>
       </c>
@@ -3109,9 +3229,11 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>379</v>
       </c>
@@ -3123,9 +3245,11 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>381</v>
       </c>
@@ -3137,9 +3261,11 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>383</v>
       </c>
@@ -3151,9 +3277,11 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="4"/>
-    </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>385</v>
       </c>
@@ -3165,9 +3293,11 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>387</v>
       </c>
@@ -3179,9 +3309,11 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>389</v>
       </c>
@@ -3193,9 +3325,11 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="4"/>
-    </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>391</v>
       </c>
@@ -3207,9 +3341,11 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="4"/>
-    </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>393</v>
       </c>
@@ -3221,9 +3357,11 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="4"/>
-    </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>395</v>
       </c>
@@ -3235,9 +3373,11 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="4"/>
-    </row>
-    <row r="65" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>397</v>
       </c>
@@ -3249,9 +3389,11 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="4"/>
-    </row>
-    <row r="66" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>399</v>
       </c>
@@ -3263,9 +3405,11 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="4"/>
-    </row>
-    <row r="67" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>401</v>
       </c>
@@ -3277,23 +3421,27 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="4"/>
-    </row>
-    <row r="68" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="4"/>
+    </row>
+    <row r="68" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="4" t="s">
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>290</v>
       </c>
@@ -3305,9 +3453,11 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="4"/>
-    </row>
-    <row r="70" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="4"/>
+    </row>
+    <row r="70" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>292</v>
       </c>
@@ -3319,9 +3469,11 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>294</v>
       </c>
@@ -3333,9 +3485,11 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="4"/>
-    </row>
-    <row r="72" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="4"/>
+    </row>
+    <row r="72" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>296</v>
       </c>
@@ -3347,9 +3501,11 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-      <c r="H72" s="4"/>
-    </row>
-    <row r="73" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="4"/>
+    </row>
+    <row r="73" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>298</v>
       </c>
@@ -3361,9 +3517,11 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
-      <c r="H73" s="4"/>
-    </row>
-    <row r="74" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="4"/>
+    </row>
+    <row r="74" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>300</v>
       </c>
@@ -3375,9 +3533,11 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="4"/>
-    </row>
-    <row r="75" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="4"/>
+    </row>
+    <row r="75" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>302</v>
       </c>
@@ -3389,9 +3549,11 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
-      <c r="H75" s="4"/>
-    </row>
-    <row r="76" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="4"/>
+    </row>
+    <row r="76" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>304</v>
       </c>
@@ -3403,9 +3565,11 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
-      <c r="H76" s="4"/>
-    </row>
-    <row r="77" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="4"/>
+    </row>
+    <row r="77" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>306</v>
       </c>
@@ -3417,9 +3581,11 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
-      <c r="H77" s="4"/>
-    </row>
-    <row r="78" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="4"/>
+    </row>
+    <row r="78" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>308</v>
       </c>
@@ -3431,9 +3597,11 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="H78" s="4"/>
-    </row>
-    <row r="79" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="4"/>
+    </row>
+    <row r="79" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>310</v>
       </c>
@@ -3445,9 +3613,11 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="4"/>
-    </row>
-    <row r="80" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="4"/>
+    </row>
+    <row r="80" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>312</v>
       </c>
@@ -3459,9 +3629,11 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="4"/>
-    </row>
-    <row r="81" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="4"/>
+    </row>
+    <row r="81" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>314</v>
       </c>
@@ -3473,9 +3645,11 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="4"/>
-    </row>
-    <row r="82" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="4"/>
+    </row>
+    <row r="82" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>316</v>
       </c>
@@ -3487,9 +3661,11 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="4"/>
-    </row>
-    <row r="83" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="4"/>
+    </row>
+    <row r="83" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>318</v>
       </c>
@@ -3501,9 +3677,11 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
-      <c r="H83" s="4"/>
-    </row>
-    <row r="84" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="4"/>
+    </row>
+    <row r="84" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>320</v>
       </c>
@@ -3515,9 +3693,11 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-      <c r="H84" s="4"/>
-    </row>
-    <row r="85" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="4"/>
+    </row>
+    <row r="85" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>322</v>
       </c>
@@ -3529,9 +3709,11 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
-      <c r="H85" s="4"/>
-    </row>
-    <row r="86" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="4"/>
+    </row>
+    <row r="86" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>324</v>
       </c>
@@ -3543,9 +3725,11 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
-      <c r="H86" s="4"/>
-    </row>
-    <row r="87" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="4"/>
+    </row>
+    <row r="87" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>326</v>
       </c>
@@ -3557,9 +3741,11 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
-      <c r="H87" s="4"/>
-    </row>
-    <row r="88" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="4"/>
+    </row>
+    <row r="88" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>328</v>
       </c>
@@ -3571,9 +3757,11 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
-      <c r="H88" s="4"/>
-    </row>
-    <row r="89" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="4"/>
+    </row>
+    <row r="89" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>330</v>
       </c>
@@ -3585,9 +3773,11 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="4"/>
-    </row>
-    <row r="90" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="4"/>
+    </row>
+    <row r="90" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>332</v>
       </c>
@@ -3599,9 +3789,11 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-      <c r="H90" s="4"/>
-    </row>
-    <row r="91" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="4"/>
+    </row>
+    <row r="91" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>334</v>
       </c>
@@ -3613,9 +3805,11 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
-      <c r="H91" s="4"/>
-    </row>
-    <row r="92" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="4"/>
+    </row>
+    <row r="92" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>336</v>
       </c>
@@ -3627,9 +3821,11 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-      <c r="H92" s="4"/>
-    </row>
-    <row r="93" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="4"/>
+    </row>
+    <row r="93" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>338</v>
       </c>
@@ -3641,9 +3837,11 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-      <c r="H93" s="4"/>
-    </row>
-    <row r="94" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="4"/>
+    </row>
+    <row r="94" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>340</v>
       </c>
@@ -3655,9 +3853,11 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
-      <c r="H94" s="4"/>
-    </row>
-    <row r="95" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="4"/>
+    </row>
+    <row r="95" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>342</v>
       </c>
@@ -3669,9 +3869,11 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
-      <c r="H95" s="4"/>
-    </row>
-    <row r="96" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="4"/>
+    </row>
+    <row r="96" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>344</v>
       </c>
@@ -3683,9 +3885,11 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="4"/>
-    </row>
-    <row r="97" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="4"/>
+    </row>
+    <row r="97" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>346</v>
       </c>
@@ -3697,9 +3901,11 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="4"/>
-    </row>
-    <row r="98" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="4"/>
+    </row>
+    <row r="98" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>348</v>
       </c>
@@ -3711,9 +3917,11 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="4"/>
-    </row>
-    <row r="99" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="4"/>
+    </row>
+    <row r="99" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>350</v>
       </c>
@@ -3725,9 +3933,11 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-      <c r="H99" s="4"/>
-    </row>
-    <row r="100" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="4"/>
+    </row>
+    <row r="100" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>352</v>
       </c>
@@ -3739,9 +3949,11 @@
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
-      <c r="H100" s="4"/>
-    </row>
-    <row r="101" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="4"/>
+    </row>
+    <row r="101" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>354</v>
       </c>
@@ -3753,23 +3965,27 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
-      <c r="H101" s="4"/>
-    </row>
-    <row r="102" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="15" t="s">
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="4"/>
+    </row>
+    <row r="102" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="B102" s="16"/>
-      <c r="C102" s="16"/>
-      <c r="D102" s="16"/>
-      <c r="E102" s="16"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="4" t="s">
+      <c r="B102" s="18"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="18"/>
+      <c r="E102" s="18"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>111</v>
       </c>
@@ -3781,9 +3997,11 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
-      <c r="H103" s="4"/>
-    </row>
-    <row r="104" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="4"/>
+    </row>
+    <row r="104" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>113</v>
       </c>
@@ -3795,9 +4013,11 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
-      <c r="H104" s="4"/>
-    </row>
-    <row r="105" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="4"/>
+    </row>
+    <row r="105" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>115</v>
       </c>
@@ -3809,9 +4029,11 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
-      <c r="H105" s="4"/>
-    </row>
-    <row r="106" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="4"/>
+    </row>
+    <row r="106" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>117</v>
       </c>
@@ -3823,9 +4045,11 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
-      <c r="H106" s="4"/>
-    </row>
-    <row r="107" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="J106" s="4"/>
+    </row>
+    <row r="107" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>119</v>
       </c>
@@ -3837,9 +4061,11 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
-      <c r="H107" s="4"/>
-    </row>
-    <row r="108" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="4"/>
+    </row>
+    <row r="108" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>121</v>
       </c>
@@ -3851,9 +4077,11 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
-      <c r="H108" s="4"/>
-    </row>
-    <row r="109" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="4"/>
+    </row>
+    <row r="109" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>123</v>
       </c>
@@ -3865,9 +4093,11 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
-      <c r="H109" s="4"/>
-    </row>
-    <row r="110" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="4"/>
+    </row>
+    <row r="110" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>125</v>
       </c>
@@ -3879,9 +4109,11 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
-      <c r="H110" s="4"/>
-    </row>
-    <row r="111" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="4"/>
+    </row>
+    <row r="111" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>127</v>
       </c>
@@ -3893,9 +4125,11 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
-      <c r="H111" s="4"/>
-    </row>
-    <row r="112" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="4"/>
+    </row>
+    <row r="112" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>129</v>
       </c>
@@ -3907,9 +4141,11 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
-      <c r="H112" s="4"/>
-    </row>
-    <row r="113" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="4"/>
+    </row>
+    <row r="113" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>131</v>
       </c>
@@ -3921,9 +4157,11 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
-      <c r="H113" s="4"/>
-    </row>
-    <row r="114" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="4"/>
+    </row>
+    <row r="114" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>133</v>
       </c>
@@ -3935,23 +4173,27 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
-      <c r="H114" s="4"/>
-    </row>
-    <row r="115" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="15" t="s">
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="4"/>
+    </row>
+    <row r="115" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="4" t="s">
+      <c r="B115" s="18"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>136</v>
       </c>
@@ -3963,9 +4205,11 @@
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
-      <c r="H116" s="4"/>
-    </row>
-    <row r="117" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="4"/>
+    </row>
+    <row r="117" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>138</v>
       </c>
@@ -3977,9 +4221,11 @@
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
-      <c r="H117" s="4"/>
-    </row>
-    <row r="118" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="4"/>
+    </row>
+    <row r="118" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>140</v>
       </c>
@@ -3991,9 +4237,11 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
-      <c r="H118" s="4"/>
-    </row>
-    <row r="119" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="4"/>
+    </row>
+    <row r="119" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>142</v>
       </c>
@@ -4005,9 +4253,11 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
-      <c r="H119" s="4"/>
-    </row>
-    <row r="120" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="4"/>
+    </row>
+    <row r="120" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>144</v>
       </c>
@@ -4019,9 +4269,11 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
-      <c r="H120" s="4"/>
-    </row>
-    <row r="121" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="4"/>
+    </row>
+    <row r="121" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>146</v>
       </c>
@@ -4033,9 +4285,11 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
-      <c r="H121" s="4"/>
-    </row>
-    <row r="122" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="4"/>
+    </row>
+    <row r="122" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>148</v>
       </c>
@@ -4047,9 +4301,11 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
-      <c r="H122" s="4"/>
-    </row>
-    <row r="123" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="4"/>
+    </row>
+    <row r="123" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>150</v>
       </c>
@@ -4061,9 +4317,11 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
-      <c r="H123" s="4"/>
-    </row>
-    <row r="124" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H123" s="2"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="4"/>
+    </row>
+    <row r="124" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>152</v>
       </c>
@@ -4075,9 +4333,11 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
-      <c r="H124" s="4"/>
-    </row>
-    <row r="125" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H124" s="2"/>
+      <c r="I124" s="2"/>
+      <c r="J124" s="4"/>
+    </row>
+    <row r="125" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>154</v>
       </c>
@@ -4089,10 +4349,12 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
-      <c r="H125" s="4"/>
-    </row>
-    <row r="126" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="21">
+      <c r="H125" s="2"/>
+      <c r="I125" s="2"/>
+      <c r="J125" s="4"/>
+    </row>
+    <row r="126" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="16">
         <v>29242</v>
       </c>
       <c r="B126" s="2" t="s">
@@ -4103,9 +4365,11 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
-      <c r="H126" s="4"/>
-    </row>
-    <row r="127" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H126" s="2"/>
+      <c r="I126" s="2"/>
+      <c r="J126" s="4"/>
+    </row>
+    <row r="127" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>156</v>
       </c>
@@ -4117,9 +4381,11 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
-      <c r="H127" s="4"/>
-    </row>
-    <row r="128" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="4"/>
+    </row>
+    <row r="128" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>158</v>
       </c>
@@ -4131,9 +4397,11 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
-      <c r="H128" s="4"/>
-    </row>
-    <row r="129" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
+      <c r="J128" s="4"/>
+    </row>
+    <row r="129" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>160</v>
       </c>
@@ -4145,9 +4413,11 @@
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
-      <c r="H129" s="4"/>
-    </row>
-    <row r="130" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
+      <c r="J129" s="4"/>
+    </row>
+    <row r="130" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>162</v>
       </c>
@@ -4159,23 +4429,27 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
-      <c r="H130" s="4"/>
-    </row>
-    <row r="131" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="15" t="s">
+      <c r="H130" s="2"/>
+      <c r="I130" s="2"/>
+      <c r="J130" s="4"/>
+    </row>
+    <row r="131" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B131" s="16"/>
-      <c r="C131" s="16"/>
-      <c r="D131" s="16"/>
-      <c r="E131" s="16"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="4" t="s">
+      <c r="B131" s="18"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="14"/>
+      <c r="G131" s="14"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
+      <c r="J131" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>95</v>
       </c>
@@ -4187,9 +4461,11 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
-      <c r="H132" s="4"/>
-    </row>
-    <row r="133" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H132" s="2"/>
+      <c r="I132" s="2"/>
+      <c r="J132" s="4"/>
+    </row>
+    <row r="133" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>97</v>
       </c>
@@ -4201,9 +4477,11 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
-      <c r="H133" s="4"/>
-    </row>
-    <row r="134" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="4"/>
+    </row>
+    <row r="134" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>99</v>
       </c>
@@ -4215,9 +4493,11 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
-      <c r="H134" s="4"/>
-    </row>
-    <row r="135" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="4"/>
+    </row>
+    <row r="135" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>101</v>
       </c>
@@ -4229,9 +4509,11 @@
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
-      <c r="H135" s="4"/>
-    </row>
-    <row r="136" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H135" s="2"/>
+      <c r="I135" s="2"/>
+      <c r="J135" s="4"/>
+    </row>
+    <row r="136" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>103</v>
       </c>
@@ -4243,23 +4525,27 @@
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
-      <c r="H136" s="4"/>
-    </row>
-    <row r="137" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="15" t="s">
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="4"/>
+    </row>
+    <row r="137" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B137" s="16"/>
-      <c r="C137" s="16"/>
-      <c r="D137" s="16"/>
-      <c r="E137" s="16"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-      <c r="H137" s="4" t="s">
+      <c r="B137" s="18"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="18"/>
+      <c r="E137" s="18"/>
+      <c r="F137" s="14"/>
+      <c r="G137" s="14"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>106</v>
       </c>
@@ -4271,9 +4557,11 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
-      <c r="H138" s="4"/>
-    </row>
-    <row r="139" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="4"/>
+    </row>
+    <row r="139" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>108</v>
       </c>
@@ -4285,23 +4573,27 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
-      <c r="H139" s="4"/>
-    </row>
-    <row r="140" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15" t="s">
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="4"/>
+    </row>
+    <row r="140" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B140" s="16"/>
-      <c r="C140" s="16"/>
-      <c r="D140" s="16"/>
-      <c r="E140" s="16"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="4" t="s">
+      <c r="B140" s="18"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="14"/>
+      <c r="G140" s="14"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
+      <c r="J140" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>30</v>
       </c>
@@ -4313,9 +4605,11 @@
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
-      <c r="H141" s="4"/>
-    </row>
-    <row r="142" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
+      <c r="J141" s="4"/>
+    </row>
+    <row r="142" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>32</v>
       </c>
@@ -4327,9 +4621,11 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
-      <c r="H142" s="4"/>
-    </row>
-    <row r="143" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
+      <c r="J142" s="4"/>
+    </row>
+    <row r="143" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>34</v>
       </c>
@@ -4341,9 +4637,11 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
-      <c r="H143" s="4"/>
-    </row>
-    <row r="144" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
+      <c r="J143" s="4"/>
+    </row>
+    <row r="144" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>36</v>
       </c>
@@ -4355,9 +4653,11 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
-      <c r="H144" s="4"/>
-    </row>
-    <row r="145" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H144" s="2"/>
+      <c r="I144" s="2"/>
+      <c r="J144" s="4"/>
+    </row>
+    <row r="145" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>38</v>
       </c>
@@ -4369,9 +4669,11 @@
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
-      <c r="H145" s="4"/>
-    </row>
-    <row r="146" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H145" s="2"/>
+      <c r="I145" s="2"/>
+      <c r="J145" s="4"/>
+    </row>
+    <row r="146" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>40</v>
       </c>
@@ -4383,9 +4685,11 @@
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
-      <c r="H146" s="4"/>
-    </row>
-    <row r="147" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H146" s="2"/>
+      <c r="I146" s="2"/>
+      <c r="J146" s="4"/>
+    </row>
+    <row r="147" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>42</v>
       </c>
@@ -4397,9 +4701,11 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
-      <c r="H147" s="4"/>
-    </row>
-    <row r="148" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H147" s="2"/>
+      <c r="I147" s="2"/>
+      <c r="J147" s="4"/>
+    </row>
+    <row r="148" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>44</v>
       </c>
@@ -4411,9 +4717,11 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
-      <c r="H148" s="4"/>
-    </row>
-    <row r="149" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H148" s="2"/>
+      <c r="I148" s="2"/>
+      <c r="J148" s="4"/>
+    </row>
+    <row r="149" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>46</v>
       </c>
@@ -4425,9 +4733,11 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
-      <c r="H149" s="4"/>
-    </row>
-    <row r="150" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H149" s="2"/>
+      <c r="I149" s="2"/>
+      <c r="J149" s="4"/>
+    </row>
+    <row r="150" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>48</v>
       </c>
@@ -4439,9 +4749,11 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
-      <c r="H150" s="4"/>
-    </row>
-    <row r="151" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H150" s="2"/>
+      <c r="I150" s="2"/>
+      <c r="J150" s="4"/>
+    </row>
+    <row r="151" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>50</v>
       </c>
@@ -4453,9 +4765,11 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
-      <c r="H151" s="4"/>
-    </row>
-    <row r="152" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H151" s="2"/>
+      <c r="I151" s="2"/>
+      <c r="J151" s="4"/>
+    </row>
+    <row r="152" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>52</v>
       </c>
@@ -4467,9 +4781,11 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-      <c r="H152" s="4"/>
-    </row>
-    <row r="153" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H152" s="2"/>
+      <c r="I152" s="2"/>
+      <c r="J152" s="4"/>
+    </row>
+    <row r="153" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>54</v>
       </c>
@@ -4481,9 +4797,11 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
-      <c r="H153" s="4"/>
-    </row>
-    <row r="154" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H153" s="2"/>
+      <c r="I153" s="2"/>
+      <c r="J153" s="4"/>
+    </row>
+    <row r="154" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>56</v>
       </c>
@@ -4495,9 +4813,11 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
-      <c r="H154" s="4"/>
-    </row>
-    <row r="155" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H154" s="2"/>
+      <c r="I154" s="2"/>
+      <c r="J154" s="4"/>
+    </row>
+    <row r="155" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>58</v>
       </c>
@@ -4509,9 +4829,11 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
-      <c r="H155" s="4"/>
-    </row>
-    <row r="156" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H155" s="2"/>
+      <c r="I155" s="2"/>
+      <c r="J155" s="4"/>
+    </row>
+    <row r="156" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>60</v>
       </c>
@@ -4523,9 +4845,11 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-      <c r="H156" s="4"/>
-    </row>
-    <row r="157" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H156" s="2"/>
+      <c r="I156" s="2"/>
+      <c r="J156" s="4"/>
+    </row>
+    <row r="157" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>62</v>
       </c>
@@ -4537,9 +4861,11 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
-      <c r="H157" s="4"/>
-    </row>
-    <row r="158" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H157" s="2"/>
+      <c r="I157" s="2"/>
+      <c r="J157" s="4"/>
+    </row>
+    <row r="158" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>64</v>
       </c>
@@ -4551,9 +4877,11 @@
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-      <c r="H158" s="4"/>
-    </row>
-    <row r="159" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H158" s="2"/>
+      <c r="I158" s="2"/>
+      <c r="J158" s="4"/>
+    </row>
+    <row r="159" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>66</v>
       </c>
@@ -4565,9 +4893,11 @@
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
-      <c r="H159" s="4"/>
-    </row>
-    <row r="160" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H159" s="2"/>
+      <c r="I159" s="2"/>
+      <c r="J159" s="4"/>
+    </row>
+    <row r="160" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>68</v>
       </c>
@@ -4579,9 +4909,11 @@
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
-      <c r="H160" s="4"/>
-    </row>
-    <row r="161" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H160" s="2"/>
+      <c r="I160" s="2"/>
+      <c r="J160" s="4"/>
+    </row>
+    <row r="161" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>70</v>
       </c>
@@ -4593,9 +4925,11 @@
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
-      <c r="H161" s="4"/>
-    </row>
-    <row r="162" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H161" s="2"/>
+      <c r="I161" s="2"/>
+      <c r="J161" s="4"/>
+    </row>
+    <row r="162" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>72</v>
       </c>
@@ -4607,9 +4941,11 @@
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
-      <c r="H162" s="4"/>
-    </row>
-    <row r="163" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H162" s="2"/>
+      <c r="I162" s="2"/>
+      <c r="J162" s="4"/>
+    </row>
+    <row r="163" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>74</v>
       </c>
@@ -4621,9 +4957,11 @@
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
-      <c r="H163" s="4"/>
-    </row>
-    <row r="164" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H163" s="2"/>
+      <c r="I163" s="2"/>
+      <c r="J163" s="4"/>
+    </row>
+    <row r="164" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>76</v>
       </c>
@@ -4635,9 +4973,11 @@
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
-      <c r="H164" s="4"/>
-    </row>
-    <row r="165" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H164" s="2"/>
+      <c r="I164" s="2"/>
+      <c r="J164" s="4"/>
+    </row>
+    <row r="165" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>78</v>
       </c>
@@ -4649,9 +4989,11 @@
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
-      <c r="H165" s="4"/>
-    </row>
-    <row r="166" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H165" s="2"/>
+      <c r="I165" s="2"/>
+      <c r="J165" s="4"/>
+    </row>
+    <row r="166" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>80</v>
       </c>
@@ -4663,9 +5005,11 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
-      <c r="H166" s="4"/>
-    </row>
-    <row r="167" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H166" s="2"/>
+      <c r="I166" s="2"/>
+      <c r="J166" s="4"/>
+    </row>
+    <row r="167" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>82</v>
       </c>
@@ -4677,9 +5021,11 @@
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
-      <c r="H167" s="4"/>
-    </row>
-    <row r="168" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H167" s="2"/>
+      <c r="I167" s="2"/>
+      <c r="J167" s="4"/>
+    </row>
+    <row r="168" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>84</v>
       </c>
@@ -4691,9 +5037,11 @@
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
-      <c r="H168" s="4"/>
-    </row>
-    <row r="169" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H168" s="2"/>
+      <c r="I168" s="2"/>
+      <c r="J168" s="4"/>
+    </row>
+    <row r="169" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>86</v>
       </c>
@@ -4705,9 +5053,11 @@
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
-      <c r="H169" s="4"/>
-    </row>
-    <row r="170" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H169" s="2"/>
+      <c r="I169" s="2"/>
+      <c r="J169" s="4"/>
+    </row>
+    <row r="170" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>88</v>
       </c>
@@ -4719,9 +5069,11 @@
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
-      <c r="H170" s="4"/>
-    </row>
-    <row r="171" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H170" s="2"/>
+      <c r="I170" s="2"/>
+      <c r="J170" s="4"/>
+    </row>
+    <row r="171" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>90</v>
       </c>
@@ -4733,9 +5085,11 @@
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
-      <c r="H171" s="4"/>
-    </row>
-    <row r="172" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H171" s="2"/>
+      <c r="I171" s="2"/>
+      <c r="J171" s="4"/>
+    </row>
+    <row r="172" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>92</v>
       </c>
@@ -4747,23 +5101,27 @@
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
-      <c r="H172" s="4"/>
-    </row>
-    <row r="173" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="15" t="s">
+      <c r="H172" s="2"/>
+      <c r="I172" s="2"/>
+      <c r="J172" s="4"/>
+    </row>
+    <row r="173" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B173" s="16"/>
-      <c r="C173" s="16"/>
-      <c r="D173" s="16"/>
-      <c r="E173" s="16"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="4" t="s">
+      <c r="B173" s="18"/>
+      <c r="C173" s="18"/>
+      <c r="D173" s="18"/>
+      <c r="E173" s="18"/>
+      <c r="F173" s="14"/>
+      <c r="G173" s="14"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2"/>
+      <c r="J173" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>165</v>
       </c>
@@ -4775,9 +5133,11 @@
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
-      <c r="H174" s="4"/>
-    </row>
-    <row r="175" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="4"/>
+    </row>
+    <row r="175" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>167</v>
       </c>
@@ -4789,10 +5149,12 @@
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
-      <c r="H175" s="4"/>
-    </row>
-    <row r="176" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="21">
+      <c r="H175" s="2"/>
+      <c r="I175" s="2"/>
+      <c r="J175" s="4"/>
+    </row>
+    <row r="176" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="16">
         <v>1120</v>
       </c>
       <c r="B176" s="2" t="s">
@@ -4803,9 +5165,11 @@
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
-      <c r="H176" s="4"/>
-    </row>
-    <row r="177" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H176" s="2"/>
+      <c r="I176" s="2"/>
+      <c r="J176" s="4"/>
+    </row>
+    <row r="177" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>169</v>
       </c>
@@ -4817,9 +5181,11 @@
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
-      <c r="H177" s="4"/>
-    </row>
-    <row r="178" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H177" s="2"/>
+      <c r="I177" s="2"/>
+      <c r="J177" s="4"/>
+    </row>
+    <row r="178" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>171</v>
       </c>
@@ -4831,9 +5197,11 @@
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
-      <c r="H178" s="4"/>
-    </row>
-    <row r="179" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
+      <c r="J178" s="4"/>
+    </row>
+    <row r="179" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>173</v>
       </c>
@@ -4845,9 +5213,11 @@
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
-      <c r="H179" s="4"/>
-    </row>
-    <row r="180" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H179" s="2"/>
+      <c r="I179" s="2"/>
+      <c r="J179" s="4"/>
+    </row>
+    <row r="180" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>175</v>
       </c>
@@ -4859,9 +5229,11 @@
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
-      <c r="H180" s="4"/>
-    </row>
-    <row r="181" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H180" s="2"/>
+      <c r="I180" s="2"/>
+      <c r="J180" s="4"/>
+    </row>
+    <row r="181" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>177</v>
       </c>
@@ -4873,9 +5245,11 @@
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
-      <c r="H181" s="4"/>
-    </row>
-    <row r="182" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H181" s="2"/>
+      <c r="I181" s="2"/>
+      <c r="J181" s="4"/>
+    </row>
+    <row r="182" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>179</v>
       </c>
@@ -4887,9 +5261,11 @@
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
-      <c r="H182" s="4"/>
-    </row>
-    <row r="183" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H182" s="2"/>
+      <c r="I182" s="2"/>
+      <c r="J182" s="4"/>
+    </row>
+    <row r="183" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>181</v>
       </c>
@@ -4901,9 +5277,11 @@
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
-      <c r="H183" s="4"/>
-    </row>
-    <row r="184" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H183" s="2"/>
+      <c r="I183" s="2"/>
+      <c r="J183" s="4"/>
+    </row>
+    <row r="184" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>183</v>
       </c>
@@ -4915,9 +5293,11 @@
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
-      <c r="H184" s="4"/>
-    </row>
-    <row r="185" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H184" s="2"/>
+      <c r="I184" s="2"/>
+      <c r="J184" s="4"/>
+    </row>
+    <row r="185" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>185</v>
       </c>
@@ -4929,9 +5309,11 @@
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
-      <c r="H185" s="4"/>
-    </row>
-    <row r="186" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H185" s="2"/>
+      <c r="I185" s="2"/>
+      <c r="J185" s="4"/>
+    </row>
+    <row r="186" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>187</v>
       </c>
@@ -4943,9 +5325,11 @@
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
-      <c r="H186" s="4"/>
-    </row>
-    <row r="187" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H186" s="2"/>
+      <c r="I186" s="2"/>
+      <c r="J186" s="4"/>
+    </row>
+    <row r="187" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>189</v>
       </c>
@@ -4957,9 +5341,11 @@
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
-      <c r="H187" s="4"/>
-    </row>
-    <row r="188" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H187" s="2"/>
+      <c r="I187" s="2"/>
+      <c r="J187" s="4"/>
+    </row>
+    <row r="188" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>191</v>
       </c>
@@ -4971,9 +5357,11 @@
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
-      <c r="H188" s="4"/>
-    </row>
-    <row r="189" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H188" s="2"/>
+      <c r="I188" s="2"/>
+      <c r="J188" s="4"/>
+    </row>
+    <row r="189" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>193</v>
       </c>
@@ -4985,9 +5373,11 @@
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
-      <c r="H189" s="4"/>
-    </row>
-    <row r="190" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H189" s="2"/>
+      <c r="I189" s="2"/>
+      <c r="J189" s="4"/>
+    </row>
+    <row r="190" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>195</v>
       </c>
@@ -4999,9 +5389,11 @@
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
-      <c r="H190" s="4"/>
-    </row>
-    <row r="191" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H190" s="2"/>
+      <c r="I190" s="2"/>
+      <c r="J190" s="4"/>
+    </row>
+    <row r="191" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>197</v>
       </c>
@@ -5013,9 +5405,11 @@
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
-      <c r="H191" s="4"/>
-    </row>
-    <row r="192" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H191" s="2"/>
+      <c r="I191" s="2"/>
+      <c r="J191" s="4"/>
+    </row>
+    <row r="192" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>199</v>
       </c>
@@ -5027,9 +5421,11 @@
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
-      <c r="H192" s="4"/>
-    </row>
-    <row r="193" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H192" s="2"/>
+      <c r="I192" s="2"/>
+      <c r="J192" s="4"/>
+    </row>
+    <row r="193" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>201</v>
       </c>
@@ -5041,9 +5437,11 @@
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
-      <c r="H193" s="4"/>
-    </row>
-    <row r="194" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H193" s="2"/>
+      <c r="I193" s="2"/>
+      <c r="J193" s="4"/>
+    </row>
+    <row r="194" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>203</v>
       </c>
@@ -5055,9 +5453,11 @@
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
-      <c r="H194" s="4"/>
-    </row>
-    <row r="195" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H194" s="2"/>
+      <c r="I194" s="2"/>
+      <c r="J194" s="4"/>
+    </row>
+    <row r="195" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>205</v>
       </c>
@@ -5069,9 +5469,11 @@
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
-      <c r="H195" s="4"/>
-    </row>
-    <row r="196" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H195" s="2"/>
+      <c r="I195" s="2"/>
+      <c r="J195" s="4"/>
+    </row>
+    <row r="196" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>207</v>
       </c>
@@ -5083,9 +5485,11 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
-      <c r="H196" s="4"/>
-    </row>
-    <row r="197" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H196" s="2"/>
+      <c r="I196" s="2"/>
+      <c r="J196" s="4"/>
+    </row>
+    <row r="197" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>209</v>
       </c>
@@ -5097,9 +5501,11 @@
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
-      <c r="H197" s="4"/>
-    </row>
-    <row r="198" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
+      <c r="J197" s="4"/>
+    </row>
+    <row r="198" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>211</v>
       </c>
@@ -5111,9 +5517,11 @@
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
-      <c r="H198" s="4"/>
-    </row>
-    <row r="199" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H198" s="2"/>
+      <c r="I198" s="2"/>
+      <c r="J198" s="4"/>
+    </row>
+    <row r="199" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>213</v>
       </c>
@@ -5125,9 +5533,11 @@
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
-      <c r="H199" s="4"/>
-    </row>
-    <row r="200" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H199" s="2"/>
+      <c r="I199" s="2"/>
+      <c r="J199" s="4"/>
+    </row>
+    <row r="200" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>215</v>
       </c>
@@ -5139,9 +5549,11 @@
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
-      <c r="H200" s="4"/>
-    </row>
-    <row r="201" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
+      <c r="J200" s="4"/>
+    </row>
+    <row r="201" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>217</v>
       </c>
@@ -5153,23 +5565,27 @@
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
-      <c r="H201" s="4"/>
-    </row>
-    <row r="202" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="15" t="s">
+      <c r="H201" s="2"/>
+      <c r="I201" s="2"/>
+      <c r="J201" s="4"/>
+    </row>
+    <row r="202" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="B202" s="16"/>
-      <c r="C202" s="16"/>
-      <c r="D202" s="16"/>
-      <c r="E202" s="16"/>
-      <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-      <c r="H202" s="4" t="s">
+      <c r="B202" s="18"/>
+      <c r="C202" s="18"/>
+      <c r="D202" s="18"/>
+      <c r="E202" s="18"/>
+      <c r="F202" s="14"/>
+      <c r="G202" s="14"/>
+      <c r="H202" s="2"/>
+      <c r="I202" s="2"/>
+      <c r="J202" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>220</v>
       </c>
@@ -5181,9 +5597,11 @@
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
-      <c r="H203" s="4"/>
-    </row>
-    <row r="204" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H203" s="2"/>
+      <c r="I203" s="2"/>
+      <c r="J203" s="4"/>
+    </row>
+    <row r="204" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>222</v>
       </c>
@@ -5195,9 +5613,11 @@
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
-      <c r="H204" s="4"/>
-    </row>
-    <row r="205" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H204" s="2"/>
+      <c r="I204" s="2"/>
+      <c r="J204" s="4"/>
+    </row>
+    <row r="205" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>224</v>
       </c>
@@ -5209,9 +5629,11 @@
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
-      <c r="H205" s="4"/>
-    </row>
-    <row r="206" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H205" s="2"/>
+      <c r="I205" s="2"/>
+      <c r="J205" s="4"/>
+    </row>
+    <row r="206" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>226</v>
       </c>
@@ -5223,9 +5645,11 @@
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
-      <c r="H206" s="4"/>
-    </row>
-    <row r="207" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H206" s="2"/>
+      <c r="I206" s="2"/>
+      <c r="J206" s="4"/>
+    </row>
+    <row r="207" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>228</v>
       </c>
@@ -5237,9 +5661,11 @@
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
-      <c r="H207" s="4"/>
-    </row>
-    <row r="208" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H207" s="2"/>
+      <c r="I207" s="2"/>
+      <c r="J207" s="4"/>
+    </row>
+    <row r="208" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>230</v>
       </c>
@@ -5251,9 +5677,11 @@
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
-      <c r="H208" s="4"/>
-    </row>
-    <row r="209" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H208" s="2"/>
+      <c r="I208" s="2"/>
+      <c r="J208" s="4"/>
+    </row>
+    <row r="209" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>232</v>
       </c>
@@ -5265,9 +5693,11 @@
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
-      <c r="H209" s="4"/>
-    </row>
-    <row r="210" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H209" s="2"/>
+      <c r="I209" s="2"/>
+      <c r="J209" s="4"/>
+    </row>
+    <row r="210" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>234</v>
       </c>
@@ -5279,9 +5709,11 @@
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
-      <c r="H210" s="4"/>
-    </row>
-    <row r="211" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H210" s="2"/>
+      <c r="I210" s="2"/>
+      <c r="J210" s="4"/>
+    </row>
+    <row r="211" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>236</v>
       </c>
@@ -5293,9 +5725,11 @@
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
-      <c r="H211" s="4"/>
-    </row>
-    <row r="212" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H211" s="2"/>
+      <c r="I211" s="2"/>
+      <c r="J211" s="4"/>
+    </row>
+    <row r="212" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>238</v>
       </c>
@@ -5307,9 +5741,11 @@
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
-      <c r="H212" s="4"/>
-    </row>
-    <row r="213" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
+      <c r="J212" s="4"/>
+    </row>
+    <row r="213" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>240</v>
       </c>
@@ -5321,9 +5757,11 @@
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
-      <c r="H213" s="4"/>
-    </row>
-    <row r="214" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H213" s="2"/>
+      <c r="I213" s="2"/>
+      <c r="J213" s="4"/>
+    </row>
+    <row r="214" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>242</v>
       </c>
@@ -5335,9 +5773,11 @@
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
-      <c r="H214" s="4"/>
-    </row>
-    <row r="215" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
+      <c r="J214" s="4"/>
+    </row>
+    <row r="215" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>244</v>
       </c>
@@ -5349,9 +5789,11 @@
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
-      <c r="H215" s="4"/>
-    </row>
-    <row r="216" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="4"/>
+    </row>
+    <row r="216" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>246</v>
       </c>
@@ -5363,9 +5805,11 @@
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
-      <c r="H216" s="4"/>
-    </row>
-    <row r="217" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+      <c r="J216" s="4"/>
+    </row>
+    <row r="217" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>248</v>
       </c>
@@ -5377,9 +5821,11 @@
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
-      <c r="H217" s="4"/>
-    </row>
-    <row r="218" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+      <c r="J217" s="4"/>
+    </row>
+    <row r="218" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>250</v>
       </c>
@@ -5391,9 +5837,11 @@
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
-      <c r="H218" s="4"/>
-    </row>
-    <row r="219" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+      <c r="J218" s="4"/>
+    </row>
+    <row r="219" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>252</v>
       </c>
@@ -5405,9 +5853,11 @@
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
-      <c r="H219" s="4"/>
-    </row>
-    <row r="220" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+      <c r="J219" s="4"/>
+    </row>
+    <row r="220" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>254</v>
       </c>
@@ -5419,9 +5869,11 @@
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
-      <c r="H220" s="4"/>
-    </row>
-    <row r="221" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="4"/>
+    </row>
+    <row r="221" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>256</v>
       </c>
@@ -5433,9 +5885,11 @@
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
-      <c r="H221" s="4"/>
-    </row>
-    <row r="222" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="4"/>
+    </row>
+    <row r="222" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>258</v>
       </c>
@@ -5447,23 +5901,27 @@
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
-      <c r="H222" s="4"/>
-    </row>
-    <row r="223" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="15" t="s">
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="4"/>
+    </row>
+    <row r="223" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="B223" s="16"/>
-      <c r="C223" s="16"/>
-      <c r="D223" s="16"/>
-      <c r="E223" s="16"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-      <c r="H223" s="4" t="s">
+      <c r="B223" s="18"/>
+      <c r="C223" s="18"/>
+      <c r="D223" s="18"/>
+      <c r="E223" s="18"/>
+      <c r="F223" s="14"/>
+      <c r="G223" s="14"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>495</v>
       </c>
@@ -5475,9 +5933,11 @@
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
-      <c r="H224" s="4"/>
-    </row>
-    <row r="225" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+      <c r="J224" s="4"/>
+    </row>
+    <row r="225" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>497</v>
       </c>
@@ -5489,9 +5949,11 @@
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
-      <c r="H225" s="4"/>
-    </row>
-    <row r="226" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H225" s="2"/>
+      <c r="I225" s="2"/>
+      <c r="J225" s="4"/>
+    </row>
+    <row r="226" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>499</v>
       </c>
@@ -5503,9 +5965,11 @@
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
-      <c r="H226" s="4"/>
-    </row>
-    <row r="227" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H226" s="2"/>
+      <c r="I226" s="2"/>
+      <c r="J226" s="4"/>
+    </row>
+    <row r="227" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>501</v>
       </c>
@@ -5517,9 +5981,11 @@
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
-      <c r="H227" s="4"/>
-    </row>
-    <row r="228" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H227" s="2"/>
+      <c r="I227" s="2"/>
+      <c r="J227" s="4"/>
+    </row>
+    <row r="228" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>503</v>
       </c>
@@ -5531,9 +5997,11 @@
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
-      <c r="H228" s="4"/>
-    </row>
-    <row r="229" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H228" s="2"/>
+      <c r="I228" s="2"/>
+      <c r="J228" s="4"/>
+    </row>
+    <row r="229" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>505</v>
       </c>
@@ -5545,9 +6013,11 @@
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
-      <c r="H229" s="4"/>
-    </row>
-    <row r="230" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H229" s="2"/>
+      <c r="I229" s="2"/>
+      <c r="J229" s="4"/>
+    </row>
+    <row r="230" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>507</v>
       </c>
@@ -5559,9 +6029,11 @@
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
-      <c r="H230" s="4"/>
-    </row>
-    <row r="231" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H230" s="2"/>
+      <c r="I230" s="2"/>
+      <c r="J230" s="4"/>
+    </row>
+    <row r="231" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>509</v>
       </c>
@@ -5573,9 +6045,11 @@
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
-      <c r="H231" s="4"/>
-    </row>
-    <row r="232" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H231" s="2"/>
+      <c r="I231" s="2"/>
+      <c r="J231" s="4"/>
+    </row>
+    <row r="232" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>511</v>
       </c>
@@ -5587,9 +6061,11 @@
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
-      <c r="H232" s="4"/>
-    </row>
-    <row r="233" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H232" s="2"/>
+      <c r="I232" s="2"/>
+      <c r="J232" s="4"/>
+    </row>
+    <row r="233" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>513</v>
       </c>
@@ -5601,9 +6077,11 @@
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
-      <c r="H233" s="4"/>
-    </row>
-    <row r="234" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H233" s="2"/>
+      <c r="I233" s="2"/>
+      <c r="J233" s="4"/>
+    </row>
+    <row r="234" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>515</v>
       </c>
@@ -5615,9 +6093,11 @@
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
-      <c r="H234" s="4"/>
-    </row>
-    <row r="235" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H234" s="2"/>
+      <c r="I234" s="2"/>
+      <c r="J234" s="4"/>
+    </row>
+    <row r="235" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>517</v>
       </c>
@@ -5629,9 +6109,11 @@
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
-      <c r="H235" s="4"/>
-    </row>
-    <row r="236" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H235" s="2"/>
+      <c r="I235" s="2"/>
+      <c r="J235" s="4"/>
+    </row>
+    <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>519</v>
       </c>
@@ -5643,9 +6125,11 @@
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
-      <c r="H236" s="4"/>
-    </row>
-    <row r="237" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H236" s="2"/>
+      <c r="I236" s="2"/>
+      <c r="J236" s="4"/>
+    </row>
+    <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>521</v>
       </c>
@@ -5657,9 +6141,11 @@
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
-      <c r="H237" s="4"/>
-    </row>
-    <row r="238" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H237" s="2"/>
+      <c r="I237" s="2"/>
+      <c r="J237" s="4"/>
+    </row>
+    <row r="238" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>523</v>
       </c>
@@ -5671,9 +6157,11 @@
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
-      <c r="H238" s="4"/>
-    </row>
-    <row r="239" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H238" s="2"/>
+      <c r="I238" s="2"/>
+      <c r="J238" s="4"/>
+    </row>
+    <row r="239" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>525</v>
       </c>
@@ -5685,9 +6173,11 @@
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
-      <c r="H239" s="4"/>
-    </row>
-    <row r="240" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+      <c r="J239" s="4"/>
+    </row>
+    <row r="240" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>527</v>
       </c>
@@ -5699,9 +6189,11 @@
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
-      <c r="H240" s="4"/>
-    </row>
-    <row r="241" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H240" s="2"/>
+      <c r="I240" s="2"/>
+      <c r="J240" s="4"/>
+    </row>
+    <row r="241" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>529</v>
       </c>
@@ -5713,9 +6205,11 @@
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
-      <c r="H241" s="4"/>
-    </row>
-    <row r="242" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H241" s="2"/>
+      <c r="I241" s="2"/>
+      <c r="J241" s="4"/>
+    </row>
+    <row r="242" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>531</v>
       </c>
@@ -5727,9 +6221,11 @@
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
-      <c r="H242" s="4"/>
-    </row>
-    <row r="243" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H242" s="2"/>
+      <c r="I242" s="2"/>
+      <c r="J242" s="4"/>
+    </row>
+    <row r="243" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>533</v>
       </c>
@@ -5741,23 +6237,27 @@
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
-      <c r="H243" s="4"/>
-    </row>
-    <row r="244" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="15" t="s">
+      <c r="H243" s="2"/>
+      <c r="I243" s="2"/>
+      <c r="J243" s="4"/>
+    </row>
+    <row r="244" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="17" t="s">
         <v>535</v>
       </c>
-      <c r="B244" s="16"/>
-      <c r="C244" s="16"/>
-      <c r="D244" s="16"/>
-      <c r="E244" s="16"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="2"/>
-      <c r="H244" s="4" t="s">
+      <c r="B244" s="18"/>
+      <c r="C244" s="18"/>
+      <c r="D244" s="18"/>
+      <c r="E244" s="18"/>
+      <c r="F244" s="14"/>
+      <c r="G244" s="14"/>
+      <c r="H244" s="2"/>
+      <c r="I244" s="2"/>
+      <c r="J244" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>261</v>
       </c>
@@ -5769,9 +6269,11 @@
       <c r="E245" s="2"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
-      <c r="H245" s="4"/>
-    </row>
-    <row r="246" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H245" s="2"/>
+      <c r="I245" s="2"/>
+      <c r="J245" s="4"/>
+    </row>
+    <row r="246" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>263</v>
       </c>
@@ -5783,9 +6285,11 @@
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
-      <c r="H246" s="4"/>
-    </row>
-    <row r="247" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H246" s="2"/>
+      <c r="I246" s="2"/>
+      <c r="J246" s="4"/>
+    </row>
+    <row r="247" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>265</v>
       </c>
@@ -5797,9 +6301,11 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
-      <c r="H247" s="4"/>
-    </row>
-    <row r="248" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H247" s="2"/>
+      <c r="I247" s="2"/>
+      <c r="J247" s="4"/>
+    </row>
+    <row r="248" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>267</v>
       </c>
@@ -5811,9 +6317,11 @@
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
-      <c r="H248" s="4"/>
-    </row>
-    <row r="249" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H248" s="2"/>
+      <c r="I248" s="2"/>
+      <c r="J248" s="4"/>
+    </row>
+    <row r="249" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>269</v>
       </c>
@@ -5825,9 +6333,11 @@
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
-      <c r="H249" s="4"/>
-    </row>
-    <row r="250" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H249" s="2"/>
+      <c r="I249" s="2"/>
+      <c r="J249" s="4"/>
+    </row>
+    <row r="250" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
         <v>271</v>
       </c>
@@ -5839,9 +6349,11 @@
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
-      <c r="H250" s="4"/>
-    </row>
-    <row r="251" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H250" s="2"/>
+      <c r="I250" s="2"/>
+      <c r="J250" s="4"/>
+    </row>
+    <row r="251" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>273</v>
       </c>
@@ -5853,9 +6365,11 @@
       <c r="E251" s="2"/>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
-      <c r="H251" s="4"/>
-    </row>
-    <row r="252" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H251" s="2"/>
+      <c r="I251" s="2"/>
+      <c r="J251" s="4"/>
+    </row>
+    <row r="252" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
         <v>275</v>
       </c>
@@ -5867,9 +6381,11 @@
       <c r="E252" s="2"/>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
-      <c r="H252" s="4"/>
-    </row>
-    <row r="253" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H252" s="2"/>
+      <c r="I252" s="2"/>
+      <c r="J252" s="4"/>
+    </row>
+    <row r="253" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>277</v>
       </c>
@@ -5881,9 +6397,11 @@
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
-      <c r="H253" s="4"/>
-    </row>
-    <row r="254" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H253" s="2"/>
+      <c r="I253" s="2"/>
+      <c r="J253" s="4"/>
+    </row>
+    <row r="254" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>279</v>
       </c>
@@ -5895,9 +6413,11 @@
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
-      <c r="H254" s="4"/>
-    </row>
-    <row r="255" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H254" s="2"/>
+      <c r="I254" s="2"/>
+      <c r="J254" s="4"/>
+    </row>
+    <row r="255" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>281</v>
       </c>
@@ -5909,9 +6429,11 @@
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
-      <c r="H255" s="4"/>
-    </row>
-    <row r="256" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H255" s="2"/>
+      <c r="I255" s="2"/>
+      <c r="J255" s="4"/>
+    </row>
+    <row r="256" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
         <v>283</v>
       </c>
@@ -5923,9 +6445,11 @@
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
-      <c r="H256" s="4"/>
-    </row>
-    <row r="257" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H256" s="2"/>
+      <c r="I256" s="2"/>
+      <c r="J256" s="4"/>
+    </row>
+    <row r="257" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>285</v>
       </c>
@@ -5937,9 +6461,11 @@
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
-      <c r="H257" s="4"/>
-    </row>
-    <row r="258" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H257" s="2"/>
+      <c r="I257" s="2"/>
+      <c r="J257" s="4"/>
+    </row>
+    <row r="258" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
         <v>287</v>
       </c>
@@ -5951,23 +6477,27 @@
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
-      <c r="H258" s="4"/>
-    </row>
-    <row r="259" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="15" t="s">
+      <c r="H258" s="2"/>
+      <c r="I258" s="2"/>
+      <c r="J258" s="4"/>
+    </row>
+    <row r="259" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="B259" s="16"/>
-      <c r="C259" s="16"/>
-      <c r="D259" s="16"/>
-      <c r="E259" s="16"/>
-      <c r="F259" s="2"/>
-      <c r="G259" s="2"/>
-      <c r="H259" s="4" t="s">
+      <c r="B259" s="18"/>
+      <c r="C259" s="18"/>
+      <c r="D259" s="18"/>
+      <c r="E259" s="18"/>
+      <c r="F259" s="14"/>
+      <c r="G259" s="14"/>
+      <c r="H259" s="2"/>
+      <c r="I259" s="2"/>
+      <c r="J259" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
         <v>447</v>
       </c>
@@ -5979,9 +6509,11 @@
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
-      <c r="H260" s="4"/>
-    </row>
-    <row r="261" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H260" s="2"/>
+      <c r="I260" s="2"/>
+      <c r="J260" s="4"/>
+    </row>
+    <row r="261" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
         <v>449</v>
       </c>
@@ -5993,9 +6525,11 @@
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
-      <c r="H261" s="4"/>
-    </row>
-    <row r="262" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H261" s="2"/>
+      <c r="I261" s="2"/>
+      <c r="J261" s="4"/>
+    </row>
+    <row r="262" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>451</v>
       </c>
@@ -6007,9 +6541,11 @@
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
-      <c r="H262" s="4"/>
-    </row>
-    <row r="263" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H262" s="2"/>
+      <c r="I262" s="2"/>
+      <c r="J262" s="4"/>
+    </row>
+    <row r="263" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
         <v>453</v>
       </c>
@@ -6021,9 +6557,11 @@
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
-      <c r="H263" s="4"/>
-    </row>
-    <row r="264" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H263" s="2"/>
+      <c r="I263" s="2"/>
+      <c r="J263" s="4"/>
+    </row>
+    <row r="264" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>455</v>
       </c>
@@ -6035,9 +6573,11 @@
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
-      <c r="H264" s="4"/>
-    </row>
-    <row r="265" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H264" s="2"/>
+      <c r="I264" s="2"/>
+      <c r="J264" s="4"/>
+    </row>
+    <row r="265" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
         <v>457</v>
       </c>
@@ -6049,9 +6589,11 @@
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
-      <c r="H265" s="4"/>
-    </row>
-    <row r="266" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H265" s="2"/>
+      <c r="I265" s="2"/>
+      <c r="J265" s="4"/>
+    </row>
+    <row r="266" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>459</v>
       </c>
@@ -6063,9 +6605,11 @@
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
-      <c r="H266" s="4"/>
-    </row>
-    <row r="267" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H266" s="2"/>
+      <c r="I266" s="2"/>
+      <c r="J266" s="4"/>
+    </row>
+    <row r="267" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
         <v>461</v>
       </c>
@@ -6077,9 +6621,11 @@
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
-      <c r="H267" s="4"/>
-    </row>
-    <row r="268" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H267" s="2"/>
+      <c r="I267" s="2"/>
+      <c r="J267" s="4"/>
+    </row>
+    <row r="268" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
         <v>463</v>
       </c>
@@ -6091,9 +6637,11 @@
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
-      <c r="H268" s="4"/>
-    </row>
-    <row r="269" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H268" s="2"/>
+      <c r="I268" s="2"/>
+      <c r="J268" s="4"/>
+    </row>
+    <row r="269" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>465</v>
       </c>
@@ -6105,9 +6653,11 @@
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
-      <c r="H269" s="4"/>
-    </row>
-    <row r="270" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H269" s="2"/>
+      <c r="I269" s="2"/>
+      <c r="J269" s="4"/>
+    </row>
+    <row r="270" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
         <v>467</v>
       </c>
@@ -6119,9 +6669,11 @@
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
-      <c r="H270" s="4"/>
-    </row>
-    <row r="271" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H270" s="2"/>
+      <c r="I270" s="2"/>
+      <c r="J270" s="4"/>
+    </row>
+    <row r="271" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
         <v>469</v>
       </c>
@@ -6133,9 +6685,11 @@
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
-      <c r="H271" s="4"/>
-    </row>
-    <row r="272" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H271" s="2"/>
+      <c r="I271" s="2"/>
+      <c r="J271" s="4"/>
+    </row>
+    <row r="272" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>471</v>
       </c>
@@ -6147,9 +6701,11 @@
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
-      <c r="H272" s="4"/>
-    </row>
-    <row r="273" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H272" s="2"/>
+      <c r="I272" s="2"/>
+      <c r="J272" s="4"/>
+    </row>
+    <row r="273" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
         <v>473</v>
       </c>
@@ -6161,9 +6717,11 @@
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
-      <c r="H273" s="4"/>
-    </row>
-    <row r="274" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H273" s="2"/>
+      <c r="I273" s="2"/>
+      <c r="J273" s="4"/>
+    </row>
+    <row r="274" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
         <v>475</v>
       </c>
@@ -6175,9 +6733,11 @@
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
-      <c r="H274" s="4"/>
-    </row>
-    <row r="275" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H274" s="2"/>
+      <c r="I274" s="2"/>
+      <c r="J274" s="4"/>
+    </row>
+    <row r="275" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
         <v>477</v>
       </c>
@@ -6189,9 +6749,11 @@
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
-      <c r="H275" s="4"/>
-    </row>
-    <row r="276" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H275" s="2"/>
+      <c r="I275" s="2"/>
+      <c r="J275" s="4"/>
+    </row>
+    <row r="276" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
         <v>479</v>
       </c>
@@ -6203,23 +6765,27 @@
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
-      <c r="H276" s="4"/>
-    </row>
-    <row r="277" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="15" t="s">
+      <c r="H276" s="2"/>
+      <c r="I276" s="2"/>
+      <c r="J276" s="4"/>
+    </row>
+    <row r="277" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="B277" s="16"/>
-      <c r="C277" s="16"/>
-      <c r="D277" s="16"/>
-      <c r="E277" s="16"/>
-      <c r="F277" s="2"/>
-      <c r="G277" s="2"/>
-      <c r="H277" s="4" t="s">
+      <c r="B277" s="18"/>
+      <c r="C277" s="18"/>
+      <c r="D277" s="18"/>
+      <c r="E277" s="18"/>
+      <c r="F277" s="14"/>
+      <c r="G277" s="14"/>
+      <c r="H277" s="2"/>
+      <c r="I277" s="2"/>
+      <c r="J277" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
         <v>482</v>
       </c>
@@ -6231,9 +6797,11 @@
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
-      <c r="H278" s="4"/>
-    </row>
-    <row r="279" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H278" s="2"/>
+      <c r="I278" s="2"/>
+      <c r="J278" s="4"/>
+    </row>
+    <row r="279" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
         <v>484</v>
       </c>
@@ -6245,9 +6813,11 @@
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
-      <c r="H279" s="4"/>
-    </row>
-    <row r="280" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H279" s="2"/>
+      <c r="I279" s="2"/>
+      <c r="J279" s="4"/>
+    </row>
+    <row r="280" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
         <v>486</v>
       </c>
@@ -6259,9 +6829,11 @@
       <c r="E280" s="2"/>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
-      <c r="H280" s="4"/>
-    </row>
-    <row r="281" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H280" s="2"/>
+      <c r="I280" s="2"/>
+      <c r="J280" s="4"/>
+    </row>
+    <row r="281" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
         <v>488</v>
       </c>
@@ -6273,9 +6845,11 @@
       <c r="E281" s="2"/>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
-      <c r="H281" s="4"/>
-    </row>
-    <row r="282" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H281" s="2"/>
+      <c r="I281" s="2"/>
+      <c r="J281" s="4"/>
+    </row>
+    <row r="282" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
         <v>490</v>
       </c>
@@ -6287,9 +6861,11 @@
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
-      <c r="H282" s="4"/>
-    </row>
-    <row r="283" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H282" s="2"/>
+      <c r="I282" s="2"/>
+      <c r="J282" s="4"/>
+    </row>
+    <row r="283" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
         <v>492</v>
       </c>
@@ -6301,23 +6877,27 @@
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
-      <c r="H283" s="4"/>
-    </row>
-    <row r="284" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="15" t="s">
+      <c r="H283" s="2"/>
+      <c r="I283" s="2"/>
+      <c r="J283" s="4"/>
+    </row>
+    <row r="284" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="B284" s="16"/>
-      <c r="C284" s="16"/>
-      <c r="D284" s="16"/>
-      <c r="E284" s="16"/>
-      <c r="F284" s="2"/>
-      <c r="G284" s="2"/>
-      <c r="H284" s="4" t="s">
+      <c r="B284" s="18"/>
+      <c r="C284" s="18"/>
+      <c r="D284" s="18"/>
+      <c r="E284" s="18"/>
+      <c r="F284" s="14"/>
+      <c r="G284" s="14"/>
+      <c r="H284" s="2"/>
+      <c r="I284" s="2"/>
+      <c r="J284" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="19" t="s">
         <v>542</v>
       </c>
@@ -6325,12 +6905,28 @@
       <c r="C285" s="20"/>
       <c r="D285" s="20"/>
       <c r="E285" s="20"/>
-      <c r="F285" s="5"/>
-      <c r="G285" s="5"/>
-      <c r="H285" s="6"/>
+      <c r="F285" s="15"/>
+      <c r="G285" s="15"/>
+      <c r="H285" s="5"/>
+      <c r="I285" s="5"/>
+      <c r="J285" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A173:E173"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A277:E277"/>
     <mergeCell ref="A284:E284"/>
     <mergeCell ref="A244:E244"/>
@@ -6338,26 +6934,12 @@
     <mergeCell ref="A202:E202"/>
     <mergeCell ref="A223:E223"/>
     <mergeCell ref="A259:E259"/>
-    <mergeCell ref="A2:H3"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A173:E173"/>
-    <mergeCell ref="A137:E137"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A131:E131"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A7:B21 D7:H7 B1 D1:H1 A141:B172 A22 H22 A173 H173 A177:B201 A203:B222 A202 H202 A245:B258 A223 H223 A259 H259 A260:B276 A278:B283 A277 A284 H284 H277 D4:H4 A174:B175" numberStoredAsText="1"/>
+    <ignoredError sqref="A7:B21 H7:J7 B1 H1:J1 A141:B172 A22 J22 A173 J173 A177:B201 A203:B222 A202 J202 A245:B258 A223 J223 A259 J259 A260:B276 A278:B283 A277 A284 J284 J277 H4:J4 A174:B175 D4:E4 D1:E1 D7:E7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/temp1.xlsx
+++ b/data/temp1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E64146-9B11-485A-9C52-D339A2EF8F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA0AF54-6726-44E0-AD6C-11AF0BB8FFD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="국내생산 계획" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="551">
   <si>
     <t/>
   </si>
@@ -34,1652 +34,1920 @@
     <t>규격</t>
   </si>
   <si>
-    <t>15875</t>
-  </si>
-  <si>
     <t>YS APBL22-AL22RF G</t>
   </si>
   <si>
-    <t>15874</t>
-  </si>
-  <si>
     <t>YS APBL22-AL22RF R</t>
   </si>
   <si>
-    <t>15876</t>
-  </si>
-  <si>
     <t>YS APBL22-AL22RF Y</t>
   </si>
   <si>
-    <t>15305</t>
-  </si>
-  <si>
     <t>YS APBL22-DL24RF</t>
   </si>
   <si>
-    <t>15878</t>
-  </si>
-  <si>
     <t>YS APL22-AL22 RH G</t>
   </si>
   <si>
-    <t>15877</t>
-  </si>
-  <si>
     <t>YS APL22-AL22 RH R</t>
   </si>
   <si>
-    <t>15879</t>
-  </si>
-  <si>
     <t>YS APL22-AL22 RH Y</t>
   </si>
   <si>
-    <t>15524</t>
-  </si>
-  <si>
     <t>YS APL22-DL24 RH</t>
   </si>
   <si>
-    <t>9858</t>
-  </si>
-  <si>
     <t>YS P122-11RF</t>
   </si>
   <si>
-    <t>11619</t>
-  </si>
-  <si>
     <t>YS P222-11RF</t>
   </si>
   <si>
-    <t>1950</t>
-  </si>
-  <si>
     <t>YS R22-211K</t>
   </si>
   <si>
-    <t>1937</t>
-  </si>
-  <si>
     <t>YS R22-211L</t>
   </si>
   <si>
-    <t>958</t>
-  </si>
-  <si>
     <t>YS SP322-11</t>
   </si>
   <si>
     <t>22파이</t>
   </si>
   <si>
-    <t>22609</t>
-  </si>
-  <si>
     <t>YS BP12-11 B</t>
   </si>
   <si>
-    <t>22610</t>
-  </si>
-  <si>
     <t>YS BP12-11 G</t>
   </si>
   <si>
-    <t>16954</t>
-  </si>
-  <si>
     <t>YS BP12-11 R</t>
   </si>
   <si>
-    <t>16955</t>
-  </si>
-  <si>
     <t>YS BP12-22</t>
   </si>
   <si>
-    <t>16957</t>
-  </si>
-  <si>
     <t>YS BPBL2-O06A</t>
   </si>
   <si>
-    <t>17399</t>
-  </si>
-  <si>
     <t>YS BPBL2-AL11 Y</t>
   </si>
   <si>
-    <t>17431</t>
-  </si>
-  <si>
     <t>YS BPBL2-AL12 Y</t>
   </si>
   <si>
-    <t>17441</t>
-  </si>
-  <si>
     <t>YS BPBL2-AL22 G</t>
   </si>
   <si>
-    <t>16977</t>
-  </si>
-  <si>
     <t>YS BPBL2-AL22 R</t>
   </si>
   <si>
-    <t>17442</t>
-  </si>
-  <si>
     <t>YS BPBL2-AL22 Y</t>
   </si>
   <si>
-    <t>17530</t>
-  </si>
-  <si>
     <t>YS BPBL2-AL06 G</t>
   </si>
   <si>
-    <t>17056</t>
-  </si>
-  <si>
     <t>YS BPL2-O24</t>
   </si>
   <si>
-    <t>16987</t>
-  </si>
-  <si>
     <t>YS BPL2-O06</t>
   </si>
   <si>
-    <t>16989</t>
-  </si>
-  <si>
     <t>YS BPL2-T11</t>
   </si>
   <si>
-    <t>16988</t>
-  </si>
-  <si>
     <t>YS BPL2-T22</t>
   </si>
   <si>
-    <t>16990</t>
-  </si>
-  <si>
     <t>YS BPL2-T44</t>
   </si>
   <si>
-    <t>17023</t>
-  </si>
-  <si>
     <t>YS BPL2-AL11 G</t>
   </si>
   <si>
-    <t>17022</t>
-  </si>
-  <si>
     <t>YS BPL2-AL11 R</t>
   </si>
   <si>
-    <t>17024</t>
-  </si>
-  <si>
     <t>YS BPL2-AL11 Y</t>
   </si>
   <si>
-    <t>17028</t>
-  </si>
-  <si>
     <t>YS BPL2-AL12 G</t>
   </si>
   <si>
-    <t>17027</t>
-  </si>
-  <si>
     <t>YS BPL2-AL12 R</t>
   </si>
   <si>
-    <t>17033</t>
-  </si>
-  <si>
     <t>YS BPL2-AL22 G</t>
   </si>
   <si>
-    <t>17032</t>
-  </si>
-  <si>
     <t>YS BPL2-AL22 R</t>
   </si>
   <si>
-    <t>17536</t>
-  </si>
-  <si>
     <t>YS BPL2-AL06 G</t>
   </si>
   <si>
-    <t>17535</t>
-  </si>
-  <si>
     <t>YS BPL2-AL06 R</t>
   </si>
   <si>
-    <t>17039</t>
-  </si>
-  <si>
     <t>YS BPL2-DL11 G</t>
   </si>
   <si>
-    <t>16985</t>
-  </si>
-  <si>
     <t>YS BPL2-DL11 R</t>
   </si>
   <si>
-    <t>17042</t>
-  </si>
-  <si>
     <t>YS BPL2-DL11 W</t>
   </si>
   <si>
-    <t>17040</t>
-  </si>
-  <si>
     <t>YS BPL2-DL11 Y</t>
   </si>
   <si>
-    <t>16959</t>
-  </si>
-  <si>
     <t>YS BR2-211K</t>
   </si>
   <si>
-    <t>16961</t>
-  </si>
-  <si>
     <t>YS BR2-222K</t>
   </si>
   <si>
-    <t>25956</t>
-  </si>
-  <si>
     <t>YS SPA22-11</t>
   </si>
   <si>
     <t>B TYPE</t>
   </si>
   <si>
-    <t>7091</t>
-  </si>
-  <si>
     <t>YS DNC3102-64AP10B(기본품)</t>
   </si>
   <si>
-    <t>6914</t>
-  </si>
-  <si>
     <t>YS DNC3102-C4RP10B (기본품)</t>
   </si>
   <si>
-    <t>6916</t>
-  </si>
-  <si>
     <t>YS DNC4213-64MR10B (기본품)</t>
   </si>
   <si>
-    <t>6915</t>
-  </si>
-  <si>
     <t>YS DNC4210-64MR10B (기본품)</t>
   </si>
   <si>
-    <t>6925</t>
-  </si>
-  <si>
     <t>YS DNC4307-64MR10B (기본품)</t>
   </si>
   <si>
     <t>CAM(기본)</t>
   </si>
   <si>
-    <t>19650</t>
-  </si>
-  <si>
     <t>YS 5C2207-29MKB</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>YS SC4301-1PMKWLR</t>
   </si>
   <si>
     <t>CAM(주문)</t>
   </si>
   <si>
-    <t>1032</t>
-  </si>
-  <si>
     <t>YS P12-15CG</t>
   </si>
   <si>
-    <t>1029</t>
-  </si>
-  <si>
     <t>YS P12-15CR</t>
   </si>
   <si>
-    <t>1030</t>
-  </si>
-  <si>
     <t>YS P12-15CN</t>
   </si>
   <si>
-    <t>1031</t>
-  </si>
-  <si>
     <t>YS P12-15CY</t>
   </si>
   <si>
-    <t>1026</t>
-  </si>
-  <si>
     <t>YS L2-15C</t>
   </si>
   <si>
-    <t>1027</t>
-  </si>
-  <si>
     <t>YS L3-15C</t>
   </si>
   <si>
-    <t>21785</t>
-  </si>
-  <si>
     <t>YS P-15C</t>
   </si>
   <si>
-    <t>1034</t>
-  </si>
-  <si>
     <t>YS P9S-15CR</t>
   </si>
   <si>
-    <t>1035</t>
-  </si>
-  <si>
     <t>YS P9S-15CN</t>
   </si>
   <si>
-    <t>1036</t>
-  </si>
-  <si>
     <t>YS P9S-15CY</t>
   </si>
   <si>
-    <t>18376</t>
-  </si>
-  <si>
     <t>YS R1-15C</t>
   </si>
   <si>
-    <t>21784</t>
-  </si>
-  <si>
     <t>YS R2-15C</t>
   </si>
   <si>
     <t>M S/W(V형)</t>
   </si>
   <si>
-    <t>998</t>
-  </si>
-  <si>
     <t>YS R1015 GW-B</t>
   </si>
   <si>
-    <t>999</t>
-  </si>
-  <si>
     <t>YS R1115 GW-B</t>
   </si>
   <si>
-    <t>1000</t>
-  </si>
-  <si>
     <t>YS R1215 GW-B</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
     <t>YS L2015 GW-B</t>
   </si>
   <si>
-    <t>1003</t>
-  </si>
-  <si>
     <t>YS L2215 GW-B</t>
   </si>
   <si>
-    <t>1004</t>
-  </si>
-  <si>
     <t>YS L2315 GW-B</t>
   </si>
   <si>
-    <t>1006</t>
-  </si>
-  <si>
     <t>YS P3315 GW-B</t>
   </si>
   <si>
-    <t>1007</t>
-  </si>
-  <si>
     <t>YS RP3515 GW-B</t>
   </si>
   <si>
-    <t>1008</t>
-  </si>
-  <si>
     <t>YS RP3615 GW-B</t>
   </si>
   <si>
-    <t>1010</t>
-  </si>
-  <si>
     <t>YS R1010 GW-B</t>
   </si>
   <si>
-    <t>1011</t>
-  </si>
-  <si>
     <t>YS R1110 GW-B</t>
   </si>
   <si>
-    <t>1012</t>
-  </si>
-  <si>
     <t>YS R1210 GW-B</t>
   </si>
   <si>
-    <t>1015</t>
-  </si>
-  <si>
     <t>YS L2210 GW-B</t>
   </si>
   <si>
-    <t>1020</t>
-  </si>
-  <si>
     <t>YS RP3610 GW-B</t>
   </si>
   <si>
     <t>M S/W(Z형)</t>
   </si>
   <si>
-    <t>1134</t>
-  </si>
-  <si>
     <t>YS NPBL2-O24A</t>
   </si>
   <si>
-    <t>1119</t>
-  </si>
-  <si>
     <t>YS NPBL2-T22A</t>
   </si>
   <si>
-    <t>1135</t>
-  </si>
-  <si>
     <t>YS NPBL3-O24A</t>
   </si>
   <si>
-    <t>1126</t>
-  </si>
-  <si>
     <t>YS NPBL3-T22A</t>
   </si>
   <si>
-    <t>1144</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL11 G</t>
   </si>
   <si>
-    <t>1143</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL11 R</t>
   </si>
   <si>
-    <t>1145</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL11 Y</t>
   </si>
   <si>
-    <t>1170</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL12 G</t>
   </si>
   <si>
-    <t>1169</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL12 R</t>
   </si>
   <si>
-    <t>1171</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL12 Y</t>
   </si>
   <si>
-    <t>1152</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL22 G</t>
   </si>
   <si>
-    <t>1151</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL22 R</t>
   </si>
   <si>
-    <t>1153</t>
-  </si>
-  <si>
     <t>YS NPBL2-AL22 Y</t>
   </si>
   <si>
-    <t>1190</t>
-  </si>
-  <si>
     <t>YS NPBL2-DL11 G</t>
   </si>
   <si>
-    <t>1189</t>
-  </si>
-  <si>
     <t>YS NPBL2-DL11 R</t>
   </si>
   <si>
-    <t>1196</t>
-  </si>
-  <si>
     <t>YS NPBL2-DL12 Y</t>
   </si>
   <si>
-    <t>1180</t>
-  </si>
-  <si>
     <t>YS NPBL2-DL24 G</t>
   </si>
   <si>
-    <t>1179</t>
-  </si>
-  <si>
     <t>YS NPBL2-DL24 R</t>
   </si>
   <si>
-    <t>1181</t>
-  </si>
-  <si>
     <t>YS NPBL2-DL24 Y</t>
   </si>
   <si>
-    <t>1160</t>
-  </si>
-  <si>
     <t>YS NPBL3-AL11 G</t>
   </si>
   <si>
-    <t>1159</t>
-  </si>
-  <si>
     <t>YS NPBL3-AL11 R</t>
   </si>
   <si>
-    <t>1165</t>
-  </si>
-  <si>
     <t>YS NPBL3-AL22 G</t>
   </si>
   <si>
-    <t>1164</t>
-  </si>
-  <si>
     <t>YS NPBL3-AL22 R</t>
   </si>
   <si>
-    <t>1166</t>
-  </si>
-  <si>
     <t>YS NPBL3-AL22 Y</t>
   </si>
   <si>
-    <t>1210</t>
-  </si>
-  <si>
     <t>YS NPBL3-DL11 G</t>
   </si>
   <si>
-    <t>1209</t>
-  </si>
-  <si>
     <t>YS NPBL3-DL11 R</t>
   </si>
   <si>
-    <t>1211</t>
-  </si>
-  <si>
     <t>YS NPBL3-DL11 Y</t>
   </si>
   <si>
     <t>NPBL</t>
   </si>
   <si>
-    <t>1613</t>
-  </si>
-  <si>
     <t>YS BRL34-AL11 RGYO</t>
   </si>
   <si>
-    <t>1618</t>
-  </si>
-  <si>
     <t>YS BRL34-AL22 RGYO</t>
   </si>
   <si>
-    <t>1633</t>
-  </si>
-  <si>
     <t>YS BRL34-DL11 RGYO</t>
   </si>
   <si>
-    <t>1638</t>
-  </si>
-  <si>
     <t>YS BRL34-DL12 RGYO</t>
   </si>
   <si>
-    <t>11280</t>
-  </si>
-  <si>
     <t>YS BRL34-DL22 RGYO</t>
   </si>
   <si>
-    <t>1623</t>
-  </si>
-  <si>
     <t>YS BRL34-DL24 RGYO</t>
   </si>
   <si>
-    <t>1555</t>
-  </si>
-  <si>
     <t>YS BSL33-AL11 RGYO</t>
   </si>
   <si>
-    <t>1560</t>
-  </si>
-  <si>
     <t>YS BSL33-AL22 RGYO</t>
   </si>
   <si>
-    <t>1575</t>
-  </si>
-  <si>
     <t>YS BSL33-DL11 RGYO</t>
   </si>
   <si>
-    <t>1580</t>
-  </si>
-  <si>
     <t>YS BSL33-DL12 RGYO</t>
   </si>
   <si>
-    <t>15194</t>
-  </si>
-  <si>
     <t>YS BSL33-DL22 RGYO</t>
   </si>
   <si>
-    <t>1565</t>
-  </si>
-  <si>
     <t>YS BSL33-DL24 RGYO</t>
   </si>
   <si>
-    <t>1602</t>
-  </si>
-  <si>
     <t>YS NRL34-O24A</t>
   </si>
   <si>
-    <t>1599</t>
-  </si>
-  <si>
     <t>YS NRL34-T11A</t>
   </si>
   <si>
-    <t>1601</t>
-  </si>
-  <si>
     <t>YS NRL34-T22A</t>
   </si>
   <si>
-    <t>1539</t>
-  </si>
-  <si>
     <t>YS SL325-DL12</t>
   </si>
   <si>
-    <t>1536</t>
-  </si>
-  <si>
     <t>YS SL325-DL24</t>
   </si>
   <si>
-    <t>18844</t>
-  </si>
-  <si>
     <t>YS SL33-O24A</t>
   </si>
   <si>
-    <t>1540</t>
-  </si>
-  <si>
     <t>YS SL33-T11A</t>
   </si>
   <si>
-    <t>1541</t>
-  </si>
-  <si>
     <t>YS SL33-T22A</t>
   </si>
   <si>
     <t>SL-33(곤지암)</t>
   </si>
   <si>
-    <t>22089</t>
-  </si>
-  <si>
     <t>YS FT-F00 10 06S</t>
   </si>
   <si>
-    <t>22090</t>
-  </si>
-  <si>
     <t>YS FT-F00 10 12S</t>
   </si>
   <si>
-    <t>22091</t>
-  </si>
-  <si>
     <t>YS FT-F00 10 30S</t>
   </si>
   <si>
-    <t>22092</t>
-  </si>
-  <si>
     <t>YS FT-F00 10 60S</t>
   </si>
   <si>
-    <t>2510</t>
-  </si>
-  <si>
     <t>YS FS-C22-M4</t>
   </si>
   <si>
-    <t>21937</t>
-  </si>
-  <si>
     <t>YS LT-F00 11 03M</t>
   </si>
   <si>
-    <t>21938</t>
-  </si>
-  <si>
     <t>YS LT-F00 11 06M</t>
   </si>
   <si>
-    <t>21934</t>
-  </si>
-  <si>
     <t>YS LT-F00 11 12S</t>
   </si>
   <si>
-    <t>21945</t>
-  </si>
-  <si>
     <t>YS LT-F00 11 24H</t>
   </si>
   <si>
-    <t>21940</t>
-  </si>
-  <si>
     <t>YS LT-F00 11 30M</t>
   </si>
   <si>
-    <t>21935</t>
-  </si>
-  <si>
     <t>YS LT-F00 11 30S</t>
   </si>
   <si>
-    <t>21936</t>
-  </si>
-  <si>
     <t>YS LT-F00 11 60S</t>
   </si>
   <si>
-    <t>26034</t>
-  </si>
-  <si>
     <t>YS YT-F00 13 30S</t>
   </si>
   <si>
-    <t>26036</t>
-  </si>
-  <si>
     <t>YS YT-F00 13 60S</t>
   </si>
   <si>
     <t>대륜전자</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>YS LY-10-2P-220ASL</t>
   </si>
   <si>
-    <t>2026</t>
-  </si>
-  <si>
     <t>YS LY-10-2P-110DSL</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>YS LY-10-2P-024DSL</t>
   </si>
   <si>
-    <t>14419</t>
-  </si>
-  <si>
     <t>YS LY-10-4P-220AS L</t>
   </si>
   <si>
-    <t>14423</t>
-  </si>
-  <si>
     <t>YS LY-10-4P-024DS L</t>
   </si>
   <si>
-    <t>2087</t>
-  </si>
-  <si>
     <t>YS MM-4PC-125D</t>
   </si>
   <si>
-    <t>2091</t>
-  </si>
-  <si>
     <t>YS MMK-4PB-220A</t>
   </si>
   <si>
-    <t>2093</t>
-  </si>
-  <si>
     <t>YS MMK-4PB-024D</t>
   </si>
   <si>
-    <t>2095</t>
-  </si>
-  <si>
     <t>YS MMK-4PB-110D</t>
   </si>
   <si>
-    <t>2098</t>
-  </si>
-  <si>
     <t>YS MMK-4PB-125D</t>
   </si>
   <si>
-    <t>2099</t>
-  </si>
-  <si>
     <t>YS MMK-4PB A110/D110</t>
   </si>
   <si>
-    <t>2033</t>
-  </si>
-  <si>
     <t>YS MR-07-2P-110A</t>
   </si>
   <si>
-    <t>2052</t>
-  </si>
-  <si>
     <t>YS MR-05-3P-220A</t>
   </si>
   <si>
-    <t>2035</t>
-  </si>
-  <si>
     <t>YS MR-07-2P-220A</t>
   </si>
   <si>
-    <t>2055</t>
-  </si>
-  <si>
     <t>YS MR-05-3P-024D</t>
   </si>
   <si>
-    <t>2038</t>
-  </si>
-  <si>
     <t>YS MR-07-2P-024D</t>
   </si>
   <si>
-    <t>2040</t>
-  </si>
-  <si>
     <t>YS MR-07-2P-110D</t>
   </si>
   <si>
-    <t>2058</t>
-  </si>
-  <si>
     <t>YS MR-05-3P-125D</t>
   </si>
   <si>
-    <t>2041</t>
-  </si>
-  <si>
     <t>YS MR-07-2P-125D</t>
   </si>
   <si>
-    <t>1971</t>
-  </si>
-  <si>
     <t>YS MY-05-2P-220ASL</t>
   </si>
   <si>
-    <t>1974</t>
-  </si>
-  <si>
     <t>YS MY-05-2P-024DSL</t>
   </si>
   <si>
-    <t>1977</t>
-  </si>
-  <si>
     <t>YS MY-05-2P-125DSL</t>
   </si>
   <si>
-    <t>1998</t>
-  </si>
-  <si>
     <t>YS MY-03-4P-110ASL</t>
   </si>
   <si>
-    <t>1999</t>
-  </si>
-  <si>
     <t>YS MY-03-4P-220ASL</t>
   </si>
   <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>YS MY-03-4P-024DSL</t>
   </si>
   <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>YS MY-03-4P-110DSL</t>
   </si>
   <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>YS MY-03-4P-125DSL</t>
   </si>
   <si>
-    <t>16676</t>
-  </si>
-  <si>
     <t>YS APR30-2PA-220A</t>
   </si>
   <si>
-    <t>11615</t>
-  </si>
-  <si>
     <t>YS APR30-2PC-220A</t>
   </si>
   <si>
-    <t>16674</t>
-  </si>
-  <si>
     <t>YS APR30-2PA-110D</t>
   </si>
   <si>
-    <t>16672</t>
-  </si>
-  <si>
     <t>YS APR30-2PA-024D</t>
   </si>
   <si>
-    <t>11623</t>
-  </si>
-  <si>
     <t>YS APR30-2PC-024D</t>
   </si>
   <si>
-    <t>26491</t>
-  </si>
-  <si>
     <t>YM4-L AC220V</t>
   </si>
   <si>
     <t>릴레이</t>
   </si>
   <si>
-    <t>24675</t>
-  </si>
-  <si>
     <t>YS BC22-6</t>
   </si>
   <si>
-    <t>24676</t>
-  </si>
-  <si>
     <t>YS BC25-6</t>
   </si>
   <si>
-    <t>24677</t>
-  </si>
-  <si>
     <t>YS BC30-6</t>
   </si>
   <si>
-    <t>1079</t>
-  </si>
-  <si>
     <t>YS AX-10(강)</t>
   </si>
   <si>
-    <t>22613</t>
-  </si>
-  <si>
     <t>YS AX-10(약)</t>
   </si>
   <si>
-    <t>2761</t>
-  </si>
-  <si>
     <t>YS CN-16-P(상)</t>
   </si>
   <si>
-    <t>2758</t>
-  </si>
-  <si>
     <t>YS CN-16-S</t>
   </si>
   <si>
-    <t>2762</t>
-  </si>
-  <si>
     <t>YS CN-32-C(하)</t>
   </si>
   <si>
-    <t>2763</t>
-  </si>
-  <si>
     <t>YS CN-32-P(상)</t>
   </si>
   <si>
-    <t>2759</t>
-  </si>
-  <si>
     <t>YS CN-32-S</t>
   </si>
   <si>
-    <t>15867</t>
-  </si>
-  <si>
     <t>YS ACN-06-S</t>
   </si>
   <si>
-    <t>15864</t>
-  </si>
-  <si>
     <t>YS ACN-10-S</t>
   </si>
   <si>
-    <t>15437</t>
-  </si>
-  <si>
     <t>YS ACN-24-S</t>
   </si>
   <si>
-    <t>8255</t>
-  </si>
-  <si>
     <t>YS CN-16-C(하)</t>
   </si>
   <si>
-    <t>860</t>
-  </si>
-  <si>
     <t>YS LS13-2222-10101010(장)</t>
   </si>
   <si>
-    <t>1046</t>
-  </si>
-  <si>
     <t>YS 511RL</t>
   </si>
   <si>
-    <t>1047</t>
-  </si>
-  <si>
     <t>YS 512RL</t>
   </si>
   <si>
-    <t>1048</t>
-  </si>
-  <si>
     <t>YS 513RL</t>
   </si>
   <si>
-    <t>1054</t>
-  </si>
-  <si>
     <t>YS 518S</t>
   </si>
   <si>
-    <t>20595</t>
-  </si>
-  <si>
     <t>YS BC2-A</t>
   </si>
   <si>
-    <t>20596</t>
-  </si>
-  <si>
     <t>YS BC3-A</t>
   </si>
   <si>
-    <t>16451</t>
-  </si>
-  <si>
     <t>YS ARP30-22</t>
   </si>
   <si>
-    <t>7135</t>
-  </si>
-  <si>
     <t>YS FT400-03ZF</t>
   </si>
   <si>
+    <t>YS AEP12-11</t>
+  </si>
+  <si>
+    <t>YS AEP13-11</t>
+  </si>
+  <si>
+    <t>YS AK2-211</t>
+  </si>
+  <si>
+    <t>YS AK2-222</t>
+  </si>
+  <si>
+    <t>YS AK3-211</t>
+  </si>
+  <si>
+    <t>YS PL2-AL12 G</t>
+  </si>
+  <si>
+    <t>YS PL2-AL12 R</t>
+  </si>
+  <si>
+    <t>YS PL2-AL12 Y</t>
+  </si>
+  <si>
+    <t>YS PL2-AL22 W</t>
+  </si>
+  <si>
+    <t>YS PL2-DL22 G</t>
+  </si>
+  <si>
+    <t>YS PL2-DL22 R</t>
+  </si>
+  <si>
+    <t>YS PL2-DL22 Y</t>
+  </si>
+  <si>
+    <t>YS PL2-DL24 G</t>
+  </si>
+  <si>
+    <t>YS PL2-DL24 R</t>
+  </si>
+  <si>
+    <t>YS PL2-DL24 Y</t>
+  </si>
+  <si>
+    <t>YS PL2-DL48 G</t>
+  </si>
+  <si>
+    <t>YS PL2-DL48 R</t>
+  </si>
+  <si>
+    <t>YS PL2-DL48 Y</t>
+  </si>
+  <si>
+    <t>YS PL3-DL24 G</t>
+  </si>
+  <si>
+    <t>YS PL3-DL24 R</t>
+  </si>
+  <si>
+    <t>YS PL3-DL24 Y</t>
+  </si>
+  <si>
+    <t>서브 라인</t>
+  </si>
+  <si>
+    <t>YS FT060-03ZF</t>
+  </si>
+  <si>
+    <t>YS FT060-03SF</t>
+  </si>
+  <si>
+    <t>YS FT060-04ZF</t>
+  </si>
+  <si>
+    <t>YS FT060-04SF</t>
+  </si>
+  <si>
+    <t>YS FT100-03ZF</t>
+  </si>
+  <si>
+    <t>YS FT100-04ZF</t>
+  </si>
+  <si>
+    <t>YS FT100-03SF</t>
+  </si>
+  <si>
+    <t>YS FT100-04SF</t>
+  </si>
+  <si>
+    <t>YS FT150-03ZF</t>
+  </si>
+  <si>
+    <t>YS FT150-04ZF</t>
+  </si>
+  <si>
+    <t>YS FT150-03SF</t>
+  </si>
+  <si>
+    <t>YS FT150-04SF</t>
+  </si>
+  <si>
+    <t>YS FT200-03ZF</t>
+  </si>
+  <si>
+    <t>YS FT200-04ZF</t>
+  </si>
+  <si>
+    <t>YS FT200-04SF</t>
+  </si>
+  <si>
+    <t>YS FT300-03ZF</t>
+  </si>
+  <si>
+    <t>YS FT300-04ZF</t>
+  </si>
+  <si>
+    <t>신일ENG</t>
+  </si>
+  <si>
+    <t>AT 번호띠</t>
+  </si>
+  <si>
+    <t>YS AR-1</t>
+  </si>
+  <si>
+    <t>YS AR-2</t>
+  </si>
+  <si>
+    <t>YS AC-1S</t>
+  </si>
+  <si>
+    <t>YS AC-2S</t>
+  </si>
+  <si>
+    <t>YS AP-1</t>
+  </si>
+  <si>
+    <t>영업부 출고분</t>
+  </si>
+  <si>
+    <t>YS ACC-A22</t>
+  </si>
+  <si>
+    <t>YS MB2-11A</t>
+  </si>
+  <si>
+    <t>YS MB2-22A</t>
+  </si>
+  <si>
+    <t>YS EB2-24D</t>
+  </si>
+  <si>
+    <t>YS MB3-11A</t>
+  </si>
+  <si>
+    <t>YS MB3-22A</t>
+  </si>
+  <si>
+    <t>YS EB3-24D</t>
+  </si>
+  <si>
+    <t>YS MB6-22A</t>
+  </si>
+  <si>
+    <t>YS EB6-24D</t>
+  </si>
+  <si>
+    <t>YS EB6-24D L</t>
+  </si>
+  <si>
+    <t>YS EB6-00F</t>
+  </si>
+  <si>
+    <t>YS EB6-00F L</t>
+  </si>
+  <si>
+    <t>YS EB7-00F</t>
+  </si>
+  <si>
+    <t>YS EB7-00F L</t>
+  </si>
+  <si>
+    <t>YS FS-3S</t>
+  </si>
+  <si>
+    <t>YS FS-B22-M4 (고감도)</t>
+  </si>
+  <si>
+    <t>YS FS-C22-M5</t>
+  </si>
+  <si>
+    <t>YS FS-A22-M5-4A</t>
+  </si>
+  <si>
+    <t>YS OT-F00 12 30S</t>
+  </si>
+  <si>
+    <t>YS OT-F00 12 60S</t>
+  </si>
+  <si>
+    <t>전자</t>
+  </si>
+  <si>
+    <t>재고 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균 판매량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균 계획량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계획 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계획 금액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품 단가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 계획 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 계획 금액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YS R1010 GW-B - LS용 UL</t>
+  </si>
+  <si>
+    <t>YS NPBL2-T22A(Y)</t>
+  </si>
+  <si>
+    <t>전전월 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전월 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015875</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015874</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015876</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015305</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015878</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015877</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015524</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009858</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>011619</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001937</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000958</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>014193</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>014194</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>008010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>008011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>008022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001330</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001329</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001331</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001314</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>007182</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001354</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001353</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001355</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001359</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001361</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001378</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001377</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001379</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>024675</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>024676</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>024677</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002761</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002758</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002762</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002763</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002759</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015867</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015864</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015437</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>008255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000860</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001054</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>020595</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>020596</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016451</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>007135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>복합</t>
-  </si>
-  <si>
-    <t>14193</t>
-  </si>
-  <si>
-    <t>YS AEP12-11</t>
-  </si>
-  <si>
-    <t>14194</t>
-  </si>
-  <si>
-    <t>YS AEP13-11</t>
-  </si>
-  <si>
-    <t>8010</t>
-  </si>
-  <si>
-    <t>YS AK2-211</t>
-  </si>
-  <si>
-    <t>8011</t>
-  </si>
-  <si>
-    <t>YS AK2-222</t>
-  </si>
-  <si>
-    <t>8022</t>
-  </si>
-  <si>
-    <t>YS AK3-211</t>
-  </si>
-  <si>
-    <t>1330</t>
-  </si>
-  <si>
-    <t>YS PL2-AL12 G</t>
-  </si>
-  <si>
-    <t>1329</t>
-  </si>
-  <si>
-    <t>YS PL2-AL12 R</t>
-  </si>
-  <si>
-    <t>1331</t>
-  </si>
-  <si>
-    <t>YS PL2-AL12 Y</t>
-  </si>
-  <si>
-    <t>1314</t>
-  </si>
-  <si>
-    <t>YS PL2-AL22 W</t>
-  </si>
-  <si>
-    <t>1402</t>
-  </si>
-  <si>
-    <t>YS PL2-DL22 G</t>
-  </si>
-  <si>
-    <t>1401</t>
-  </si>
-  <si>
-    <t>YS PL2-DL22 R</t>
-  </si>
-  <si>
-    <t>7182</t>
-  </si>
-  <si>
-    <t>YS PL2-DL22 Y</t>
-  </si>
-  <si>
-    <t>1354</t>
-  </si>
-  <si>
-    <t>YS PL2-DL24 G</t>
-  </si>
-  <si>
-    <t>1353</t>
-  </si>
-  <si>
-    <t>YS PL2-DL24 R</t>
-  </si>
-  <si>
-    <t>1355</t>
-  </si>
-  <si>
-    <t>YS PL2-DL24 Y</t>
-  </si>
-  <si>
-    <t>1360</t>
-  </si>
-  <si>
-    <t>YS PL2-DL48 G</t>
-  </si>
-  <si>
-    <t>1359</t>
-  </si>
-  <si>
-    <t>YS PL2-DL48 R</t>
-  </si>
-  <si>
-    <t>1361</t>
-  </si>
-  <si>
-    <t>YS PL2-DL48 Y</t>
-  </si>
-  <si>
-    <t>1378</t>
-  </si>
-  <si>
-    <t>YS PL3-DL24 G</t>
-  </si>
-  <si>
-    <t>1377</t>
-  </si>
-  <si>
-    <t>YS PL3-DL24 R</t>
-  </si>
-  <si>
-    <t>1379</t>
-  </si>
-  <si>
-    <t>YS PL3-DL24 Y</t>
-  </si>
-  <si>
-    <t>서브 라인</t>
-  </si>
-  <si>
-    <t>2676</t>
-  </si>
-  <si>
-    <t>YS FT060-03ZF</t>
-  </si>
-  <si>
-    <t>2704</t>
-  </si>
-  <si>
-    <t>YS FT060-03SF</t>
-  </si>
-  <si>
-    <t>2677</t>
-  </si>
-  <si>
-    <t>YS FT060-04ZF</t>
-  </si>
-  <si>
-    <t>2705</t>
-  </si>
-  <si>
-    <t>YS FT060-04SF</t>
-  </si>
-  <si>
-    <t>2679</t>
-  </si>
-  <si>
-    <t>YS FT100-03ZF</t>
-  </si>
-  <si>
-    <t>2680</t>
-  </si>
-  <si>
-    <t>YS FT100-04ZF</t>
-  </si>
-  <si>
-    <t>2706</t>
-  </si>
-  <si>
-    <t>YS FT100-03SF</t>
-  </si>
-  <si>
-    <t>2707</t>
-  </si>
-  <si>
-    <t>YS FT100-04SF</t>
-  </si>
-  <si>
-    <t>2681</t>
-  </si>
-  <si>
-    <t>YS FT150-03ZF</t>
-  </si>
-  <si>
-    <t>2682</t>
-  </si>
-  <si>
-    <t>YS FT150-04ZF</t>
-  </si>
-  <si>
-    <t>2708</t>
-  </si>
-  <si>
-    <t>YS FT150-03SF</t>
-  </si>
-  <si>
-    <t>2709</t>
-  </si>
-  <si>
-    <t>YS FT150-04SF</t>
-  </si>
-  <si>
-    <t>2683</t>
-  </si>
-  <si>
-    <t>YS FT200-03ZF</t>
-  </si>
-  <si>
-    <t>2684</t>
-  </si>
-  <si>
-    <t>YS FT200-04ZF</t>
-  </si>
-  <si>
-    <t>2711</t>
-  </si>
-  <si>
-    <t>YS FT200-04SF</t>
-  </si>
-  <si>
-    <t>2685</t>
-  </si>
-  <si>
-    <t>YS FT300-03ZF</t>
-  </si>
-  <si>
-    <t>2686</t>
-  </si>
-  <si>
-    <t>YS FT300-04ZF</t>
-  </si>
-  <si>
-    <t>신일ENG</t>
-  </si>
-  <si>
-    <t>27878</t>
-  </si>
-  <si>
-    <t>AT 번호띠</t>
-  </si>
-  <si>
-    <t>2774</t>
-  </si>
-  <si>
-    <t>YS AR-1</t>
-  </si>
-  <si>
-    <t>2775</t>
-  </si>
-  <si>
-    <t>YS AR-2</t>
-  </si>
-  <si>
-    <t>2776</t>
-  </si>
-  <si>
-    <t>YS AC-1S</t>
-  </si>
-  <si>
-    <t>2777</t>
-  </si>
-  <si>
-    <t>YS AC-2S</t>
-  </si>
-  <si>
-    <t>2783</t>
-  </si>
-  <si>
-    <t>YS AP-1</t>
-  </si>
-  <si>
-    <t>영업부 출고분</t>
-  </si>
-  <si>
-    <t>8254</t>
-  </si>
-  <si>
-    <t>YS ACC-A22</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>YS MB2-11A</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>YS MB2-22A</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>YS EB2-24D</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>YS MB3-11A</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>YS MB3-22A</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>YS EB3-24D</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>YS MB6-22A</t>
-  </si>
-  <si>
-    <t>2113</t>
-  </si>
-  <si>
-    <t>YS EB6-24D</t>
-  </si>
-  <si>
-    <t>20408</t>
-  </si>
-  <si>
-    <t>YS EB6-24D L</t>
-  </si>
-  <si>
-    <t>7103</t>
-  </si>
-  <si>
-    <t>YS EB6-00F</t>
-  </si>
-  <si>
-    <t>20407</t>
-  </si>
-  <si>
-    <t>YS EB6-00F L</t>
-  </si>
-  <si>
-    <t>10415</t>
-  </si>
-  <si>
-    <t>YS EB7-00F</t>
-  </si>
-  <si>
-    <t>20409</t>
-  </si>
-  <si>
-    <t>YS EB7-00F L</t>
-  </si>
-  <si>
-    <t>2515</t>
-  </si>
-  <si>
-    <t>YS FS-3S</t>
-  </si>
-  <si>
-    <t>2511</t>
-  </si>
-  <si>
-    <t>YS FS-B22-M4 (고감도)</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>YS FS-C22-M5</t>
-  </si>
-  <si>
-    <t>2514</t>
-  </si>
-  <si>
-    <t>YS FS-A22-M5-4A</t>
-  </si>
-  <si>
-    <t>2223</t>
-  </si>
-  <si>
-    <t>YS OT-F00 12 30S</t>
-  </si>
-  <si>
-    <t>2225</t>
-  </si>
-  <si>
-    <t>YS OT-F00 12 60S</t>
-  </si>
-  <si>
-    <t>전자</t>
-  </si>
-  <si>
-    <t>재고 수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>평균 판매량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>평균 계획량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>계획 수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>계획 금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제품 단가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>합계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총 계획 수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총 계획 금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YS R1010 GW-B - LS용 UL</t>
-  </si>
-  <si>
-    <t>YS NPBL2-T22A(Y)</t>
-  </si>
-  <si>
-    <t>전전월 수량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전월 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>014419</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>014423</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002087</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002093</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002095</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002098</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002099</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002055</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001971</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001974</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001977</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001998</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016676</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>011615</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016674</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016672</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>011623</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>026491</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021785</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>018376</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021784</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000998</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>029242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006914</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006916</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006915</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>006925</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>007091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>019650</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022609</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022610</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016954</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016955</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016957</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017399</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017431</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017441</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016977</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017442</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017530</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016987</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016989</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016988</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016990</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017536</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017535</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017039</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016985</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>017040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016959</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>016961</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>025956</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001145</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001171</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001151</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001189</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001179</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001159</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001165</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001164</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001166</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001209</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001618</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001633</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001638</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>011280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001623</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001560</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001575</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001580</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>015194</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001565</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001602</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001599</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001539</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001536</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>018844</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001540</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>001541</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>008254</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002113</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>020408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>007103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>020407</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010415</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>020409</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002515</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002511</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002507</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002514</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002223</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002225</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022090</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>022091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021937</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021938</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021934</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021945</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021940</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021935</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>021936</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>026034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>026036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002676</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002704</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002677</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002705</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002679</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002680</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002706</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002707</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002681</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002682</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002708</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002709</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002683</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002684</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002711</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002685</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002686</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>027878</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002774</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002775</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002776</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002777</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>002783</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1936,15 +2204,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1954,9 +2219,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1983,13 +2245,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1998,13 +2266,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2385,28 +2650,28 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
     </row>
     <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
@@ -2429,80 +2694,80 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="23" t="s">
-        <v>543</v>
-      </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
+      <c r="E5" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
     </row>
     <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="23" t="s">
-        <v>544</v>
-      </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
+      <c r="E6" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>548</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>539</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>541</v>
+      <c r="C8" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2511,14 +2776,14 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="4"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>7</v>
+      <c r="A11" s="21" t="s">
+        <v>291</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -2527,14 +2792,14 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="4"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
+      <c r="A12" s="21" t="s">
+        <v>292</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -2543,14 +2808,14 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="4"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>11</v>
+      <c r="A13" s="21" t="s">
+        <v>293</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -2559,14 +2824,14 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="4"/>
+      <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>13</v>
+      <c r="A14" s="21" t="s">
+        <v>294</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -2575,14 +2840,14 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="4"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>15</v>
+      <c r="A15" s="21" t="s">
+        <v>295</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -2591,14 +2856,14 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="4"/>
+      <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>17</v>
+      <c r="A16" s="21" t="s">
+        <v>296</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -2607,14 +2872,14 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="4"/>
+      <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>19</v>
+      <c r="A17" s="21" t="s">
+        <v>297</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -2623,14 +2888,14 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="4"/>
+      <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>21</v>
+      <c r="A18" s="21" t="s">
+        <v>298</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -2639,14 +2904,14 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="4"/>
+      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>23</v>
+      <c r="A19" s="21" t="s">
+        <v>299</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -2654,15 +2919,15 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="4"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>25</v>
+      <c r="A20" s="21" t="s">
+        <v>300</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -2671,14 +2936,14 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="4"/>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>27</v>
+      <c r="A21" s="21" t="s">
+        <v>301</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -2687,30 +2952,30 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="4"/>
+      <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+      <c r="A22" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>404</v>
+      <c r="A23" s="21" t="s">
+        <v>302</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>405</v>
+        <v>208</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -2719,14 +2984,14 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="4"/>
+      <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>406</v>
+      <c r="A24" s="21" t="s">
+        <v>303</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>407</v>
+        <v>209</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -2735,14 +3000,14 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="4"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>408</v>
+      <c r="A25" s="21" t="s">
+        <v>304</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>409</v>
+        <v>210</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -2751,14 +3016,14 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="4"/>
+      <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>410</v>
+      <c r="A26" s="21" t="s">
+        <v>305</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>411</v>
+        <v>211</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -2767,14 +3032,14 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="4"/>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>412</v>
+      <c r="A27" s="21" t="s">
+        <v>306</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>413</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -2783,14 +3048,14 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="4"/>
+      <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>414</v>
+      <c r="A28" s="21" t="s">
+        <v>307</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>415</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -2799,14 +3064,14 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="4"/>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>416</v>
+      <c r="A29" s="21" t="s">
+        <v>308</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>417</v>
+        <v>214</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -2815,14 +3080,14 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="4"/>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>418</v>
+      <c r="A30" s="21" t="s">
+        <v>309</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>419</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -2831,14 +3096,14 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
+      <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>420</v>
+      <c r="A31" s="21" t="s">
+        <v>310</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>421</v>
+        <v>216</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -2847,14 +3112,14 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="4"/>
+      <c r="J31" s="3"/>
     </row>
     <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>422</v>
+      <c r="A32" s="21" t="s">
+        <v>311</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>423</v>
+        <v>217</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -2863,14 +3128,14 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="4"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>424</v>
+      <c r="A33" s="21" t="s">
+        <v>312</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>425</v>
+        <v>218</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -2879,14 +3144,14 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="4"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>426</v>
+      <c r="A34" s="21" t="s">
+        <v>313</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>427</v>
+        <v>219</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -2895,14 +3160,14 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="4"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>428</v>
+      <c r="A35" s="21" t="s">
+        <v>314</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>429</v>
+        <v>220</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -2911,14 +3176,14 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="4"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>430</v>
+      <c r="A36" s="21" t="s">
+        <v>315</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>431</v>
+        <v>221</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -2927,14 +3192,14 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
-      <c r="J36" s="4"/>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>432</v>
+      <c r="A37" s="21" t="s">
+        <v>316</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>433</v>
+        <v>222</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -2943,14 +3208,14 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="4"/>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>434</v>
+      <c r="A38" s="21" t="s">
+        <v>317</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>435</v>
+        <v>223</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -2959,14 +3224,14 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="4"/>
+      <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>436</v>
+      <c r="A39" s="21" t="s">
+        <v>318</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>437</v>
+        <v>224</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -2975,14 +3240,14 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="4"/>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>438</v>
+      <c r="A40" s="21" t="s">
+        <v>319</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>439</v>
+        <v>225</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -2991,14 +3256,14 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="4"/>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>440</v>
+      <c r="A41" s="21" t="s">
+        <v>320</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>441</v>
+        <v>226</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -3007,14 +3272,14 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
-      <c r="J41" s="4"/>
+      <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>442</v>
+      <c r="A42" s="21" t="s">
+        <v>321</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>443</v>
+        <v>227</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -3023,14 +3288,14 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="4"/>
+      <c r="J42" s="3"/>
     </row>
     <row r="43" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>444</v>
+      <c r="A43" s="21" t="s">
+        <v>322</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>445</v>
+        <v>228</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -3039,30 +3304,30 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="4"/>
+      <c r="J43" s="3"/>
     </row>
     <row r="44" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="17" t="s">
-        <v>446</v>
-      </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
+      <c r="A44" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="4" t="s">
+      <c r="J44" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>357</v>
+      <c r="A45" s="21" t="s">
+        <v>323</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>358</v>
+        <v>185</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -3071,14 +3336,14 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="4"/>
+      <c r="J45" s="3"/>
     </row>
     <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>359</v>
+      <c r="A46" s="21" t="s">
+        <v>324</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>360</v>
+        <v>186</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -3087,14 +3352,14 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="4"/>
+      <c r="J46" s="3"/>
     </row>
     <row r="47" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>361</v>
+      <c r="A47" s="21" t="s">
+        <v>325</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>362</v>
+        <v>187</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -3103,14 +3368,14 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="4"/>
+      <c r="J47" s="3"/>
     </row>
     <row r="48" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>363</v>
+      <c r="A48" s="21" t="s">
+        <v>326</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>364</v>
+        <v>188</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -3119,14 +3384,14 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="4"/>
+      <c r="J48" s="3"/>
     </row>
     <row r="49" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>365</v>
+      <c r="A49" s="21" t="s">
+        <v>327</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>366</v>
+        <v>189</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -3135,14 +3400,14 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="4"/>
+      <c r="J49" s="3"/>
     </row>
     <row r="50" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>367</v>
+      <c r="A50" s="21" t="s">
+        <v>328</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>368</v>
+        <v>190</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -3151,14 +3416,14 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="4"/>
+      <c r="J50" s="3"/>
     </row>
     <row r="51" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>369</v>
+      <c r="A51" s="21" t="s">
+        <v>329</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>370</v>
+        <v>191</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -3167,14 +3432,14 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="4"/>
+      <c r="J51" s="3"/>
     </row>
     <row r="52" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
-        <v>371</v>
+      <c r="A52" s="21" t="s">
+        <v>330</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>372</v>
+        <v>192</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -3183,14 +3448,14 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="4"/>
+      <c r="J52" s="3"/>
     </row>
     <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
-        <v>373</v>
+      <c r="A53" s="21" t="s">
+        <v>331</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>374</v>
+        <v>193</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -3199,14 +3464,14 @@
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="J53" s="4"/>
+      <c r="J53" s="3"/>
     </row>
     <row r="54" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
-        <v>375</v>
+      <c r="A54" s="21" t="s">
+        <v>332</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>376</v>
+        <v>194</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -3215,14 +3480,14 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
-      <c r="J54" s="4"/>
+      <c r="J54" s="3"/>
     </row>
     <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
-        <v>377</v>
+      <c r="A55" s="21" t="s">
+        <v>333</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>378</v>
+        <v>195</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -3231,14 +3496,14 @@
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="J55" s="4"/>
+      <c r="J55" s="3"/>
     </row>
     <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
-        <v>379</v>
+      <c r="A56" s="21" t="s">
+        <v>334</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>380</v>
+        <v>196</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -3247,14 +3512,14 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="J56" s="4"/>
+      <c r="J56" s="3"/>
     </row>
     <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
-        <v>381</v>
+      <c r="A57" s="21" t="s">
+        <v>335</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>382</v>
+        <v>197</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -3263,14 +3528,14 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
-      <c r="J57" s="4"/>
+      <c r="J57" s="3"/>
     </row>
     <row r="58" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
-        <v>383</v>
+      <c r="A58" s="21" t="s">
+        <v>336</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>384</v>
+        <v>198</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -3279,14 +3544,14 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
-      <c r="J58" s="4"/>
+      <c r="J58" s="3"/>
     </row>
     <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
-        <v>385</v>
+      <c r="A59" s="21" t="s">
+        <v>337</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>386</v>
+        <v>199</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -3295,14 +3560,14 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
-      <c r="J59" s="4"/>
+      <c r="J59" s="3"/>
     </row>
     <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
-        <v>387</v>
+      <c r="A60" s="21" t="s">
+        <v>338</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>388</v>
+        <v>200</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -3311,14 +3576,14 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
-      <c r="J60" s="4"/>
+      <c r="J60" s="3"/>
     </row>
     <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
-        <v>389</v>
+      <c r="A61" s="21" t="s">
+        <v>339</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>390</v>
+        <v>201</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -3327,14 +3592,14 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
-      <c r="J61" s="4"/>
+      <c r="J61" s="3"/>
     </row>
     <row r="62" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
-        <v>391</v>
+      <c r="A62" s="21" t="s">
+        <v>340</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>392</v>
+        <v>202</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -3343,14 +3608,14 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
-      <c r="J62" s="4"/>
+      <c r="J62" s="3"/>
     </row>
     <row r="63" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
-        <v>393</v>
+      <c r="A63" s="21" t="s">
+        <v>341</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>394</v>
+        <v>203</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -3359,14 +3624,14 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
-      <c r="J63" s="4"/>
+      <c r="J63" s="3"/>
     </row>
     <row r="64" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
-        <v>395</v>
+      <c r="A64" s="21" t="s">
+        <v>342</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>396</v>
+        <v>204</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -3375,14 +3640,14 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
-      <c r="J64" s="4"/>
+      <c r="J64" s="3"/>
     </row>
     <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
-        <v>397</v>
+      <c r="A65" s="21" t="s">
+        <v>343</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>398</v>
+        <v>205</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -3391,14 +3656,14 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
-      <c r="J65" s="4"/>
+      <c r="J65" s="3"/>
     </row>
     <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
-        <v>399</v>
+      <c r="A66" s="21" t="s">
+        <v>344</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>400</v>
+        <v>206</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -3407,14 +3672,14 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
-      <c r="J66" s="4"/>
+      <c r="J66" s="3"/>
     </row>
     <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
-        <v>401</v>
+      <c r="A67" s="21" t="s">
+        <v>345</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>402</v>
+        <v>207</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -3423,30 +3688,30 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
-      <c r="J67" s="4"/>
+      <c r="J67" s="3"/>
     </row>
     <row r="68" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+      <c r="A68" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
-      <c r="J68" s="4" t="s">
+      <c r="J68" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
-        <v>290</v>
+      <c r="A69" s="21" t="s">
+        <v>347</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>291</v>
+        <v>151</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -3455,14 +3720,14 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
-      <c r="J69" s="4"/>
+      <c r="J69" s="3"/>
     </row>
     <row r="70" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
-        <v>292</v>
+      <c r="A70" s="21" t="s">
+        <v>348</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>293</v>
+        <v>152</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -3471,14 +3736,14 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
-      <c r="J70" s="4"/>
+      <c r="J70" s="3"/>
     </row>
     <row r="71" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
-        <v>294</v>
+      <c r="A71" s="21" t="s">
+        <v>349</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>295</v>
+        <v>153</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -3487,14 +3752,14 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
-      <c r="J71" s="4"/>
+      <c r="J71" s="3"/>
     </row>
     <row r="72" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
-        <v>296</v>
+      <c r="A72" s="21" t="s">
+        <v>350</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>297</v>
+        <v>154</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -3503,14 +3768,14 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
-      <c r="J72" s="4"/>
+      <c r="J72" s="3"/>
     </row>
     <row r="73" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
-        <v>298</v>
+      <c r="A73" s="21" t="s">
+        <v>351</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>299</v>
+        <v>155</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -3519,14 +3784,14 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
-      <c r="J73" s="4"/>
+      <c r="J73" s="3"/>
     </row>
     <row r="74" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
-        <v>300</v>
+      <c r="A74" s="21" t="s">
+        <v>352</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>301</v>
+        <v>156</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -3535,14 +3800,14 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
-      <c r="J74" s="4"/>
+      <c r="J74" s="3"/>
     </row>
     <row r="75" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
-        <v>302</v>
+      <c r="A75" s="21" t="s">
+        <v>353</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>303</v>
+        <v>157</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -3551,14 +3816,14 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
-      <c r="J75" s="4"/>
+      <c r="J75" s="3"/>
     </row>
     <row r="76" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
-        <v>304</v>
+      <c r="A76" s="21" t="s">
+        <v>354</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>305</v>
+        <v>158</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -3567,14 +3832,14 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
-      <c r="J76" s="4"/>
+      <c r="J76" s="3"/>
     </row>
     <row r="77" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
-        <v>306</v>
+      <c r="A77" s="21" t="s">
+        <v>355</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -3583,14 +3848,14 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
-      <c r="J77" s="4"/>
+      <c r="J77" s="3"/>
     </row>
     <row r="78" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
-        <v>308</v>
+      <c r="A78" s="21" t="s">
+        <v>356</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>309</v>
+        <v>160</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -3599,14 +3864,14 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
-      <c r="J78" s="4"/>
+      <c r="J78" s="3"/>
     </row>
     <row r="79" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
-        <v>310</v>
+      <c r="A79" s="21" t="s">
+        <v>357</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>311</v>
+        <v>161</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -3615,14 +3880,14 @@
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
-      <c r="J79" s="4"/>
+      <c r="J79" s="3"/>
     </row>
     <row r="80" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
-        <v>312</v>
+      <c r="A80" s="21" t="s">
+        <v>358</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>313</v>
+        <v>162</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -3631,14 +3896,14 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
-      <c r="J80" s="4"/>
+      <c r="J80" s="3"/>
     </row>
     <row r="81" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
-        <v>314</v>
+      <c r="A81" s="21" t="s">
+        <v>359</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>315</v>
+        <v>163</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -3647,14 +3912,14 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-      <c r="J81" s="4"/>
+      <c r="J81" s="3"/>
     </row>
     <row r="82" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
-        <v>316</v>
+      <c r="A82" s="21" t="s">
+        <v>360</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>317</v>
+        <v>164</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -3663,14 +3928,14 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
-      <c r="J82" s="4"/>
+      <c r="J82" s="3"/>
     </row>
     <row r="83" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
-        <v>318</v>
+      <c r="A83" s="21" t="s">
+        <v>361</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>319</v>
+        <v>165</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -3679,14 +3944,14 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-      <c r="J83" s="4"/>
+      <c r="J83" s="3"/>
     </row>
     <row r="84" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
-        <v>320</v>
+      <c r="A84" s="21" t="s">
+        <v>362</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>321</v>
+        <v>166</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -3695,14 +3960,14 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
-      <c r="J84" s="4"/>
+      <c r="J84" s="3"/>
     </row>
     <row r="85" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
-        <v>322</v>
+      <c r="A85" s="21" t="s">
+        <v>363</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>323</v>
+        <v>167</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -3711,14 +3976,14 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
-      <c r="J85" s="4"/>
+      <c r="J85" s="3"/>
     </row>
     <row r="86" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
-        <v>324</v>
+      <c r="A86" s="21" t="s">
+        <v>364</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>325</v>
+        <v>168</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -3727,14 +3992,14 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
-      <c r="J86" s="4"/>
+      <c r="J86" s="3"/>
     </row>
     <row r="87" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
-        <v>326</v>
+      <c r="A87" s="21" t="s">
+        <v>365</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>327</v>
+        <v>169</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -3743,14 +4008,14 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
-      <c r="J87" s="4"/>
+      <c r="J87" s="3"/>
     </row>
     <row r="88" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
-        <v>328</v>
+      <c r="A88" s="21" t="s">
+        <v>366</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>329</v>
+        <v>170</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -3759,14 +4024,14 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
-      <c r="J88" s="4"/>
+      <c r="J88" s="3"/>
     </row>
     <row r="89" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
-        <v>330</v>
+      <c r="A89" s="21" t="s">
+        <v>367</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>331</v>
+        <v>171</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -3775,14 +4040,14 @@
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
-      <c r="J89" s="4"/>
+      <c r="J89" s="3"/>
     </row>
     <row r="90" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
-        <v>332</v>
+      <c r="A90" s="21" t="s">
+        <v>368</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>333</v>
+        <v>172</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -3791,14 +4056,14 @@
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
-      <c r="J90" s="4"/>
+      <c r="J90" s="3"/>
     </row>
     <row r="91" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
-        <v>334</v>
+      <c r="A91" s="21" t="s">
+        <v>369</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>335</v>
+        <v>173</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -3807,14 +4072,14 @@
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
-      <c r="J91" s="4"/>
+      <c r="J91" s="3"/>
     </row>
     <row r="92" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
-        <v>336</v>
+      <c r="A92" s="21" t="s">
+        <v>370</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>337</v>
+        <v>174</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -3823,14 +4088,14 @@
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
-      <c r="J92" s="4"/>
+      <c r="J92" s="3"/>
     </row>
     <row r="93" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
-        <v>338</v>
+      <c r="A93" s="21" t="s">
+        <v>371</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>339</v>
+        <v>175</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -3839,14 +4104,14 @@
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
-      <c r="J93" s="4"/>
+      <c r="J93" s="3"/>
     </row>
     <row r="94" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
-        <v>340</v>
+      <c r="A94" s="21" t="s">
+        <v>372</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>341</v>
+        <v>176</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -3855,14 +4120,14 @@
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
-      <c r="J94" s="4"/>
+      <c r="J94" s="3"/>
     </row>
     <row r="95" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
-        <v>342</v>
+      <c r="A95" s="21" t="s">
+        <v>378</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>343</v>
+        <v>177</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -3871,14 +4136,14 @@
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
-      <c r="J95" s="4"/>
+      <c r="J95" s="3"/>
     </row>
     <row r="96" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
-        <v>344</v>
+      <c r="A96" s="21" t="s">
+        <v>373</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>345</v>
+        <v>178</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -3887,14 +4152,14 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
-      <c r="J96" s="4"/>
+      <c r="J96" s="3"/>
     </row>
     <row r="97" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
-        <v>346</v>
+      <c r="A97" s="21" t="s">
+        <v>374</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -3903,14 +4168,14 @@
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
-      <c r="J97" s="4"/>
+      <c r="J97" s="3"/>
     </row>
     <row r="98" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
-        <v>348</v>
+      <c r="A98" s="21" t="s">
+        <v>375</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>349</v>
+        <v>180</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -3919,14 +4184,14 @@
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
-      <c r="J98" s="4"/>
+      <c r="J98" s="3"/>
     </row>
     <row r="99" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
-        <v>350</v>
+      <c r="A99" s="21" t="s">
+        <v>376</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>351</v>
+        <v>181</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -3935,14 +4200,14 @@
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
-      <c r="J99" s="4"/>
+      <c r="J99" s="3"/>
     </row>
     <row r="100" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
-        <v>352</v>
+      <c r="A100" s="21" t="s">
+        <v>377</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>353</v>
+        <v>182</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -3951,14 +4216,14 @@
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
-      <c r="J100" s="4"/>
+      <c r="J100" s="3"/>
     </row>
     <row r="101" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
-        <v>354</v>
+      <c r="A101" s="21" t="s">
+        <v>379</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>355</v>
+        <v>183</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -3967,30 +4232,30 @@
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
-      <c r="J101" s="4"/>
+      <c r="J101" s="3"/>
     </row>
     <row r="102" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="B102" s="18"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="18"/>
-      <c r="F102" s="14"/>
-      <c r="G102" s="14"/>
+      <c r="A102" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
-      <c r="J102" s="4" t="s">
+      <c r="J102" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
-        <v>111</v>
+      <c r="A103" s="21" t="s">
+        <v>380</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -3999,14 +4264,14 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
-      <c r="J103" s="4"/>
+      <c r="J103" s="3"/>
     </row>
     <row r="104" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
-        <v>113</v>
+      <c r="A104" s="21" t="s">
+        <v>381</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -4015,14 +4280,14 @@
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
-      <c r="J104" s="4"/>
+      <c r="J104" s="3"/>
     </row>
     <row r="105" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
-        <v>115</v>
+      <c r="A105" s="21" t="s">
+        <v>382</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -4031,14 +4296,14 @@
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
-      <c r="J105" s="4"/>
+      <c r="J105" s="3"/>
     </row>
     <row r="106" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
-        <v>117</v>
+      <c r="A106" s="21" t="s">
+        <v>383</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -4047,14 +4312,14 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
-      <c r="J106" s="4"/>
+      <c r="J106" s="3"/>
     </row>
     <row r="107" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
-        <v>119</v>
+      <c r="A107" s="21" t="s">
+        <v>384</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -4063,14 +4328,14 @@
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
-      <c r="J107" s="4"/>
+      <c r="J107" s="3"/>
     </row>
     <row r="108" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
-        <v>121</v>
+      <c r="A108" s="21" t="s">
+        <v>385</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -4079,14 +4344,14 @@
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
-      <c r="J108" s="4"/>
+      <c r="J108" s="3"/>
     </row>
     <row r="109" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="3" t="s">
-        <v>123</v>
+      <c r="A109" s="21" t="s">
+        <v>386</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -4095,14 +4360,14 @@
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
-      <c r="J109" s="4"/>
+      <c r="J109" s="3"/>
     </row>
     <row r="110" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="3" t="s">
-        <v>125</v>
+      <c r="A110" s="21" t="s">
+        <v>387</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -4111,14 +4376,14 @@
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
-      <c r="J110" s="4"/>
+      <c r="J110" s="3"/>
     </row>
     <row r="111" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="3" t="s">
-        <v>127</v>
+      <c r="A111" s="21" t="s">
+        <v>388</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -4127,14 +4392,14 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
-      <c r="J111" s="4"/>
+      <c r="J111" s="3"/>
     </row>
     <row r="112" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="3" t="s">
-        <v>129</v>
+      <c r="A112" s="21" t="s">
+        <v>389</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -4143,14 +4408,14 @@
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
-      <c r="J112" s="4"/>
+      <c r="J112" s="3"/>
     </row>
     <row r="113" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
-        <v>131</v>
+      <c r="A113" s="21" t="s">
+        <v>390</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -4159,14 +4424,14 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
-      <c r="J113" s="4"/>
+      <c r="J113" s="3"/>
     </row>
     <row r="114" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="3" t="s">
-        <v>133</v>
+      <c r="A114" s="21" t="s">
+        <v>391</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -4175,30 +4440,30 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
-      <c r="J114" s="4"/>
+      <c r="J114" s="3"/>
     </row>
     <row r="115" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="B115" s="18"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="18"/>
-      <c r="F115" s="14"/>
-      <c r="G115" s="14"/>
+      <c r="A115" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="16"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
-      <c r="J115" s="4" t="s">
+      <c r="J115" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
-        <v>136</v>
+      <c r="A116" s="21" t="s">
+        <v>392</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -4207,14 +4472,14 @@
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
-      <c r="J116" s="4"/>
+      <c r="J116" s="3"/>
     </row>
     <row r="117" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
-        <v>138</v>
+      <c r="A117" s="21" t="s">
+        <v>393</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -4223,14 +4488,14 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
-      <c r="J117" s="4"/>
+      <c r="J117" s="3"/>
     </row>
     <row r="118" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="3" t="s">
-        <v>140</v>
+      <c r="A118" s="21" t="s">
+        <v>394</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -4239,14 +4504,14 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
-      <c r="J118" s="4"/>
+      <c r="J118" s="3"/>
     </row>
     <row r="119" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="3" t="s">
-        <v>142</v>
+      <c r="A119" s="21" t="s">
+        <v>395</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -4255,14 +4520,14 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
-      <c r="J119" s="4"/>
+      <c r="J119" s="3"/>
     </row>
     <row r="120" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="3" t="s">
-        <v>144</v>
+      <c r="A120" s="21" t="s">
+        <v>396</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -4271,14 +4536,14 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
-      <c r="J120" s="4"/>
+      <c r="J120" s="3"/>
     </row>
     <row r="121" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="3" t="s">
-        <v>146</v>
+      <c r="A121" s="21" t="s">
+        <v>397</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -4287,14 +4552,14 @@
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
-      <c r="J121" s="4"/>
+      <c r="J121" s="3"/>
     </row>
     <row r="122" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="3" t="s">
-        <v>148</v>
+      <c r="A122" s="21" t="s">
+        <v>402</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -4303,14 +4568,14 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
-      <c r="J122" s="4"/>
+      <c r="J122" s="3"/>
     </row>
     <row r="123" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="3" t="s">
-        <v>150</v>
+      <c r="A123" s="21" t="s">
+        <v>398</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -4319,14 +4584,14 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
-      <c r="J123" s="4"/>
+      <c r="J123" s="3"/>
     </row>
     <row r="124" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="3" t="s">
-        <v>152</v>
+      <c r="A124" s="21" t="s">
+        <v>399</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -4335,14 +4600,14 @@
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
-      <c r="J124" s="4"/>
+      <c r="J124" s="3"/>
     </row>
     <row r="125" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
-        <v>154</v>
+      <c r="A125" s="21" t="s">
+        <v>400</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -4351,14 +4616,14 @@
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
-      <c r="J125" s="4"/>
+      <c r="J125" s="3"/>
     </row>
     <row r="126" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="16">
-        <v>29242</v>
+      <c r="A126" s="21" t="s">
+        <v>401</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>545</v>
+        <v>285</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -4367,14 +4632,14 @@
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
-      <c r="J126" s="4"/>
+      <c r="J126" s="3"/>
     </row>
     <row r="127" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="3" t="s">
-        <v>156</v>
+      <c r="A127" s="21" t="s">
+        <v>403</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -4383,14 +4648,14 @@
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
-      <c r="J127" s="4"/>
+      <c r="J127" s="3"/>
     </row>
     <row r="128" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="3" t="s">
-        <v>158</v>
+      <c r="A128" s="21" t="s">
+        <v>404</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -4399,14 +4664,14 @@
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
-      <c r="J128" s="4"/>
+      <c r="J128" s="3"/>
     </row>
     <row r="129" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
-        <v>160</v>
+      <c r="A129" s="21" t="s">
+        <v>405</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -4415,14 +4680,14 @@
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
-      <c r="J129" s="4"/>
+      <c r="J129" s="3"/>
     </row>
     <row r="130" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="3" t="s">
-        <v>162</v>
+      <c r="A130" s="21" t="s">
+        <v>406</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>163</v>
+        <v>85</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -4431,30 +4696,30 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
-      <c r="J130" s="4"/>
+      <c r="J130" s="3"/>
     </row>
     <row r="131" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B131" s="18"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
-      <c r="F131" s="14"/>
-      <c r="G131" s="14"/>
+      <c r="A131" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B131" s="16"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="16"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
-      <c r="J131" s="4" t="s">
+      <c r="J131" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
-        <v>95</v>
+      <c r="A132" s="21" t="s">
+        <v>411</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -4463,14 +4728,14 @@
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
-      <c r="J132" s="4"/>
+      <c r="J132" s="3"/>
     </row>
     <row r="133" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
-        <v>97</v>
+      <c r="A133" s="21" t="s">
+        <v>407</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -4479,14 +4744,14 @@
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
-      <c r="J133" s="4"/>
+      <c r="J133" s="3"/>
     </row>
     <row r="134" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
-        <v>99</v>
+      <c r="A134" s="21" t="s">
+        <v>408</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -4495,14 +4760,14 @@
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
-      <c r="J134" s="4"/>
+      <c r="J134" s="3"/>
     </row>
     <row r="135" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
-        <v>101</v>
+      <c r="A135" s="21" t="s">
+        <v>409</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -4511,14 +4776,14 @@
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
-      <c r="J135" s="4"/>
+      <c r="J135" s="3"/>
     </row>
     <row r="136" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="3" t="s">
-        <v>103</v>
+      <c r="A136" s="21" t="s">
+        <v>410</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -4527,30 +4792,30 @@
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
-      <c r="J136" s="4"/>
+      <c r="J136" s="3"/>
     </row>
     <row r="137" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B137" s="18"/>
-      <c r="C137" s="18"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="18"/>
-      <c r="F137" s="14"/>
-      <c r="G137" s="14"/>
+      <c r="A137" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B137" s="16"/>
+      <c r="C137" s="16"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="16"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
-      <c r="J137" s="4" t="s">
+      <c r="J137" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="3" t="s">
-        <v>106</v>
+      <c r="A138" s="21" t="s">
+        <v>412</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -4559,14 +4824,14 @@
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
-      <c r="J138" s="4"/>
+      <c r="J138" s="3"/>
     </row>
     <row r="139" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="3" t="s">
-        <v>108</v>
+      <c r="A139" s="21" t="s">
+        <v>413</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -4575,30 +4840,30 @@
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
-      <c r="J139" s="4"/>
+      <c r="J139" s="3"/>
     </row>
     <row r="140" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B140" s="18"/>
-      <c r="C140" s="18"/>
-      <c r="D140" s="18"/>
-      <c r="E140" s="18"/>
-      <c r="F140" s="14"/>
-      <c r="G140" s="14"/>
+      <c r="A140" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B140" s="16"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
-      <c r="J140" s="4" t="s">
+      <c r="J140" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="3" t="s">
-        <v>30</v>
+      <c r="A141" s="21" t="s">
+        <v>414</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -4607,14 +4872,14 @@
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
-      <c r="J141" s="4"/>
+      <c r="J141" s="3"/>
     </row>
     <row r="142" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="3" t="s">
-        <v>32</v>
+      <c r="A142" s="21" t="s">
+        <v>415</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -4623,14 +4888,14 @@
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
-      <c r="J142" s="4"/>
+      <c r="J142" s="3"/>
     </row>
     <row r="143" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
-        <v>34</v>
+      <c r="A143" s="21" t="s">
+        <v>416</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -4639,14 +4904,14 @@
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
-      <c r="J143" s="4"/>
+      <c r="J143" s="3"/>
     </row>
     <row r="144" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
-        <v>36</v>
+      <c r="A144" s="21" t="s">
+        <v>417</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -4655,14 +4920,14 @@
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
-      <c r="J144" s="4"/>
+      <c r="J144" s="3"/>
     </row>
     <row r="145" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
-        <v>38</v>
+      <c r="A145" s="21" t="s">
+        <v>418</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -4671,14 +4936,14 @@
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
-      <c r="J145" s="4"/>
+      <c r="J145" s="3"/>
     </row>
     <row r="146" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
-        <v>40</v>
+      <c r="A146" s="21" t="s">
+        <v>419</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -4687,14 +4952,14 @@
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
-      <c r="J146" s="4"/>
+      <c r="J146" s="3"/>
     </row>
     <row r="147" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
-        <v>42</v>
+      <c r="A147" s="21" t="s">
+        <v>420</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -4703,14 +4968,14 @@
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
-      <c r="J147" s="4"/>
+      <c r="J147" s="3"/>
     </row>
     <row r="148" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="3" t="s">
-        <v>44</v>
+      <c r="A148" s="21" t="s">
+        <v>421</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -4719,14 +4984,14 @@
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
-      <c r="J148" s="4"/>
+      <c r="J148" s="3"/>
     </row>
     <row r="149" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
-        <v>46</v>
+      <c r="A149" s="21" t="s">
+        <v>422</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
@@ -4735,14 +5000,14 @@
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
-      <c r="J149" s="4"/>
+      <c r="J149" s="3"/>
     </row>
     <row r="150" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="3" t="s">
-        <v>48</v>
+      <c r="A150" s="21" t="s">
+        <v>423</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -4751,14 +5016,14 @@
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
-      <c r="J150" s="4"/>
+      <c r="J150" s="3"/>
     </row>
     <row r="151" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
-        <v>50</v>
+      <c r="A151" s="21" t="s">
+        <v>424</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -4767,14 +5032,14 @@
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
-      <c r="J151" s="4"/>
+      <c r="J151" s="3"/>
     </row>
     <row r="152" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
-        <v>52</v>
+      <c r="A152" s="21" t="s">
+        <v>425</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -4783,14 +5048,14 @@
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
-      <c r="J152" s="4"/>
+      <c r="J152" s="3"/>
     </row>
     <row r="153" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
-        <v>54</v>
+      <c r="A153" s="21" t="s">
+        <v>426</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -4799,14 +5064,14 @@
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
-      <c r="J153" s="4"/>
+      <c r="J153" s="3"/>
     </row>
     <row r="154" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
-        <v>56</v>
+      <c r="A154" s="21" t="s">
+        <v>427</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -4815,14 +5080,14 @@
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
-      <c r="J154" s="4"/>
+      <c r="J154" s="3"/>
     </row>
     <row r="155" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="3" t="s">
-        <v>58</v>
+      <c r="A155" s="21" t="s">
+        <v>428</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -4831,14 +5096,14 @@
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
-      <c r="J155" s="4"/>
+      <c r="J155" s="3"/>
     </row>
     <row r="156" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="3" t="s">
-        <v>60</v>
+      <c r="A156" s="21" t="s">
+        <v>429</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -4847,14 +5112,14 @@
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
-      <c r="J156" s="4"/>
+      <c r="J156" s="3"/>
     </row>
     <row r="157" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="3" t="s">
-        <v>62</v>
+      <c r="A157" s="21" t="s">
+        <v>430</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -4863,14 +5128,14 @@
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
-      <c r="J157" s="4"/>
+      <c r="J157" s="3"/>
     </row>
     <row r="158" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="3" t="s">
-        <v>64</v>
+      <c r="A158" s="21" t="s">
+        <v>431</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
@@ -4879,14 +5144,14 @@
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
-      <c r="J158" s="4"/>
+      <c r="J158" s="3"/>
     </row>
     <row r="159" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
-        <v>66</v>
+      <c r="A159" s="21" t="s">
+        <v>432</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -4895,14 +5160,14 @@
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
-      <c r="J159" s="4"/>
+      <c r="J159" s="3"/>
     </row>
     <row r="160" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="3" t="s">
-        <v>68</v>
+      <c r="A160" s="21" t="s">
+        <v>433</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -4911,14 +5176,14 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
-      <c r="J160" s="4"/>
+      <c r="J160" s="3"/>
     </row>
     <row r="161" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
-        <v>70</v>
+      <c r="A161" s="21" t="s">
+        <v>434</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -4927,14 +5192,14 @@
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
-      <c r="J161" s="4"/>
+      <c r="J161" s="3"/>
     </row>
     <row r="162" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
-        <v>72</v>
+      <c r="A162" s="21" t="s">
+        <v>435</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -4943,14 +5208,14 @@
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
-      <c r="J162" s="4"/>
+      <c r="J162" s="3"/>
     </row>
     <row r="163" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="3" t="s">
-        <v>74</v>
+      <c r="A163" s="21" t="s">
+        <v>436</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -4959,14 +5224,14 @@
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
-      <c r="J163" s="4"/>
+      <c r="J163" s="3"/>
     </row>
     <row r="164" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
-        <v>76</v>
+      <c r="A164" s="21" t="s">
+        <v>437</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -4975,14 +5240,14 @@
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
-      <c r="J164" s="4"/>
+      <c r="J164" s="3"/>
     </row>
     <row r="165" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="3" t="s">
-        <v>78</v>
+      <c r="A165" s="21" t="s">
+        <v>438</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -4991,14 +5256,14 @@
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
-      <c r="J165" s="4"/>
+      <c r="J165" s="3"/>
     </row>
     <row r="166" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
-        <v>80</v>
+      <c r="A166" s="21" t="s">
+        <v>439</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -5007,14 +5272,14 @@
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
-      <c r="J166" s="4"/>
+      <c r="J166" s="3"/>
     </row>
     <row r="167" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
-        <v>82</v>
+      <c r="A167" s="21" t="s">
+        <v>440</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -5023,14 +5288,14 @@
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
-      <c r="J167" s="4"/>
+      <c r="J167" s="3"/>
     </row>
     <row r="168" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
-        <v>84</v>
+      <c r="A168" s="21" t="s">
+        <v>441</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -5039,14 +5304,14 @@
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
-      <c r="J168" s="4"/>
+      <c r="J168" s="3"/>
     </row>
     <row r="169" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
-        <v>86</v>
+      <c r="A169" s="21" t="s">
+        <v>442</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -5055,14 +5320,14 @@
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
-      <c r="J169" s="4"/>
+      <c r="J169" s="3"/>
     </row>
     <row r="170" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="3" t="s">
-        <v>88</v>
+      <c r="A170" s="21" t="s">
+        <v>443</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -5071,14 +5336,14 @@
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
-      <c r="J170" s="4"/>
+      <c r="J170" s="3"/>
     </row>
     <row r="171" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
-        <v>90</v>
+      <c r="A171" s="21" t="s">
+        <v>444</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -5087,14 +5352,14 @@
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
-      <c r="J171" s="4"/>
+      <c r="J171" s="3"/>
     </row>
     <row r="172" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="3" t="s">
-        <v>92</v>
+      <c r="A172" s="21" t="s">
+        <v>445</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -5103,30 +5368,30 @@
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
-      <c r="J172" s="4"/>
+      <c r="J172" s="3"/>
     </row>
     <row r="173" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B173" s="18"/>
-      <c r="C173" s="18"/>
-      <c r="D173" s="18"/>
-      <c r="E173" s="18"/>
-      <c r="F173" s="14"/>
-      <c r="G173" s="14"/>
+      <c r="A173" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B173" s="16"/>
+      <c r="C173" s="16"/>
+      <c r="D173" s="16"/>
+      <c r="E173" s="16"/>
+      <c r="F173" s="12"/>
+      <c r="G173" s="12"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
-      <c r="J173" s="4" t="s">
+      <c r="J173" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="3" t="s">
-        <v>165</v>
+      <c r="A174" s="21" t="s">
+        <v>446</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -5135,14 +5400,14 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
-      <c r="J174" s="4"/>
+      <c r="J174" s="3"/>
     </row>
     <row r="175" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="3" t="s">
-        <v>167</v>
+      <c r="A175" s="21" t="s">
+        <v>447</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -5151,14 +5416,14 @@
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
-      <c r="J175" s="4"/>
+      <c r="J175" s="3"/>
     </row>
     <row r="176" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="16">
-        <v>1120</v>
+      <c r="A176" s="21" t="s">
+        <v>448</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>546</v>
+        <v>286</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -5167,14 +5432,14 @@
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
-      <c r="J176" s="4"/>
+      <c r="J176" s="3"/>
     </row>
     <row r="177" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="3" t="s">
-        <v>169</v>
+      <c r="A177" s="21" t="s">
+        <v>449</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>170</v>
+        <v>89</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -5183,14 +5448,14 @@
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
-      <c r="J177" s="4"/>
+      <c r="J177" s="3"/>
     </row>
     <row r="178" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="3" t="s">
-        <v>171</v>
+      <c r="A178" s="21" t="s">
+        <v>450</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -5199,14 +5464,14 @@
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
-      <c r="J178" s="4"/>
+      <c r="J178" s="3"/>
     </row>
     <row r="179" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="3" t="s">
-        <v>173</v>
+      <c r="A179" s="21" t="s">
+        <v>451</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -5215,14 +5480,14 @@
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
-      <c r="J179" s="4"/>
+      <c r="J179" s="3"/>
     </row>
     <row r="180" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="3" t="s">
-        <v>175</v>
+      <c r="A180" s="21" t="s">
+        <v>452</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -5231,14 +5496,14 @@
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
-      <c r="J180" s="4"/>
+      <c r="J180" s="3"/>
     </row>
     <row r="181" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
-        <v>177</v>
+      <c r="A181" s="21" t="s">
+        <v>453</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -5247,14 +5512,14 @@
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
-      <c r="J181" s="4"/>
+      <c r="J181" s="3"/>
     </row>
     <row r="182" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="3" t="s">
-        <v>179</v>
+      <c r="A182" s="21" t="s">
+        <v>454</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>180</v>
+        <v>94</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -5263,14 +5528,14 @@
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
-      <c r="J182" s="4"/>
+      <c r="J182" s="3"/>
     </row>
     <row r="183" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="3" t="s">
-        <v>181</v>
+      <c r="A183" s="21" t="s">
+        <v>455</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -5279,14 +5544,14 @@
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
-      <c r="J183" s="4"/>
+      <c r="J183" s="3"/>
     </row>
     <row r="184" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="3" t="s">
-        <v>183</v>
+      <c r="A184" s="21" t="s">
+        <v>456</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -5295,14 +5560,14 @@
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
-      <c r="J184" s="4"/>
+      <c r="J184" s="3"/>
     </row>
     <row r="185" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="3" t="s">
-        <v>185</v>
+      <c r="A185" s="21" t="s">
+        <v>457</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -5311,14 +5576,14 @@
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
-      <c r="J185" s="4"/>
+      <c r="J185" s="3"/>
     </row>
     <row r="186" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="3" t="s">
-        <v>187</v>
+      <c r="A186" s="21" t="s">
+        <v>458</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -5327,14 +5592,14 @@
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
-      <c r="J186" s="4"/>
+      <c r="J186" s="3"/>
     </row>
     <row r="187" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="3" t="s">
-        <v>189</v>
+      <c r="A187" s="21" t="s">
+        <v>459</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -5343,14 +5608,14 @@
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
-      <c r="J187" s="4"/>
+      <c r="J187" s="3"/>
     </row>
     <row r="188" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="3" t="s">
-        <v>191</v>
+      <c r="A188" s="21" t="s">
+        <v>460</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>192</v>
+        <v>100</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -5359,14 +5624,14 @@
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
-      <c r="J188" s="4"/>
+      <c r="J188" s="3"/>
     </row>
     <row r="189" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="3" t="s">
-        <v>193</v>
+      <c r="A189" s="21" t="s">
+        <v>461</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -5375,14 +5640,14 @@
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
-      <c r="J189" s="4"/>
+      <c r="J189" s="3"/>
     </row>
     <row r="190" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="3" t="s">
-        <v>195</v>
+      <c r="A190" s="21" t="s">
+        <v>467</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -5391,14 +5656,14 @@
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
-      <c r="J190" s="4"/>
+      <c r="J190" s="3"/>
     </row>
     <row r="191" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="3" t="s">
-        <v>197</v>
+      <c r="A191" s="21" t="s">
+        <v>462</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -5407,14 +5672,14 @@
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
-      <c r="J191" s="4"/>
+      <c r="J191" s="3"/>
     </row>
     <row r="192" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="3" t="s">
-        <v>199</v>
+      <c r="A192" s="21" t="s">
+        <v>463</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -5423,14 +5688,14 @@
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
-      <c r="J192" s="4"/>
+      <c r="J192" s="3"/>
     </row>
     <row r="193" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="3" t="s">
-        <v>201</v>
+      <c r="A193" s="21" t="s">
+        <v>464</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -5439,14 +5704,14 @@
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
-      <c r="J193" s="4"/>
+      <c r="J193" s="3"/>
     </row>
     <row r="194" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="3" t="s">
-        <v>203</v>
+      <c r="A194" s="21" t="s">
+        <v>465</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -5455,14 +5720,14 @@
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
-      <c r="J194" s="4"/>
+      <c r="J194" s="3"/>
     </row>
     <row r="195" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="3" t="s">
-        <v>205</v>
+      <c r="A195" s="21" t="s">
+        <v>466</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>206</v>
+        <v>107</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -5471,14 +5736,14 @@
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
-      <c r="J195" s="4"/>
+      <c r="J195" s="3"/>
     </row>
     <row r="196" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="3" t="s">
-        <v>207</v>
+      <c r="A196" s="21" t="s">
+        <v>468</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -5487,14 +5752,14 @@
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
-      <c r="J196" s="4"/>
+      <c r="J196" s="3"/>
     </row>
     <row r="197" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="3" t="s">
-        <v>209</v>
+      <c r="A197" s="21" t="s">
+        <v>469</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -5503,14 +5768,14 @@
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
-      <c r="J197" s="4"/>
+      <c r="J197" s="3"/>
     </row>
     <row r="198" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="3" t="s">
-        <v>211</v>
+      <c r="A198" s="21" t="s">
+        <v>470</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -5519,14 +5784,14 @@
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
-      <c r="J198" s="4"/>
+      <c r="J198" s="3"/>
     </row>
     <row r="199" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="3" t="s">
-        <v>213</v>
+      <c r="A199" s="21" t="s">
+        <v>471</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>214</v>
+        <v>111</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -5535,14 +5800,14 @@
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
-      <c r="J199" s="4"/>
+      <c r="J199" s="3"/>
     </row>
     <row r="200" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="3" t="s">
-        <v>215</v>
+      <c r="A200" s="21" t="s">
+        <v>472</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -5551,14 +5816,14 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
-      <c r="J200" s="4"/>
+      <c r="J200" s="3"/>
     </row>
     <row r="201" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="3" t="s">
-        <v>217</v>
+      <c r="A201" s="21" t="s">
+        <v>473</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -5567,30 +5832,30 @@
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
-      <c r="J201" s="4"/>
+      <c r="J201" s="3"/>
     </row>
     <row r="202" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="B202" s="18"/>
-      <c r="C202" s="18"/>
-      <c r="D202" s="18"/>
-      <c r="E202" s="18"/>
-      <c r="F202" s="14"/>
-      <c r="G202" s="14"/>
+      <c r="A202" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B202" s="16"/>
+      <c r="C202" s="16"/>
+      <c r="D202" s="16"/>
+      <c r="E202" s="16"/>
+      <c r="F202" s="12"/>
+      <c r="G202" s="12"/>
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
-      <c r="J202" s="4" t="s">
+      <c r="J202" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="3" t="s">
-        <v>220</v>
+      <c r="A203" s="21" t="s">
+        <v>474</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>221</v>
+        <v>115</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
@@ -5599,14 +5864,14 @@
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
-      <c r="J203" s="4"/>
+      <c r="J203" s="3"/>
     </row>
     <row r="204" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="3" t="s">
-        <v>222</v>
+      <c r="A204" s="21" t="s">
+        <v>475</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
@@ -5615,14 +5880,14 @@
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
-      <c r="J204" s="4"/>
+      <c r="J204" s="3"/>
     </row>
     <row r="205" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="3" t="s">
-        <v>224</v>
+      <c r="A205" s="21" t="s">
+        <v>476</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -5631,14 +5896,14 @@
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
-      <c r="J205" s="4"/>
+      <c r="J205" s="3"/>
     </row>
     <row r="206" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="3" t="s">
-        <v>226</v>
+      <c r="A206" s="21" t="s">
+        <v>477</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>227</v>
+        <v>118</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -5647,14 +5912,14 @@
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
-      <c r="J206" s="4"/>
+      <c r="J206" s="3"/>
     </row>
     <row r="207" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="3" t="s">
-        <v>228</v>
+      <c r="A207" s="21" t="s">
+        <v>478</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
@@ -5663,14 +5928,14 @@
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
-      <c r="J207" s="4"/>
+      <c r="J207" s="3"/>
     </row>
     <row r="208" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="3" t="s">
-        <v>230</v>
+      <c r="A208" s="21" t="s">
+        <v>479</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>231</v>
+        <v>120</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
@@ -5679,14 +5944,14 @@
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
-      <c r="J208" s="4"/>
+      <c r="J208" s="3"/>
     </row>
     <row r="209" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="3" t="s">
-        <v>232</v>
+      <c r="A209" s="21" t="s">
+        <v>480</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>233</v>
+        <v>121</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -5695,14 +5960,14 @@
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
-      <c r="J209" s="4"/>
+      <c r="J209" s="3"/>
     </row>
     <row r="210" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="3" t="s">
-        <v>234</v>
+      <c r="A210" s="21" t="s">
+        <v>481</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>235</v>
+        <v>122</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
@@ -5711,14 +5976,14 @@
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
-      <c r="J210" s="4"/>
+      <c r="J210" s="3"/>
     </row>
     <row r="211" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="3" t="s">
-        <v>236</v>
+      <c r="A211" s="21" t="s">
+        <v>482</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>237</v>
+        <v>123</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -5727,14 +5992,14 @@
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
-      <c r="J211" s="4"/>
+      <c r="J211" s="3"/>
     </row>
     <row r="212" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="3" t="s">
-        <v>238</v>
+      <c r="A212" s="21" t="s">
+        <v>483</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>239</v>
+        <v>124</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -5743,14 +6008,14 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
-      <c r="J212" s="4"/>
+      <c r="J212" s="3"/>
     </row>
     <row r="213" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="3" t="s">
-        <v>240</v>
+      <c r="A213" s="21" t="s">
+        <v>484</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>241</v>
+        <v>125</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
@@ -5759,14 +6024,14 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
-      <c r="J213" s="4"/>
+      <c r="J213" s="3"/>
     </row>
     <row r="214" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="3" t="s">
-        <v>242</v>
+      <c r="A214" s="21" t="s">
+        <v>485</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -5775,14 +6040,14 @@
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
-      <c r="J214" s="4"/>
+      <c r="J214" s="3"/>
     </row>
     <row r="215" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="3" t="s">
-        <v>244</v>
+      <c r="A215" s="21" t="s">
+        <v>486</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>245</v>
+        <v>127</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
@@ -5791,14 +6056,14 @@
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
-      <c r="J215" s="4"/>
+      <c r="J215" s="3"/>
     </row>
     <row r="216" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="3" t="s">
-        <v>246</v>
+      <c r="A216" s="21" t="s">
+        <v>487</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>247</v>
+        <v>128</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -5807,14 +6072,14 @@
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
-      <c r="J216" s="4"/>
+      <c r="J216" s="3"/>
     </row>
     <row r="217" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="3" t="s">
-        <v>248</v>
+      <c r="A217" s="21" t="s">
+        <v>488</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>249</v>
+        <v>129</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
@@ -5823,14 +6088,14 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
-      <c r="J217" s="4"/>
+      <c r="J217" s="3"/>
     </row>
     <row r="218" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="3" t="s">
-        <v>250</v>
+      <c r="A218" s="21" t="s">
+        <v>489</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>251</v>
+        <v>130</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -5839,14 +6104,14 @@
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
-      <c r="J218" s="4"/>
+      <c r="J218" s="3"/>
     </row>
     <row r="219" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="3" t="s">
-        <v>252</v>
+      <c r="A219" s="21" t="s">
+        <v>490</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>253</v>
+        <v>131</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
@@ -5855,14 +6120,14 @@
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
-      <c r="J219" s="4"/>
+      <c r="J219" s="3"/>
     </row>
     <row r="220" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="3" t="s">
-        <v>254</v>
+      <c r="A220" s="21" t="s">
+        <v>491</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>255</v>
+        <v>132</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
@@ -5871,14 +6136,14 @@
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
-      <c r="J220" s="4"/>
+      <c r="J220" s="3"/>
     </row>
     <row r="221" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="3" t="s">
-        <v>256</v>
+      <c r="A221" s="21" t="s">
+        <v>492</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
@@ -5887,14 +6152,14 @@
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
-      <c r="J221" s="4"/>
+      <c r="J221" s="3"/>
     </row>
     <row r="222" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="3" t="s">
-        <v>258</v>
+      <c r="A222" s="21" t="s">
+        <v>493</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>259</v>
+        <v>134</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
@@ -5903,30 +6168,30 @@
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
-      <c r="J222" s="4"/>
+      <c r="J222" s="3"/>
     </row>
     <row r="223" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="B223" s="18"/>
-      <c r="C223" s="18"/>
-      <c r="D223" s="18"/>
-      <c r="E223" s="18"/>
-      <c r="F223" s="14"/>
-      <c r="G223" s="14"/>
+      <c r="A223" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B223" s="16"/>
+      <c r="C223" s="16"/>
+      <c r="D223" s="16"/>
+      <c r="E223" s="16"/>
+      <c r="F223" s="12"/>
+      <c r="G223" s="12"/>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
-      <c r="J223" s="4" t="s">
+      <c r="J223" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="3" t="s">
-        <v>495</v>
+      <c r="A224" s="21" t="s">
+        <v>494</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>496</v>
+        <v>255</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
@@ -5935,14 +6200,14 @@
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
-      <c r="J224" s="4"/>
+      <c r="J224" s="3"/>
     </row>
     <row r="225" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="3" t="s">
-        <v>497</v>
+      <c r="A225" s="21" t="s">
+        <v>495</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>498</v>
+        <v>256</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
@@ -5951,14 +6216,14 @@
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
-      <c r="J225" s="4"/>
+      <c r="J225" s="3"/>
     </row>
     <row r="226" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="3" t="s">
-        <v>499</v>
+      <c r="A226" s="21" t="s">
+        <v>496</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>500</v>
+        <v>257</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
@@ -5967,14 +6232,14 @@
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
-      <c r="J226" s="4"/>
+      <c r="J226" s="3"/>
     </row>
     <row r="227" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="3" t="s">
-        <v>501</v>
+      <c r="A227" s="21" t="s">
+        <v>497</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>502</v>
+        <v>258</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
@@ -5983,14 +6248,14 @@
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
-      <c r="J227" s="4"/>
+      <c r="J227" s="3"/>
     </row>
     <row r="228" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="3" t="s">
-        <v>503</v>
+      <c r="A228" s="21" t="s">
+        <v>498</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>504</v>
+        <v>259</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
@@ -5999,14 +6264,14 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
-      <c r="J228" s="4"/>
+      <c r="J228" s="3"/>
     </row>
     <row r="229" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="3" t="s">
-        <v>505</v>
+      <c r="A229" s="21" t="s">
+        <v>499</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>506</v>
+        <v>260</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
@@ -6015,14 +6280,14 @@
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
-      <c r="J229" s="4"/>
+      <c r="J229" s="3"/>
     </row>
     <row r="230" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="3" t="s">
-        <v>507</v>
+      <c r="A230" s="21" t="s">
+        <v>500</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>508</v>
+        <v>261</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
@@ -6031,14 +6296,14 @@
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
-      <c r="J230" s="4"/>
+      <c r="J230" s="3"/>
     </row>
     <row r="231" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="3" t="s">
-        <v>509</v>
+      <c r="A231" s="21" t="s">
+        <v>501</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>510</v>
+        <v>262</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
@@ -6047,14 +6312,14 @@
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
-      <c r="J231" s="4"/>
+      <c r="J231" s="3"/>
     </row>
     <row r="232" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="3" t="s">
-        <v>511</v>
+      <c r="A232" s="21" t="s">
+        <v>502</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>512</v>
+        <v>263</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
@@ -6063,14 +6328,14 @@
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
-      <c r="J232" s="4"/>
+      <c r="J232" s="3"/>
     </row>
     <row r="233" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="3" t="s">
-        <v>513</v>
+      <c r="A233" s="21" t="s">
+        <v>503</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>514</v>
+        <v>264</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
@@ -6079,14 +6344,14 @@
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
-      <c r="J233" s="4"/>
+      <c r="J233" s="3"/>
     </row>
     <row r="234" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="3" t="s">
-        <v>515</v>
+      <c r="A234" s="21" t="s">
+        <v>504</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>516</v>
+        <v>265</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
@@ -6095,14 +6360,14 @@
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
-      <c r="J234" s="4"/>
+      <c r="J234" s="3"/>
     </row>
     <row r="235" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="3" t="s">
-        <v>517</v>
+      <c r="A235" s="21" t="s">
+        <v>505</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>518</v>
+        <v>266</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
@@ -6111,14 +6376,14 @@
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
-      <c r="J235" s="4"/>
+      <c r="J235" s="3"/>
     </row>
     <row r="236" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="3" t="s">
-        <v>519</v>
+      <c r="A236" s="21" t="s">
+        <v>506</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>520</v>
+        <v>267</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
@@ -6127,14 +6392,14 @@
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
-      <c r="J236" s="4"/>
+      <c r="J236" s="3"/>
     </row>
     <row r="237" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="3" t="s">
-        <v>521</v>
+      <c r="A237" s="21" t="s">
+        <v>507</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>522</v>
+        <v>268</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
@@ -6143,14 +6408,14 @@
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
-      <c r="J237" s="4"/>
+      <c r="J237" s="3"/>
     </row>
     <row r="238" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="3" t="s">
-        <v>523</v>
+      <c r="A238" s="21" t="s">
+        <v>508</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>524</v>
+        <v>269</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
@@ -6159,14 +6424,14 @@
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
-      <c r="J238" s="4"/>
+      <c r="J238" s="3"/>
     </row>
     <row r="239" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="3" t="s">
-        <v>525</v>
+      <c r="A239" s="21" t="s">
+        <v>509</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>526</v>
+        <v>270</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
@@ -6175,14 +6440,14 @@
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
-      <c r="J239" s="4"/>
+      <c r="J239" s="3"/>
     </row>
     <row r="240" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="3" t="s">
-        <v>527</v>
+      <c r="A240" s="21" t="s">
+        <v>510</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>528</v>
+        <v>271</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
@@ -6191,14 +6456,14 @@
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
-      <c r="J240" s="4"/>
+      <c r="J240" s="3"/>
     </row>
     <row r="241" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="3" t="s">
-        <v>529</v>
+      <c r="A241" s="21" t="s">
+        <v>511</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>530</v>
+        <v>272</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
@@ -6207,14 +6472,14 @@
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
       <c r="I241" s="2"/>
-      <c r="J241" s="4"/>
+      <c r="J241" s="3"/>
     </row>
     <row r="242" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="3" t="s">
-        <v>531</v>
+      <c r="A242" s="21" t="s">
+        <v>512</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>532</v>
+        <v>273</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
@@ -6223,14 +6488,14 @@
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
-      <c r="J242" s="4"/>
+      <c r="J242" s="3"/>
     </row>
     <row r="243" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="3" t="s">
-        <v>533</v>
+      <c r="A243" s="21" t="s">
+        <v>513</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>534</v>
+        <v>274</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -6239,30 +6504,30 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
-      <c r="J243" s="4"/>
+      <c r="J243" s="3"/>
     </row>
     <row r="244" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="17" t="s">
-        <v>535</v>
-      </c>
-      <c r="B244" s="18"/>
-      <c r="C244" s="18"/>
-      <c r="D244" s="18"/>
-      <c r="E244" s="18"/>
-      <c r="F244" s="14"/>
-      <c r="G244" s="14"/>
+      <c r="A244" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="B244" s="16"/>
+      <c r="C244" s="16"/>
+      <c r="D244" s="16"/>
+      <c r="E244" s="16"/>
+      <c r="F244" s="12"/>
+      <c r="G244" s="12"/>
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
-      <c r="J244" s="4" t="s">
+      <c r="J244" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="3" t="s">
-        <v>261</v>
+      <c r="A245" s="21" t="s">
+        <v>514</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>262</v>
+        <v>136</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
@@ -6271,14 +6536,14 @@
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
-      <c r="J245" s="4"/>
+      <c r="J245" s="3"/>
     </row>
     <row r="246" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="3" t="s">
-        <v>263</v>
+      <c r="A246" s="21" t="s">
+        <v>515</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>264</v>
+        <v>137</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
@@ -6287,14 +6552,14 @@
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
-      <c r="J246" s="4"/>
+      <c r="J246" s="3"/>
     </row>
     <row r="247" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="3" t="s">
-        <v>265</v>
+      <c r="A247" s="21" t="s">
+        <v>517</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
@@ -6303,14 +6568,14 @@
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
-      <c r="J247" s="4"/>
+      <c r="J247" s="3"/>
     </row>
     <row r="248" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="3" t="s">
-        <v>267</v>
+      <c r="A248" s="21" t="s">
+        <v>516</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>268</v>
+        <v>139</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
@@ -6319,14 +6584,14 @@
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
-      <c r="J248" s="4"/>
+      <c r="J248" s="3"/>
     </row>
     <row r="249" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="3" t="s">
-        <v>269</v>
+      <c r="A249" s="21" t="s">
+        <v>518</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
@@ -6335,14 +6600,14 @@
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
-      <c r="J249" s="4"/>
+      <c r="J249" s="3"/>
     </row>
     <row r="250" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="3" t="s">
-        <v>271</v>
+      <c r="A250" s="21" t="s">
+        <v>519</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>272</v>
+        <v>141</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
@@ -6351,14 +6616,14 @@
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="2"/>
-      <c r="J250" s="4"/>
+      <c r="J250" s="3"/>
     </row>
     <row r="251" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="3" t="s">
-        <v>273</v>
+      <c r="A251" s="21" t="s">
+        <v>520</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
@@ -6367,14 +6632,14 @@
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="2"/>
-      <c r="J251" s="4"/>
+      <c r="J251" s="3"/>
     </row>
     <row r="252" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="3" t="s">
-        <v>275</v>
+      <c r="A252" s="21" t="s">
+        <v>521</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>276</v>
+        <v>143</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
@@ -6383,14 +6648,14 @@
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
       <c r="I252" s="2"/>
-      <c r="J252" s="4"/>
+      <c r="J252" s="3"/>
     </row>
     <row r="253" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="3" t="s">
-        <v>277</v>
+      <c r="A253" s="21" t="s">
+        <v>522</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>278</v>
+        <v>144</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
@@ -6399,14 +6664,14 @@
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
       <c r="I253" s="2"/>
-      <c r="J253" s="4"/>
+      <c r="J253" s="3"/>
     </row>
     <row r="254" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="3" t="s">
-        <v>279</v>
+      <c r="A254" s="21" t="s">
+        <v>523</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>280</v>
+        <v>145</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
@@ -6415,14 +6680,14 @@
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
       <c r="I254" s="2"/>
-      <c r="J254" s="4"/>
+      <c r="J254" s="3"/>
     </row>
     <row r="255" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="3" t="s">
-        <v>281</v>
+      <c r="A255" s="21" t="s">
+        <v>524</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>282</v>
+        <v>146</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
@@ -6431,14 +6696,14 @@
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
       <c r="I255" s="2"/>
-      <c r="J255" s="4"/>
+      <c r="J255" s="3"/>
     </row>
     <row r="256" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="3" t="s">
-        <v>283</v>
+      <c r="A256" s="21" t="s">
+        <v>525</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>284</v>
+        <v>147</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
@@ -6447,14 +6712,14 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
       <c r="I256" s="2"/>
-      <c r="J256" s="4"/>
+      <c r="J256" s="3"/>
     </row>
     <row r="257" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="3" t="s">
-        <v>285</v>
+      <c r="A257" s="21" t="s">
+        <v>526</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>286</v>
+        <v>148</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
@@ -6463,14 +6728,14 @@
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
       <c r="I257" s="2"/>
-      <c r="J257" s="4"/>
+      <c r="J257" s="3"/>
     </row>
     <row r="258" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="3" t="s">
-        <v>287</v>
+      <c r="A258" s="21" t="s">
+        <v>527</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>288</v>
+        <v>149</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
@@ -6479,30 +6744,30 @@
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
       <c r="I258" s="2"/>
-      <c r="J258" s="4"/>
+      <c r="J258" s="3"/>
     </row>
     <row r="259" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="B259" s="18"/>
-      <c r="C259" s="18"/>
-      <c r="D259" s="18"/>
-      <c r="E259" s="18"/>
-      <c r="F259" s="14"/>
-      <c r="G259" s="14"/>
+      <c r="A259" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B259" s="16"/>
+      <c r="C259" s="16"/>
+      <c r="D259" s="16"/>
+      <c r="E259" s="16"/>
+      <c r="F259" s="12"/>
+      <c r="G259" s="12"/>
       <c r="H259" s="2"/>
       <c r="I259" s="2"/>
-      <c r="J259" s="4" t="s">
+      <c r="J259" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="3" t="s">
-        <v>447</v>
+      <c r="A260" s="21" t="s">
+        <v>528</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>448</v>
+        <v>230</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
@@ -6511,14 +6776,14 @@
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
       <c r="I260" s="2"/>
-      <c r="J260" s="4"/>
+      <c r="J260" s="3"/>
     </row>
     <row r="261" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="3" t="s">
-        <v>449</v>
+      <c r="A261" s="21" t="s">
+        <v>529</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>450</v>
+        <v>231</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
@@ -6527,14 +6792,14 @@
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
       <c r="I261" s="2"/>
-      <c r="J261" s="4"/>
+      <c r="J261" s="3"/>
     </row>
     <row r="262" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="3" t="s">
-        <v>451</v>
+      <c r="A262" s="21" t="s">
+        <v>530</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>452</v>
+        <v>232</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
@@ -6543,14 +6808,14 @@
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
       <c r="I262" s="2"/>
-      <c r="J262" s="4"/>
+      <c r="J262" s="3"/>
     </row>
     <row r="263" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="3" t="s">
-        <v>453</v>
+      <c r="A263" s="21" t="s">
+        <v>531</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>454</v>
+        <v>233</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
@@ -6559,14 +6824,14 @@
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
       <c r="I263" s="2"/>
-      <c r="J263" s="4"/>
+      <c r="J263" s="3"/>
     </row>
     <row r="264" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="3" t="s">
-        <v>455</v>
+      <c r="A264" s="21" t="s">
+        <v>532</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>456</v>
+        <v>234</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
@@ -6575,14 +6840,14 @@
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
       <c r="I264" s="2"/>
-      <c r="J264" s="4"/>
+      <c r="J264" s="3"/>
     </row>
     <row r="265" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="3" t="s">
-        <v>457</v>
+      <c r="A265" s="21" t="s">
+        <v>533</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>458</v>
+        <v>235</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
@@ -6591,14 +6856,14 @@
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
       <c r="I265" s="2"/>
-      <c r="J265" s="4"/>
+      <c r="J265" s="3"/>
     </row>
     <row r="266" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="3" t="s">
-        <v>459</v>
+      <c r="A266" s="21" t="s">
+        <v>534</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>460</v>
+        <v>236</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
@@ -6607,14 +6872,14 @@
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
       <c r="I266" s="2"/>
-      <c r="J266" s="4"/>
+      <c r="J266" s="3"/>
     </row>
     <row r="267" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="3" t="s">
-        <v>461</v>
+      <c r="A267" s="21" t="s">
+        <v>535</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>462</v>
+        <v>237</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
@@ -6623,14 +6888,14 @@
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
       <c r="I267" s="2"/>
-      <c r="J267" s="4"/>
+      <c r="J267" s="3"/>
     </row>
     <row r="268" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="3" t="s">
-        <v>463</v>
+      <c r="A268" s="21" t="s">
+        <v>536</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>464</v>
+        <v>238</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
@@ -6639,14 +6904,14 @@
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="2"/>
-      <c r="J268" s="4"/>
+      <c r="J268" s="3"/>
     </row>
     <row r="269" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="3" t="s">
-        <v>465</v>
+      <c r="A269" s="21" t="s">
+        <v>537</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>466</v>
+        <v>239</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
@@ -6655,14 +6920,14 @@
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
       <c r="I269" s="2"/>
-      <c r="J269" s="4"/>
+      <c r="J269" s="3"/>
     </row>
     <row r="270" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="3" t="s">
-        <v>467</v>
+      <c r="A270" s="21" t="s">
+        <v>538</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>468</v>
+        <v>240</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
@@ -6671,14 +6936,14 @@
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
       <c r="I270" s="2"/>
-      <c r="J270" s="4"/>
+      <c r="J270" s="3"/>
     </row>
     <row r="271" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="3" t="s">
-        <v>469</v>
+      <c r="A271" s="21" t="s">
+        <v>539</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>470</v>
+        <v>241</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
@@ -6687,14 +6952,14 @@
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
       <c r="I271" s="2"/>
-      <c r="J271" s="4"/>
+      <c r="J271" s="3"/>
     </row>
     <row r="272" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="3" t="s">
-        <v>471</v>
+      <c r="A272" s="21" t="s">
+        <v>540</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>472</v>
+        <v>242</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
@@ -6703,14 +6968,14 @@
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
       <c r="I272" s="2"/>
-      <c r="J272" s="4"/>
+      <c r="J272" s="3"/>
     </row>
     <row r="273" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="3" t="s">
-        <v>473</v>
+      <c r="A273" s="21" t="s">
+        <v>541</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>474</v>
+        <v>243</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -6719,14 +6984,14 @@
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
       <c r="I273" s="2"/>
-      <c r="J273" s="4"/>
+      <c r="J273" s="3"/>
     </row>
     <row r="274" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="3" t="s">
-        <v>475</v>
+      <c r="A274" s="21" t="s">
+        <v>542</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>476</v>
+        <v>244</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
@@ -6735,14 +7000,14 @@
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
       <c r="I274" s="2"/>
-      <c r="J274" s="4"/>
+      <c r="J274" s="3"/>
     </row>
     <row r="275" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="3" t="s">
-        <v>477</v>
+      <c r="A275" s="21" t="s">
+        <v>543</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>478</v>
+        <v>245</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
@@ -6751,14 +7016,14 @@
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
       <c r="I275" s="2"/>
-      <c r="J275" s="4"/>
+      <c r="J275" s="3"/>
     </row>
     <row r="276" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="3" t="s">
-        <v>479</v>
+      <c r="A276" s="21" t="s">
+        <v>544</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>480</v>
+        <v>246</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
@@ -6767,30 +7032,30 @@
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
       <c r="I276" s="2"/>
-      <c r="J276" s="4"/>
+      <c r="J276" s="3"/>
     </row>
     <row r="277" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="17" t="s">
-        <v>481</v>
-      </c>
-      <c r="B277" s="18"/>
-      <c r="C277" s="18"/>
-      <c r="D277" s="18"/>
-      <c r="E277" s="18"/>
-      <c r="F277" s="14"/>
-      <c r="G277" s="14"/>
+      <c r="A277" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="B277" s="16"/>
+      <c r="C277" s="16"/>
+      <c r="D277" s="16"/>
+      <c r="E277" s="16"/>
+      <c r="F277" s="12"/>
+      <c r="G277" s="12"/>
       <c r="H277" s="2"/>
       <c r="I277" s="2"/>
-      <c r="J277" s="4" t="s">
+      <c r="J277" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="3" t="s">
-        <v>482</v>
+      <c r="A278" s="21" t="s">
+        <v>545</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>483</v>
+        <v>248</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
@@ -6799,14 +7064,14 @@
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
       <c r="I278" s="2"/>
-      <c r="J278" s="4"/>
+      <c r="J278" s="3"/>
     </row>
     <row r="279" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="3" t="s">
-        <v>484</v>
+      <c r="A279" s="21" t="s">
+        <v>546</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>485</v>
+        <v>249</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
@@ -6815,14 +7080,14 @@
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
       <c r="I279" s="2"/>
-      <c r="J279" s="4"/>
+      <c r="J279" s="3"/>
     </row>
     <row r="280" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="3" t="s">
-        <v>486</v>
+      <c r="A280" s="21" t="s">
+        <v>547</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>487</v>
+        <v>250</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
@@ -6831,14 +7096,14 @@
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
       <c r="I280" s="2"/>
-      <c r="J280" s="4"/>
+      <c r="J280" s="3"/>
     </row>
     <row r="281" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="3" t="s">
-        <v>488</v>
+      <c r="A281" s="21" t="s">
+        <v>548</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>489</v>
+        <v>251</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
@@ -6847,14 +7112,14 @@
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
       <c r="I281" s="2"/>
-      <c r="J281" s="4"/>
+      <c r="J281" s="3"/>
     </row>
     <row r="282" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="3" t="s">
-        <v>490</v>
+      <c r="A282" s="21" t="s">
+        <v>549</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>491</v>
+        <v>252</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
@@ -6863,14 +7128,14 @@
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
       <c r="I282" s="2"/>
-      <c r="J282" s="4"/>
+      <c r="J282" s="3"/>
     </row>
     <row r="283" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="3" t="s">
-        <v>492</v>
+      <c r="A283" s="21" t="s">
+        <v>550</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>493</v>
+        <v>253</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
@@ -6879,40 +7144,47 @@
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
-      <c r="J283" s="4"/>
+      <c r="J283" s="3"/>
     </row>
     <row r="284" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="B284" s="18"/>
-      <c r="C284" s="18"/>
-      <c r="D284" s="18"/>
-      <c r="E284" s="18"/>
-      <c r="F284" s="14"/>
-      <c r="G284" s="14"/>
+      <c r="A284" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B284" s="16"/>
+      <c r="C284" s="16"/>
+      <c r="D284" s="16"/>
+      <c r="E284" s="16"/>
+      <c r="F284" s="12"/>
+      <c r="G284" s="12"/>
       <c r="H284" s="2"/>
       <c r="I284" s="2"/>
-      <c r="J284" s="4" t="s">
+      <c r="J284" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="19" t="s">
-        <v>542</v>
+        <v>282</v>
       </c>
       <c r="B285" s="20"/>
       <c r="C285" s="20"/>
       <c r="D285" s="20"/>
       <c r="E285" s="20"/>
-      <c r="F285" s="15"/>
-      <c r="G285" s="15"/>
-      <c r="H285" s="5"/>
-      <c r="I285" s="5"/>
-      <c r="J285" s="6"/>
+      <c r="F285" s="13"/>
+      <c r="G285" s="13"/>
+      <c r="H285" s="4"/>
+      <c r="I285" s="4"/>
+      <c r="J285" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A277:E277"/>
+    <mergeCell ref="A284:E284"/>
+    <mergeCell ref="A244:E244"/>
+    <mergeCell ref="A285:E285"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A223:E223"/>
+    <mergeCell ref="A259:E259"/>
     <mergeCell ref="A2:J3"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A173:E173"/>
@@ -6927,19 +7199,12 @@
     <mergeCell ref="A102:E102"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A277:E277"/>
-    <mergeCell ref="A284:E284"/>
-    <mergeCell ref="A244:E244"/>
-    <mergeCell ref="A285:E285"/>
-    <mergeCell ref="A202:E202"/>
-    <mergeCell ref="A223:E223"/>
-    <mergeCell ref="A259:E259"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A7:B21 H7:J7 B1 H1:J1 A141:B172 A22 J22 A173 J173 A177:B201 A203:B222 A202 J202 A245:B258 A223 J223 A259 J259 A260:B276 A278:B283 A277 A284 J284 J277 H4:J4 A174:B175 D4:E4 D1:E1 D7:E7" numberStoredAsText="1"/>
+    <ignoredError sqref="A7:B8 H7:J7 B1 H1:J1 B172 A22 J22 A173 J173 B201 B222 A202 J202 B258 A223 J223 A259 J259 B276 B283 A277 A284 J284 J277 H4:J4 B175 D4:E4 D1:E1 D7:E7 B21 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B141 B142 B143 B144 B145 B146 B147 B148 B149 B150 B151 B152 B153 B154 B155 B156 B157 B158 B159 B160 B161 B162 B163 B164 B165 B166 B167 B168 B169 B170 B171 B174 B177 B178 B179 B180 B181 B182 B183 B184 B185 B186 B187 B188 B189 B190 B191 B192 B193 B194 B195 B196 B197 B198 B199 B200 B203 B204 B205 B206 B207 B208 B209 B210 B211 B212 B213 B214 B215 B216 B217 B218 B219 B220 B221 B245 B246 B247 B248 B249 B250 B251 B252 B253 B254 B255 B256 B257 B260 B261 B262 B263 B264 B265 B266 B267 B268 B269 B270 B271 B272 B273 B274 B275 B278 B279 B280 B281 B282" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>